--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -844,28 +844,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1140,28 +1144,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1436,28 +1444,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1732,28 +1744,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2028,28 +2044,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2324,28 +2344,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2620,28 +2644,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2916,28 +2944,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3212,28 +3244,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3508,28 +3544,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3804,28 +3844,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4100,28 +4144,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4396,28 +4444,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4692,28 +4744,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4988,28 +5044,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5284,28 +5344,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5580,28 +5644,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5876,28 +5944,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6518,28 +6590,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6814,28 +6890,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7110,28 +7190,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7406,28 +7490,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7702,28 +7790,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7998,28 +8090,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8294,28 +8390,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8590,28 +8690,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8886,28 +8990,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9182,28 +9290,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9478,28 +9590,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9774,28 +9890,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10070,28 +10190,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10366,28 +10490,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10662,28 +10790,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10958,28 +11090,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11254,28 +11390,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11550,28 +11690,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire parsed no lineups; not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.2</v>
+        <v>69.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -828,7 +828,7 @@
         <v>35.9</v>
       </c>
       <c r="R2" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.7</v>
+        <v>67.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1128,7 +1128,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>63.5</v>
+        <v>65.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1428,7 +1428,7 @@
         <v>18.2</v>
       </c>
       <c r="R4" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>62.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1728,7 +1728,7 @@
         <v>18.2</v>
       </c>
       <c r="R5" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>61.4</v>
+        <v>63.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2028,7 +2028,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2304,11 +2304,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>58.4</v>
+        <v>60.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2328,7 +2328,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2604,11 +2604,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>58</v>
+        <v>60.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2628,7 +2628,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>57.6</v>
+        <v>59.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2928,7 +2928,7 @@
         <v>35.9</v>
       </c>
       <c r="R9" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.8</v>
+        <v>54</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3228,7 +3228,7 @@
         <v>35.9</v>
       </c>
       <c r="R10" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51.5</v>
+        <v>53.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3528,7 +3528,7 @@
         <v>18.2</v>
       </c>
       <c r="R11" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3828,7 +3828,7 @@
         <v>18.2</v>
       </c>
       <c r="R12" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>50.5</v>
+        <v>52.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -4128,7 +4128,7 @@
         <v>18.2</v>
       </c>
       <c r="R13" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK13" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>47.9</v>
+        <v>50</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4428,7 +4428,7 @@
         <v>18.2</v>
       </c>
       <c r="R14" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK14" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.2</v>
+        <v>46.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4728,7 +4728,7 @@
         <v>35.9</v>
       </c>
       <c r="R15" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK15" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>43.6</v>
+        <v>45.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -5028,7 +5028,7 @@
         <v>18.2</v>
       </c>
       <c r="R16" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK16" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.3</v>
+        <v>42.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5328,7 +5328,7 @@
         <v>18.2</v>
       </c>
       <c r="R17" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK17" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.9</v>
+        <v>39.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5628,7 +5628,7 @@
         <v>17.2</v>
       </c>
       <c r="R18" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S18" t="n">
         <v>76.2</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK18" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.7</v>
+        <v>37.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5928,7 +5928,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK19" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.2</v>
+        <v>69.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6574,7 +6574,7 @@
         <v>35.9</v>
       </c>
       <c r="R2" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.7</v>
+        <v>67.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6874,7 +6874,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>63.5</v>
+        <v>65.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7174,7 +7174,7 @@
         <v>18.2</v>
       </c>
       <c r="R4" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>62.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7474,7 +7474,7 @@
         <v>18.2</v>
       </c>
       <c r="R5" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>61.4</v>
+        <v>63.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7774,7 +7774,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8050,11 +8050,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>58.4</v>
+        <v>60.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8074,7 +8074,7 @@
         <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8350,11 +8350,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>58</v>
+        <v>60.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -8374,7 +8374,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S8" t="n">
         <v>86.40000000000001</v>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>57.6</v>
+        <v>59.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8674,7 +8674,7 @@
         <v>35.9</v>
       </c>
       <c r="R9" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S9" t="n">
         <v>64.3</v>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.8</v>
+        <v>54</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8974,7 +8974,7 @@
         <v>35.9</v>
       </c>
       <c r="R10" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51.5</v>
+        <v>53.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9274,7 +9274,7 @@
         <v>18.2</v>
       </c>
       <c r="R11" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S11" t="n">
         <v>86.40000000000001</v>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.6</v>
+        <v>52.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -9574,7 +9574,7 @@
         <v>18.2</v>
       </c>
       <c r="R12" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>50.5</v>
+        <v>52.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9874,7 +9874,7 @@
         <v>18.2</v>
       </c>
       <c r="R13" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK13" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>47.9</v>
+        <v>50</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10174,7 +10174,7 @@
         <v>18.2</v>
       </c>
       <c r="R14" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK14" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.2</v>
+        <v>46.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -10474,7 +10474,7 @@
         <v>35.9</v>
       </c>
       <c r="R15" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK15" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>43.6</v>
+        <v>45.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -10774,7 +10774,7 @@
         <v>18.2</v>
       </c>
       <c r="R16" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK16" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11050,7 +11050,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.3</v>
+        <v>42.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -11074,7 +11074,7 @@
         <v>18.2</v>
       </c>
       <c r="R17" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK17" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.9</v>
+        <v>39.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -11374,7 +11374,7 @@
         <v>17.2</v>
       </c>
       <c r="R18" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S18" t="n">
         <v>76.2</v>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK18" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11650,7 +11650,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.7</v>
+        <v>37.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -11674,7 +11674,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>60.8</v>
+        <v>75.3</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BK19" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -804,11 +804,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>69.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -831,7 +831,7 @@
         <v>64.8</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -841,39 +841,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1018,7 +1014,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1084,7 +1080,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1108,7 +1104,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>68.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1122,7 +1118,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1135,7 +1131,7 @@
         <v>64.8</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1145,39 +1141,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1322,7 +1314,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1388,7 +1380,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1412,7 +1404,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.7</v>
+        <v>57.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1426,7 +1418,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1439,7 +1431,7 @@
         <v>64.8</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>75</v>
@@ -1449,39 +1441,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1626,7 +1614,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1692,7 +1680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1716,7 +1704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.4</v>
+        <v>57</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1730,7 +1718,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1743,7 +1731,7 @@
         <v>64.8</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1753,39 +1741,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1930,7 +1914,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -1996,7 +1980,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2020,7 +2004,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>56</v>
+        <v>56.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2034,7 +2018,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2047,7 +2031,7 @@
         <v>64.8</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -2057,39 +2041,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2234,7 +2214,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2300,7 +2280,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2324,7 +2304,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>55.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2338,7 +2318,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2351,7 +2331,7 @@
         <v>64.8</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2361,39 +2341,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2538,7 +2514,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2604,7 +2580,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2628,7 +2604,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>54.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2642,7 +2618,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2655,7 +2631,7 @@
         <v>64.8</v>
       </c>
       <c r="S8" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2665,39 +2641,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2842,7 +2814,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2908,7 +2880,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2932,7 +2904,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2946,7 +2918,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2959,7 +2931,7 @@
         <v>64.8</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -2969,39 +2941,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3146,7 +3114,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3212,7 +3180,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3236,7 +3204,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3250,7 +3218,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3263,7 +3231,7 @@
         <v>64.8</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3273,39 +3241,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3450,7 +3414,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3516,7 +3480,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3540,7 +3504,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>51.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3554,7 +3518,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3567,7 +3531,7 @@
         <v>64.8</v>
       </c>
       <c r="S11" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -3577,39 +3541,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3754,7 +3714,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3820,7 +3780,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3844,7 +3804,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3858,7 +3818,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3871,7 +3831,7 @@
         <v>64.8</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3881,39 +3841,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4058,7 +4014,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -4124,7 +4080,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4148,7 +4104,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>45.5</v>
+        <v>46.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4162,7 +4118,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -4175,7 +4131,7 @@
         <v>64.8</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -4185,39 +4141,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4362,7 +4314,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4428,7 +4380,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4452,7 +4404,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>44.7</v>
+        <v>45.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4466,7 +4418,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4479,7 +4431,7 @@
         <v>64.8</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -4489,39 +4441,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4666,7 +4614,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4732,7 +4680,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4756,7 +4704,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4770,7 +4718,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4783,7 +4731,7 @@
         <v>64.8</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -4793,39 +4741,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4970,7 +4914,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -5016,7 +4960,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gabriel Rincones</t>
+          <t>Gabriel Rincones Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5036,7 +4980,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5060,7 +5004,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5074,7 +5018,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -5087,7 +5031,7 @@
         <v>64.8</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
@@ -5097,39 +5041,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -5274,7 +5214,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5340,7 +5280,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5364,7 +5304,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>44.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5378,7 +5318,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5391,7 +5331,7 @@
         <v>64.8</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -5401,39 +5341,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5578,7 +5514,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5644,7 +5580,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5668,7 +5604,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5682,7 +5618,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5695,7 +5631,7 @@
         <v>64.8</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -5705,39 +5641,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5882,7 +5814,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5948,7 +5880,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5972,7 +5904,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.8</v>
+        <v>36.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5986,7 +5918,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5999,7 +5931,7 @@
         <v>64.8</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
@@ -6009,39 +5941,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -6186,7 +6114,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6598,7 +6526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6622,11 +6550,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>69.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6636,7 +6564,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6649,7 +6577,7 @@
         <v>64.8</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6659,39 +6587,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6836,7 +6760,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6902,7 +6826,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6926,7 +6850,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>68.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6940,7 +6864,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6953,7 +6877,7 @@
         <v>64.8</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6963,39 +6887,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7140,7 +7060,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -7206,7 +7126,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7230,7 +7150,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.7</v>
+        <v>57.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7244,7 +7164,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7257,7 +7177,7 @@
         <v>64.8</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>75</v>
@@ -7267,39 +7187,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7444,7 +7360,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -7510,7 +7426,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7534,7 +7450,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.4</v>
+        <v>57</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7548,7 +7464,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7561,7 +7477,7 @@
         <v>64.8</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -7571,39 +7487,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7748,7 +7660,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7814,7 +7726,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7838,7 +7750,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>56</v>
+        <v>56.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7852,7 +7764,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7865,7 +7777,7 @@
         <v>64.8</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7875,39 +7787,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8052,7 +7960,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -8118,7 +8026,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8142,7 +8050,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>55.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8156,7 +8064,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8169,7 +8077,7 @@
         <v>64.8</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -8179,39 +8087,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8356,7 +8260,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -8422,7 +8326,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8446,7 +8350,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>54.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8460,7 +8364,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -8473,7 +8377,7 @@
         <v>64.8</v>
       </c>
       <c r="S8" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -8483,39 +8387,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8660,7 +8560,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8726,7 +8626,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8750,7 +8650,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8764,7 +8664,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8777,7 +8677,7 @@
         <v>64.8</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -8787,39 +8687,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8964,7 +8860,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -9030,7 +8926,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9054,7 +8950,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9068,7 +8964,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9081,7 +8977,7 @@
         <v>64.8</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -9091,39 +8987,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9268,7 +9160,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -9334,7 +9226,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9358,7 +9250,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>51.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9372,7 +9264,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9385,7 +9277,7 @@
         <v>64.8</v>
       </c>
       <c r="S11" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -9395,39 +9287,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9572,7 +9460,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -9638,7 +9526,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9662,7 +9550,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9676,7 +9564,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -9689,7 +9577,7 @@
         <v>64.8</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -9699,39 +9587,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9876,7 +9760,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9942,7 +9826,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9966,7 +9850,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>45.5</v>
+        <v>46.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9980,7 +9864,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9993,7 +9877,7 @@
         <v>64.8</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -10003,39 +9887,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10180,7 +10060,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -10246,7 +10126,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10270,7 +10150,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>44.7</v>
+        <v>45.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10284,7 +10164,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10297,7 +10177,7 @@
         <v>64.8</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -10307,39 +10187,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10484,7 +10360,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -10550,7 +10426,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10574,7 +10450,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10588,7 +10464,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -10601,7 +10477,7 @@
         <v>64.8</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -10611,39 +10487,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10788,7 +10660,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10834,7 +10706,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gabriel Rincones</t>
+          <t>Gabriel Rincones Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10854,7 +10726,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10878,7 +10750,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10892,7 +10764,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -10905,7 +10777,7 @@
         <v>64.8</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
@@ -10915,39 +10787,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -11092,7 +10960,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -11158,7 +11026,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11182,7 +11050,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>44.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11196,7 +11064,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -11209,7 +11077,7 @@
         <v>64.8</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -11219,39 +11087,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11396,7 +11260,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -11462,7 +11326,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11486,7 +11350,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11500,7 +11364,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -11513,7 +11377,7 @@
         <v>64.8</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -11523,39 +11387,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11700,7 +11560,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -11766,7 +11626,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11790,7 +11650,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.8</v>
+        <v>36.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11804,7 +11664,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -11817,7 +11677,7 @@
         <v>64.8</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
@@ -11827,39 +11687,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -12004,7 +11860,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -788,11 +788,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>67.8</v>
+        <v>60.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -806,65 +818,61 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>82.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R2" t="n">
         <v>60.7</v>
       </c>
       <c r="S2" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>74.5</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -901,7 +909,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -974,15 +982,39 @@
           <t>0.2798</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1048,7 +1080,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1072,11 +1104,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.7</v>
+        <v>60.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1086,7 +1118,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1099,7 +1131,7 @@
         <v>60.7</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1109,39 +1141,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1286,7 +1314,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1327,24 +1355,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -1352,19 +1380,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>53.6</v>
+        <v>52.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1378,65 +1418,61 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>47</v>
+        <v>50.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R4" t="n">
         <v>60.7</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>15.3</v>
+        <v>57.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1458,22 +1494,22 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1483,78 +1519,102 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.8553</t>
+          <t>101.1264</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4894</t>
+          <t>0.4679</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.2122</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>70.51</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1986</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.1975</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1620,7 +1680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1628,11 +1688,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>53.3</v>
+        <v>48.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1646,65 +1718,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>38.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R5" t="n">
         <v>60.7</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
         <v>54.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1741,7 +1809,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1814,15 +1882,39 @@
           <t>0.196</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -1863,12 +1955,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1888,12 +1980,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1912,7 +2004,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.1</v>
+        <v>46.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1926,11 +2018,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.8</v>
+        <v>42.5</v>
       </c>
       <c r="Q6" t="n">
         <v>15.3</v>
@@ -1939,49 +2031,45 @@
         <v>60.7</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>57.8</v>
+        <v>34.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2006,17 +2094,17 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2031,67 +2119,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.1264</t>
+          <t>100.3793</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4679</t>
+          <t>0.3977</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2122</t>
+          <t>0.1805</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.3075</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.51</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>52.68</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.1907</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2126,7 +2214,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2167,12 +2255,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2192,19 +2280,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>49.5</v>
+        <v>46.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2218,65 +2318,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>39.2</v>
+        <v>47</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R7" t="n">
         <v>60.7</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2293,12 +2389,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2308,12 +2404,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2323,78 +2419,102 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.5962</t>
+          <t>100.8553</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3663</t>
+          <t>0.4894</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1528</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.2866</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>74.08</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1678</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1986</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2435,24 +2555,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>502671</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Paul Goldschmidt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -2460,19 +2580,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>48.3</v>
+        <v>44.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2486,65 +2618,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>33.8</v>
+        <v>39.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R8" t="n">
         <v>60.7</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8</v>
+        <v>18.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2566,103 +2694,127 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 3/25, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>98.5765</t>
+          <t>99.7145</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1917</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>71.69</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1697</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+          <t>0.2004</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2703,12 +2855,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2728,19 +2880,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>47.8</v>
+        <v>44.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2754,65 +2918,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>45.5</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R9" t="n">
         <v>60.7</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2829,27 +2989,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2859,78 +3019,102 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.0294</t>
+          <t>101.4308</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.4963</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.2478</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3265</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1622</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+          <t>0.234</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -2971,24 +3155,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -2996,19 +3180,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>45.8</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3022,65 +3218,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>43.9</v>
+        <v>30.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R10" t="n">
         <v>60.7</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>4.5</v>
+        <v>26.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3097,12 +3289,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3112,12 +3304,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3127,78 +3319,102 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5901</t>
+          <t>98.5451</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4091</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1732</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>32.13</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1879</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1779</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3239,24 +3455,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -3264,31 +3480,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>45.8</v>
+        <v>43.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3302,62 +3518,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>42.5</v>
+        <v>33.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R11" t="n">
         <v>60.7</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>34.9</v>
+        <v>0.8</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3377,132 +3589,132 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>38.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.3793</t>
+          <t>98.5765</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3977</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1805</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3075</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>52.68</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1907</t>
+          <t>0.1697</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3543,24 +3755,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>691176</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jasson Domínguez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -3568,19 +3780,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>45.6</v>
+        <v>43</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3594,65 +3818,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>33.3</v>
+        <v>28</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>15.2</v>
       </c>
       <c r="R12" t="n">
         <v>60.7</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>4.2</v>
+        <v>43.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3669,27 +3889,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3699,78 +3919,102 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.9121</t>
+          <t>100.8327</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4172</t>
+          <t>0.3791</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1521</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3461</t>
+          <t>0.3046</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>74.17</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1497</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.1632</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -3811,24 +4055,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>641857</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -3836,31 +4080,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>45.3</v>
+        <v>42.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3874,62 +4118,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>49.9</v>
+        <v>45.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R13" t="n">
         <v>60.7</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3949,27 +4189,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3979,102 +4219,102 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>102.1951</t>
+          <t>101.0294</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4113</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1807</t>
+          <t>0.1864</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3122</t>
+          <t>0.3265</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>74.49</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1677</t>
+          <t>0.1622</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4115,12 +4355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>669224</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4140,12 +4380,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4164,7 +4404,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.9</v>
+        <v>41.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4178,11 +4418,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>30.2</v>
+        <v>36.7</v>
       </c>
       <c r="Q14" t="n">
         <v>15.3</v>
@@ -4191,49 +4431,45 @@
         <v>60.7</v>
       </c>
       <c r="S14" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>26.4</v>
+        <v>41.2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4253,22 +4489,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -4283,67 +4519,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.5451</t>
+          <t>100.623</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.3675</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.2877</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>46.73</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1365</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4378,7 +4614,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4419,24 +4655,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>691176</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jasson Dominguez</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -4444,31 +4680,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>43.8</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4482,62 +4718,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>28</v>
+        <v>33.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.2</v>
+        <v>11.5</v>
       </c>
       <c r="R15" t="n">
         <v>60.7</v>
       </c>
       <c r="S15" t="n">
-        <v>92.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>43.2</v>
+        <v>4.2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4557,27 +4789,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4587,102 +4819,102 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.8327</t>
+          <t>98.9121</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3791</t>
+          <t>0.4172</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1521</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3046</t>
+          <t>0.3461</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>21.08</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>44.08</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1632</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -4723,12 +4955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4748,19 +4980,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>38.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4774,65 +5018,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>27.4</v>
+        <v>21.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.2</v>
+        <v>11.5</v>
       </c>
       <c r="R16" t="n">
         <v>60.7</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>36</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4849,12 +5089,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4864,12 +5104,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4879,78 +5119,102 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.14</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.1334</t>
+          <t>98.4444</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1265</t>
+          <t>0.1209</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.3161</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.55</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1472</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+          <t>0.1315</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -4991,12 +5255,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680474</t>
+          <t>683011</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Max Schuemann</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5016,12 +5280,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5040,7 +5304,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.4</v>
+        <v>34.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5054,11 +5318,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>33</v>
+        <v>21.9</v>
       </c>
       <c r="Q17" t="n">
         <v>15.3</v>
@@ -5067,49 +5331,45 @@
         <v>60.7</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>22</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 5 vs RotoWire 9</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5134,7 +5394,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5144,7 +5404,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 4/15, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5154,72 +5414,72 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.21</t>
+          <t>88.25</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4682</t>
+          <t>98.8398</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3557</t>
+          <t>0.3427</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.1127</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2975</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1649</t>
+          <t>0.1097</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5254,7 +5514,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5295,24 +5555,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>683011</t>
+          <t>672613</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Eliezer Alfonzo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -5320,31 +5580,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34</v>
+        <v>29.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5358,65 +5618,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>21.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
       <c r="R18" t="n">
         <v>60.7</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5428,17 +5684,17 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5448,117 +5704,117 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 0 HR</t>
+          <t>Last 5 games: 0/9, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.8398</t>
+          <t>95.0081</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3427</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1127</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2975</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1097</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5599,12 +5855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>645305</t>
+          <t>676609</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ali Sanchez</t>
+          <t>José Caballero</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5624,7 +5880,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5648,7 +5904,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.2</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5662,11 +5918,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q19" t="n">
         <v>15.3</v>
@@ -5675,49 +5931,45 @@
         <v>60.7</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>9.300000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5737,12 +5989,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5752,7 +6004,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/11, 0 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -5767,67 +6019,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.46</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.6331</t>
+          <t>96.3508</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.3306</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0847</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2776</t>
+          <t>0.2794</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>68.96</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0702</t>
+          <t>0.1348</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5862,7 +6114,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6274,7 +6526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6282,11 +6534,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>67.8</v>
+        <v>60.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6300,65 +6564,61 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>82.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R2" t="n">
         <v>60.7</v>
       </c>
       <c r="S2" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>74.5</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -6395,7 +6655,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -6468,15 +6728,39 @@
           <t>0.2798</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6542,7 +6826,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6566,11 +6850,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.7</v>
+        <v>60.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6580,7 +6864,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6593,7 +6877,7 @@
         <v>60.7</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6603,39 +6887,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6780,7 +7060,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -6821,24 +7101,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -6846,19 +7126,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>53.6</v>
+        <v>52.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6872,65 +7164,61 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>47</v>
+        <v>50.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R4" t="n">
         <v>60.7</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>15.3</v>
+        <v>57.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -6952,22 +7240,22 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6977,78 +7265,102 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.8553</t>
+          <t>101.1264</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4894</t>
+          <t>0.4679</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.2122</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>70.51</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1986</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.1975</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -7114,7 +7426,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7122,11 +7434,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>53.3</v>
+        <v>48.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7140,65 +7464,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
         <v>38.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R5" t="n">
         <v>60.7</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U5" t="n">
         <v>54.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -7235,7 +7555,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -7308,15 +7628,39 @@
           <t>0.196</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7357,12 +7701,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7382,12 +7726,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7406,7 +7750,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.1</v>
+        <v>46.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7420,11 +7764,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>50.8</v>
+        <v>42.5</v>
       </c>
       <c r="Q6" t="n">
         <v>15.3</v>
@@ -7433,49 +7777,45 @@
         <v>60.7</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>57.8</v>
+        <v>34.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7500,17 +7840,17 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -7525,67 +7865,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.1264</t>
+          <t>100.3793</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4679</t>
+          <t>0.3977</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2122</t>
+          <t>0.1805</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.3075</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.51</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>52.68</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.1907</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7620,7 +7960,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -7661,12 +8001,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7686,19 +8026,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>49.5</v>
+        <v>46.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7712,65 +8064,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>39.2</v>
+        <v>47</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R7" t="n">
         <v>60.7</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7787,12 +8135,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7802,12 +8150,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7817,78 +8165,102 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.5962</t>
+          <t>100.8553</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3663</t>
+          <t>0.4894</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1528</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.2866</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>74.08</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1678</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1986</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -7929,24 +8301,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>502671</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Paul Goldschmidt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -7954,19 +8326,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>48.3</v>
+        <v>44.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7980,65 +8364,61 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>33.8</v>
+        <v>39.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R8" t="n">
         <v>60.7</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8</v>
+        <v>18.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -8060,103 +8440,127 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 3/25, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>98.5765</t>
+          <t>99.7145</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1917</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>71.69</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1697</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+          <t>0.2004</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8197,12 +8601,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8222,19 +8626,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>47.8</v>
+        <v>44.5</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8248,65 +8664,61 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>45.5</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>11.5</v>
       </c>
       <c r="R9" t="n">
         <v>60.7</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -8323,27 +8735,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8353,78 +8765,102 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.96</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.0294</t>
+          <t>101.4308</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.4963</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.2478</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3265</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1622</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+          <t>0.234</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -8465,24 +8901,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -8490,19 +8926,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>45.8</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8516,65 +8964,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>43.9</v>
+        <v>30.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>15.3</v>
       </c>
       <c r="R10" t="n">
         <v>60.7</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>4.5</v>
+        <v>26.4</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -8591,12 +9035,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8606,12 +9050,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8621,78 +9065,102 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5901</t>
+          <t>98.5451</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4091</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1732</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>32.13</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1879</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1779</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -8733,24 +9201,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -8758,31 +9226,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>45.8</v>
+        <v>43.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8796,62 +9264,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>42.5</v>
+        <v>33.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R11" t="n">
         <v>60.7</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U11" t="n">
-        <v>34.9</v>
+        <v>0.8</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8871,132 +9335,132 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>38.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.3793</t>
+          <t>98.5765</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3977</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1805</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3075</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>52.68</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1907</t>
+          <t>0.1697</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -9037,24 +9501,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>691176</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jasson Domínguez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -9062,19 +9526,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Will Klein</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>694361</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>45.6</v>
+        <v>43</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9088,65 +9564,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>33.3</v>
+        <v>28</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>15.2</v>
       </c>
       <c r="R12" t="n">
         <v>60.7</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>4.2</v>
+        <v>43.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -9163,27 +9635,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9193,78 +9665,102 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.9121</t>
+          <t>100.8327</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4172</t>
+          <t>0.3791</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1521</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3461</t>
+          <t>0.3046</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>74.17</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1497</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.1632</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>38.86</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>88.65</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.3158</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.0838</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9305,24 +9801,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>641857</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -9330,31 +9826,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>45.3</v>
+        <v>42.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9368,62 +9864,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>49.9</v>
+        <v>45.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R13" t="n">
         <v>60.7</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9443,27 +9935,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9473,102 +9965,102 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>45.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>91.55</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>102.1951</t>
+          <t>101.0294</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4113</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1807</t>
+          <t>0.1864</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3122</t>
+          <t>0.3265</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>74.49</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1677</t>
+          <t>0.1622</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -9609,12 +10101,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>669224</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Austin Wells</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9634,12 +10126,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9658,7 +10150,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.9</v>
+        <v>41.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9672,11 +10164,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>30.2</v>
+        <v>36.7</v>
       </c>
       <c r="Q14" t="n">
         <v>15.3</v>
@@ -9685,49 +10177,45 @@
         <v>60.7</v>
       </c>
       <c r="S14" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>26.4</v>
+        <v>41.2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9747,22 +10235,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -9777,67 +10265,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.5451</t>
+          <t>100.623</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.3675</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.2877</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>46.73</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1365</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9872,7 +10360,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -9913,24 +10401,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>691176</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jasson Dominguez</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -9938,31 +10426,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>43.8</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9976,62 +10464,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>28</v>
+        <v>33.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.2</v>
+        <v>11.5</v>
       </c>
       <c r="R15" t="n">
         <v>60.7</v>
       </c>
       <c r="S15" t="n">
-        <v>92.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>43.2</v>
+        <v>4.2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10051,27 +10535,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -10081,102 +10565,102 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.8327</t>
+          <t>98.9121</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3791</t>
+          <t>0.4172</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1521</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3046</t>
+          <t>0.3461</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>21.08</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>44.08</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1632</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10217,12 +10701,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10242,19 +10726,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ryan Yarbrough</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>642232</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>38.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10268,65 +10764,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>27.4</v>
+        <v>21.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.2</v>
+        <v>11.5</v>
       </c>
       <c r="R16" t="n">
         <v>60.7</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>36</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10343,12 +10835,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10358,12 +10850,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10373,78 +10865,102 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.14</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.1334</t>
+          <t>98.4444</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1265</t>
+          <t>0.1209</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.3161</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.55</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1472</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+          <t>0.1315</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>84.49</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.3394</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -10485,12 +11001,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680474</t>
+          <t>683011</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Max Schuemann</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10510,12 +11026,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10534,7 +11050,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.4</v>
+        <v>34.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10548,11 +11064,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>33</v>
+        <v>21.9</v>
       </c>
       <c r="Q17" t="n">
         <v>15.3</v>
@@ -10561,49 +11077,45 @@
         <v>60.7</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>22</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed; order MLB 5 vs RotoWire 9</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10628,7 +11140,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10638,7 +11150,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 4/15, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -10648,72 +11160,72 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.21</t>
+          <t>88.25</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.4682</t>
+          <t>98.8398</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3557</t>
+          <t>0.3427</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.1127</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2975</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.82</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1649</t>
+          <t>0.1097</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10748,7 +11260,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -10789,24 +11301,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>683011</t>
+          <t>672613</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Eliezer Alfonzo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -10814,31 +11326,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34</v>
+        <v>29.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10852,65 +11364,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>21.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
       <c r="R18" t="n">
         <v>60.7</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10922,17 +11430,17 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10942,117 +11450,117 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 0 HR</t>
+          <t>Last 5 games: 0/9, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.8398</t>
+          <t>95.0081</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3427</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1127</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2975</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1097</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -11093,12 +11601,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>645305</t>
+          <t>676609</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ali Sanchez</t>
+          <t>José Caballero</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -11118,7 +11626,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11142,7 +11650,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.2</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11156,11 +11664,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q19" t="n">
         <v>15.3</v>
@@ -11169,49 +11677,45 @@
         <v>60.7</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>9.300000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11231,12 +11735,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -11246,7 +11750,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/11, 0 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -11261,67 +11765,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.46</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.6331</t>
+          <t>96.3508</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.3306</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0847</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2776</t>
+          <t>0.2794</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>68.96</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0702</t>
+          <t>0.1348</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -11356,7 +11860,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>175 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>11.5</v>
       </c>
       <c r="R2" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1027,19 +1027,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1080,7 +1072,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1104,7 +1096,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.3</v>
+        <v>60.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1128,7 +1120,7 @@
         <v>15.3</v>
       </c>
       <c r="R3" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -1319,7 +1311,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1327,19 +1319,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1380,7 +1364,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1404,7 +1388,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.7</v>
+        <v>53.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1428,7 +1412,7 @@
         <v>15.3</v>
       </c>
       <c r="R4" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -1619,7 +1603,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1627,19 +1611,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -1680,7 +1656,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1704,7 +1680,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.4</v>
+        <v>49</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1728,7 +1704,7 @@
         <v>11.5</v>
       </c>
       <c r="R5" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1919,7 +1895,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1927,19 +1903,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -1980,7 +1948,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2004,7 +1972,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.4</v>
+        <v>46.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2028,7 +1996,7 @@
         <v>15.3</v>
       </c>
       <c r="R6" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -2219,7 +2187,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2227,19 +2195,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2280,7 +2240,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2304,7 +2264,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.2</v>
+        <v>46.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2328,7 +2288,7 @@
         <v>11.5</v>
       </c>
       <c r="R7" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2519,7 +2479,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2527,19 +2487,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -2580,7 +2532,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2604,7 +2556,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.6</v>
+        <v>45.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2628,7 +2580,7 @@
         <v>15.3</v>
       </c>
       <c r="R8" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -2819,7 +2771,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2827,19 +2779,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -2855,24 +2799,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -2880,31 +2824,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ryan Yarbrough</t>
+          <t>Will Klein</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>642232</t>
+          <t>694361</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2918,26 +2862,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>57.3</v>
+        <v>30.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.5</v>
+        <v>15.3</v>
       </c>
       <c r="R9" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S9" t="n">
-        <v>52.4</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>26.4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2951,7 +2895,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2989,27 +2933,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -3019,97 +2963,97 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.46</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.4308</t>
+          <t>98.5451</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4963</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2478</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>32.13</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>84.49</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3394</t>
+          <t>0.3158</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.0838</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -3119,7 +3063,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3127,19 +3071,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -3155,24 +3091,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -3180,31 +3116,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3218,26 +3154,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>30.2</v>
+        <v>57.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R10" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S10" t="n">
-        <v>94.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>26.4</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3251,7 +3187,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3289,27 +3225,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3319,97 +3255,97 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.5451</t>
+          <t>101.4308</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.4963</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.2478</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.234</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -3419,7 +3355,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3427,19 +3363,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -3480,7 +3408,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3504,7 +3432,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.4</v>
+        <v>43.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3528,7 +3456,7 @@
         <v>11.5</v>
       </c>
       <c r="R11" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -3719,7 +3647,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3727,19 +3655,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -3780,7 +3700,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3804,7 +3724,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3828,7 +3748,7 @@
         <v>15.2</v>
       </c>
       <c r="R12" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -4019,7 +3939,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -4027,19 +3947,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -4080,7 +3992,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4104,7 +4016,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>42.9</v>
+        <v>43.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4128,7 +4040,7 @@
         <v>11.5</v>
       </c>
       <c r="R13" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S13" t="n">
         <v>64.3</v>
@@ -4319,7 +4231,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4327,19 +4239,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -4380,7 +4284,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4404,7 +4308,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4428,7 +4332,7 @@
         <v>15.3</v>
       </c>
       <c r="R14" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -4619,7 +4523,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4627,19 +4531,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -4680,7 +4576,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4704,7 +4600,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4728,7 +4624,7 @@
         <v>11.5</v>
       </c>
       <c r="R15" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -4919,7 +4815,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4927,19 +4823,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -4980,7 +4868,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5004,7 +4892,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5028,7 +4916,7 @@
         <v>11.5</v>
       </c>
       <c r="R16" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -5219,7 +5107,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -5227,19 +5115,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -5280,7 +5160,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5304,7 +5184,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.6</v>
+        <v>35.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5328,7 +5208,7 @@
         <v>15.3</v>
       </c>
       <c r="R17" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -5519,7 +5399,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5527,19 +5407,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -5580,7 +5452,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5604,7 +5476,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.1</v>
+        <v>29.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5628,7 +5500,7 @@
         <v>10.8</v>
       </c>
       <c r="R18" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -5819,7 +5691,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5827,19 +5699,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -5880,7 +5744,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5904,7 +5768,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.9</v>
+        <v>27.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5928,7 +5792,7 @@
         <v>15.3</v>
       </c>
       <c r="R19" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -6119,7 +5983,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6127,19 +5991,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -6526,7 +6382,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6550,7 +6406,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6574,7 +6430,7 @@
         <v>11.5</v>
       </c>
       <c r="R2" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S2" t="n">
         <v>93.2</v>
@@ -6765,7 +6621,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6773,19 +6629,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -6826,7 +6674,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6850,7 +6698,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.3</v>
+        <v>60.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6874,7 +6722,7 @@
         <v>15.3</v>
       </c>
       <c r="R3" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -7065,7 +6913,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -7073,19 +6921,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -7126,7 +6966,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7150,7 +6990,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.7</v>
+        <v>53.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7174,7 +7014,7 @@
         <v>15.3</v>
       </c>
       <c r="R4" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -7365,7 +7205,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -7373,19 +7213,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -7426,7 +7258,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7450,7 +7282,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.4</v>
+        <v>49</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7474,7 +7306,7 @@
         <v>11.5</v>
       </c>
       <c r="R5" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7665,7 +7497,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7673,19 +7505,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -7726,7 +7550,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7750,7 +7574,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.4</v>
+        <v>46.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7774,7 +7598,7 @@
         <v>15.3</v>
       </c>
       <c r="R6" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -7965,7 +7789,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7973,19 +7797,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -8026,7 +7842,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8050,7 +7866,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.2</v>
+        <v>46.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8074,7 +7890,7 @@
         <v>11.5</v>
       </c>
       <c r="R7" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -8265,7 +8081,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -8273,19 +8089,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -8326,7 +8134,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8350,7 +8158,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.6</v>
+        <v>45.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8374,7 +8182,7 @@
         <v>15.3</v>
       </c>
       <c r="R8" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -8565,7 +8373,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8573,19 +8381,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -8601,24 +8401,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -8626,31 +8426,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ryan Yarbrough</t>
+          <t>Will Klein</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>642232</t>
+          <t>694361</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.5</v>
+        <v>45.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8664,26 +8464,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>57.3</v>
+        <v>30.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.5</v>
+        <v>15.3</v>
       </c>
       <c r="R9" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S9" t="n">
-        <v>52.4</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>37.8</v>
+        <v>26.4</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -8697,7 +8497,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8735,27 +8535,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8765,97 +8565,97 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.46</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.4308</t>
+          <t>98.5451</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4963</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2478</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>32.13</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>84.49</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3394</t>
+          <t>0.3158</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.0838</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -8865,7 +8665,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8873,19 +8673,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -8901,24 +8693,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-07-19T23:20:00Z</t>
@@ -8926,31 +8718,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Will Klein</t>
+          <t>Ryan Yarbrough</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>694361</t>
+          <t>642232</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8964,26 +8756,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>30.2</v>
+        <v>57.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="R10" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S10" t="n">
-        <v>94.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>26.4</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8997,7 +8789,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -9035,27 +8827,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.7% barrel, 1.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -9065,97 +8857,97 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>46.74</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.5451</t>
+          <t>101.4308</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.4963</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.2478</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.234</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>84.49</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3158</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.0838</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -9165,7 +8957,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -9173,19 +8965,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -9226,7 +9010,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9250,7 +9034,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.4</v>
+        <v>43.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9274,7 +9058,7 @@
         <v>11.5</v>
       </c>
       <c r="R11" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -9465,7 +9249,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -9473,19 +9257,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -9526,7 +9302,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9550,7 +9326,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9574,7 +9350,7 @@
         <v>15.2</v>
       </c>
       <c r="R12" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -9765,7 +9541,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9773,19 +9549,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -9826,7 +9594,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9850,7 +9618,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>42.9</v>
+        <v>43.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9874,7 +9642,7 @@
         <v>11.5</v>
       </c>
       <c r="R13" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S13" t="n">
         <v>64.3</v>
@@ -10065,7 +9833,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -10073,19 +9841,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -10126,7 +9886,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10150,7 +9910,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10174,7 +9934,7 @@
         <v>15.3</v>
       </c>
       <c r="R14" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -10365,7 +10125,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -10373,19 +10133,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -10426,7 +10178,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10450,7 +10202,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10474,7 +10226,7 @@
         <v>11.5</v>
       </c>
       <c r="R15" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -10665,7 +10417,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10673,19 +10425,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -10726,7 +10470,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10750,7 +10494,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10774,7 +10518,7 @@
         <v>11.5</v>
       </c>
       <c r="R16" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S16" t="n">
         <v>76.2</v>
@@ -10965,7 +10709,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10973,19 +10717,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -11026,7 +10762,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11050,7 +10786,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.6</v>
+        <v>35.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11074,7 +10810,7 @@
         <v>15.3</v>
       </c>
       <c r="R17" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -11265,7 +11001,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -11273,19 +11009,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -11326,7 +11054,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11350,7 +11078,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.1</v>
+        <v>29.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11374,7 +11102,7 @@
         <v>10.8</v>
       </c>
       <c r="R18" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -11565,7 +11293,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -11573,19 +11301,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -11626,7 +11346,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11650,7 +11370,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.9</v>
+        <v>27.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11674,7 +11394,7 @@
         <v>15.3</v>
       </c>
       <c r="R19" t="n">
-        <v>60.7</v>
+        <v>64.2</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11865,7 +11585,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
+          <t>NOAA link only</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -11873,19 +11593,11 @@
           <t>https://forecast.weather.gov/MapClick.php?lat=40.8296&amp;lon=-73.9262</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -831,7 +831,7 @@
         <v>62.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -841,39 +841,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1059,24 +1055,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1094,12 +1090,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1108,7 +1104,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.5</v>
+        <v>59.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1122,14 +1118,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.3</v>
+        <v>40.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R3" t="n">
         <v>62.1</v>
@@ -1141,7 +1137,7 @@
         <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>72.2</v>
+        <v>51.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1193,12 +1189,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1213,107 +1209,107 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.5329</t>
+          <t>100.7812</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4627</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3309</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>55.07</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1696</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1359,24 +1355,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1394,12 +1390,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1408,7 +1404,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.2</v>
+        <v>57.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1422,62 +1418,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
         <v>62.1</v>
       </c>
       <c r="S4" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>33.9</v>
+        <v>72.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1497,127 +1489,127 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.6508</t>
+          <t>100.5329</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4627</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3309</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2075</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -1663,24 +1655,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1693,17 +1685,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1712,7 +1704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1726,62 +1718,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>40.5</v>
+        <v>51.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R5" t="n">
         <v>62.1</v>
       </c>
       <c r="S5" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1801,12 +1789,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1821,107 +1809,107 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.7812</t>
+          <t>104.2616</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.4593</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>75.51</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.07</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -1967,24 +1955,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -1997,17 +1985,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2016,7 +2004,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2030,26 +2018,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.8</v>
+        <v>42.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R6" t="n">
         <v>62.1</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>50.8</v>
+        <v>33.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -2063,7 +2051,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2101,127 +2089,127 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.2616</t>
+          <t>101.6508</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4593</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>43.04</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.2075</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -2267,24 +2255,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2297,17 +2285,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2316,7 +2304,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>55.4</v>
+        <v>53.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2330,62 +2318,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>33.6</v>
+        <v>50.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
         <v>62.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2405,12 +2389,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2420,112 +2404,112 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.33</t>
+          <t>101.8619</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3967</t>
+          <t>0.4502</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.2002</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3018</t>
+          <t>0.3368</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1812</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2571,24 +2555,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2601,17 +2585,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2620,7 +2604,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.9</v>
+        <v>53.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2634,26 +2618,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50.3</v>
+        <v>31.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R8" t="n">
         <v>62.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>26.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2667,7 +2651,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2710,122 +2694,122 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/29, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.8619</t>
+          <t>100.0639</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4502</t>
+          <t>0.4404</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2002</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3368</t>
+          <t>0.3466</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2871,24 +2855,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -2901,17 +2885,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2920,7 +2904,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.9</v>
+        <v>52</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2934,62 +2918,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>31.1</v>
+        <v>45.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
         <v>62.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>26.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3014,122 +2994,122 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.0639</t>
+          <t>101.3479</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4404</t>
+          <t>0.4376</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3466</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>24.76</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -3175,12 +3155,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3205,7 +3185,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3224,7 +3204,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.5</v>
+        <v>51.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3238,11 +3218,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>42.2</v>
+        <v>33.6</v>
       </c>
       <c r="Q10" t="n">
         <v>62.7</v>
@@ -3251,49 +3231,45 @@
         <v>62.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>81.7</v>
+        <v>0.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3313,27 +3289,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3343,67 +3319,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5346</t>
+          <t>99.33</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.3967</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1812</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3479,24 +3455,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -3514,12 +3490,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3528,7 +3504,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>50.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3542,14 +3518,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>45.1</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R11" t="n">
         <v>62.1</v>
@@ -3561,7 +3537,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>13.3</v>
+        <v>61.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3613,127 +3589,127 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>85.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.3479</t>
+          <t>97.1381</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4376</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1225</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -3828,7 +3804,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3842,7 +3818,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3855,7 +3831,7 @@
         <v>62.1</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
@@ -3865,39 +3841,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4083,24 +4055,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -4113,17 +4085,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4132,7 +4104,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4146,62 +4118,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R13" t="n">
         <v>62.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>61.4</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4221,7 +4189,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -4231,117 +4199,117 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.1381</t>
+          <t>98.1545</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1225</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.3022</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -4387,24 +4355,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -4417,17 +4385,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4436,7 +4404,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4450,26 +4418,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>17.5</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R14" t="n">
         <v>62.1</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>20.9</v>
+        <v>17.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4483,7 +4451,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4521,12 +4489,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4536,112 +4504,112 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>36.88</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.1545</t>
+          <t>99.4273</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.4244</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3022</t>
+          <t>0.3127</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.1533</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -4987,12 +4955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>664774</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5017,7 +4985,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5036,7 +5004,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>45.9</v>
+        <v>44.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5050,11 +5018,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>28.6</v>
+        <v>13.9</v>
       </c>
       <c r="Q16" t="n">
         <v>62.7</v>
@@ -5063,49 +5031,45 @@
         <v>62.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>17.7</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5125,12 +5089,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -5140,12 +5104,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -5155,67 +5119,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.88</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>86.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.4273</t>
+          <t>97.8228</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4244</t>
+          <t>0.2958</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1013</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3127</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -6586,7 +6550,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6600,7 +6564,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6613,7 +6577,7 @@
         <v>62.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6623,39 +6587,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6841,24 +6801,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -6876,12 +6836,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -6890,7 +6850,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>57.5</v>
+        <v>59.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6904,14 +6864,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.3</v>
+        <v>40.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R3" t="n">
         <v>62.1</v>
@@ -6923,7 +6883,7 @@
         <v>80</v>
       </c>
       <c r="U3" t="n">
-        <v>72.2</v>
+        <v>51.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -6975,12 +6935,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -6995,107 +6955,107 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.5329</t>
+          <t>100.7812</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4627</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3309</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>55.07</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1696</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -7141,24 +7101,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7176,12 +7136,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -7190,7 +7150,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.2</v>
+        <v>57.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7204,62 +7164,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
         <v>62.1</v>
       </c>
       <c r="S4" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>33.9</v>
+        <v>72.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7279,127 +7235,127 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.6508</t>
+          <t>100.5329</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4627</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3309</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2075</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -7445,24 +7401,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7475,17 +7431,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7494,7 +7450,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7508,62 +7464,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>40.5</v>
+        <v>51.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R5" t="n">
         <v>62.1</v>
       </c>
       <c r="S5" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7583,12 +7535,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -7603,107 +7555,107 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.7812</t>
+          <t>104.2616</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.4593</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>75.51</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.07</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -7749,24 +7701,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -7779,17 +7731,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7798,7 +7750,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7812,26 +7764,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.8</v>
+        <v>42.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R6" t="n">
         <v>62.1</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>50.8</v>
+        <v>33.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7845,7 +7797,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7883,127 +7835,127 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.2616</t>
+          <t>101.6508</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4593</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>43.04</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.2075</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -8049,24 +8001,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -8079,17 +8031,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -8098,7 +8050,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>55.4</v>
+        <v>53.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8112,62 +8064,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>33.6</v>
+        <v>50.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R7" t="n">
         <v>62.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8187,12 +8135,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -8202,112 +8150,112 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.33</t>
+          <t>101.8619</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3967</t>
+          <t>0.4502</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.2002</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3018</t>
+          <t>0.3368</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1812</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -8353,24 +8301,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -8383,17 +8331,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -8402,7 +8350,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.9</v>
+        <v>53.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8416,26 +8364,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50.3</v>
+        <v>31.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R8" t="n">
         <v>62.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>26.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -8449,7 +8397,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -8492,122 +8440,122 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/29, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.8619</t>
+          <t>100.0639</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4502</t>
+          <t>0.4404</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2002</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3368</t>
+          <t>0.3466</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -8653,24 +8601,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -8683,17 +8631,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8702,7 +8650,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.9</v>
+        <v>52</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8716,62 +8664,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>31.1</v>
+        <v>45.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
         <v>62.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>26.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8796,122 +8740,122 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.0639</t>
+          <t>101.3479</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4404</t>
+          <t>0.4376</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3466</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>24.76</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -8957,12 +8901,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8987,7 +8931,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9006,7 +8950,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52.5</v>
+        <v>51.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9020,11 +8964,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>42.2</v>
+        <v>33.6</v>
       </c>
       <c r="Q10" t="n">
         <v>62.7</v>
@@ -9033,49 +8977,45 @@
         <v>62.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>81.7</v>
+        <v>0.8</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9095,27 +9035,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -9125,67 +9065,67 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.5346</t>
+          <t>99.33</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.3967</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1812</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -9261,24 +9201,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -9296,12 +9236,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9310,7 +9250,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>50.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9324,14 +9264,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>45.1</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R11" t="n">
         <v>62.1</v>
@@ -9343,7 +9283,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>13.3</v>
+        <v>61.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -9395,127 +9335,127 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>85.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.3479</t>
+          <t>97.1381</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4376</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1225</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.286</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -9610,7 +9550,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9624,7 +9564,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -9637,7 +9577,7 @@
         <v>62.1</v>
       </c>
       <c r="S12" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>50</v>
@@ -9647,39 +9587,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9865,24 +9801,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -9895,17 +9831,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9914,7 +9850,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9928,62 +9864,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>62.7</v>
+        <v>39</v>
       </c>
       <c r="R13" t="n">
         <v>62.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>61.4</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10003,7 +9935,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -10013,117 +9945,117 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.52</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.1381</t>
+          <t>98.1545</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1225</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.3022</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.5055</t>
+          <t>0.3942</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -10169,24 +10101,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-10T00:20:00Z</t>
@@ -10199,17 +10131,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10218,7 +10150,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10232,26 +10164,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>17.5</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>39</v>
+        <v>62.7</v>
       </c>
       <c r="R14" t="n">
         <v>62.1</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>20.9</v>
+        <v>17.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -10265,7 +10197,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -10303,12 +10235,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -10318,112 +10250,112 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 3.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>36.88</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.1545</t>
+          <t>99.4273</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.4244</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3022</t>
+          <t>0.3127</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.1533</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3942</t>
+          <t>0.5055</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -10769,12 +10701,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>664774</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>LaMonte Wade Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10799,7 +10731,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10818,7 +10750,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>45.9</v>
+        <v>44.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10832,11 +10764,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>28.6</v>
+        <v>13.9</v>
       </c>
       <c r="Q16" t="n">
         <v>62.7</v>
@@ -10845,49 +10777,45 @@
         <v>62.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>17.7</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10907,12 +10835,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10922,12 +10850,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.0% barrel, 14.6 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10937,67 +10865,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.88</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>86.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.4273</t>
+          <t>97.8228</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4244</t>
+          <t>0.2958</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1013</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3127</t>
+          <t>0.2838</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.6</v>
+        <v>57.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.5</v>
+        <v>55.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>53.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.4</v>
+        <v>53.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.9</v>
+        <v>51.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.5</v>
+        <v>51.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.7</v>
+        <v>49.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.2</v>
+        <v>47.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.7</v>
+        <v>44.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>46.2</v>
+        <v>44.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.3</v>
+        <v>42.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>42.3</v>
+        <v>40.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>40.2</v>
+        <v>38.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.3</v>
+        <v>35.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>62.7</v>
       </c>
       <c r="R2" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59.6</v>
+        <v>57.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>62.7</v>
       </c>
       <c r="R3" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.5</v>
+        <v>55.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S4" t="n">
         <v>86.40000000000001</v>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>53.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.4</v>
+        <v>53.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>62.7</v>
       </c>
       <c r="R6" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S6" t="n">
         <v>76.2</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.9</v>
+        <v>51.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>53.5</v>
+        <v>51.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>62.7</v>
       </c>
       <c r="R8" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8650,7 +8650,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.7</v>
+        <v>49.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>62.7</v>
       </c>
       <c r="R10" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>62.7</v>
       </c>
       <c r="R11" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S11" t="n">
         <v>94.90000000000001</v>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.2</v>
+        <v>47.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>62.7</v>
       </c>
       <c r="R12" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>46.7</v>
+        <v>44.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>39</v>
       </c>
       <c r="R13" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>62.7</v>
       </c>
       <c r="R14" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S14" t="n">
         <v>52.4</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>46.2</v>
+        <v>44.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>39</v>
       </c>
       <c r="R15" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.3</v>
+        <v>42.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>62.7</v>
       </c>
       <c r="R16" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S16" t="n">
         <v>44.8</v>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -11050,7 +11050,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>42.3</v>
+        <v>40.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>38.6</v>
       </c>
       <c r="R17" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>40.2</v>
+        <v>38.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S18" t="n">
         <v>52.4</v>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -11650,7 +11650,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.3</v>
+        <v>35.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>62.1</v>
+        <v>48.6</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -35411,27 +35411,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>681146</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Jonah Bride</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T01:38:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -35441,22 +35441,22 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L116" t="n">
@@ -35474,26 +35474,26 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>17.5</v>
+        <v>25.5</v>
       </c>
       <c r="Q116" t="n">
-        <v>32.4</v>
+        <v>42.1</v>
       </c>
       <c r="R116" t="n">
-        <v>47.1</v>
+        <v>58.7</v>
       </c>
       <c r="S116" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T116" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U116" t="n">
-        <v>16.6</v>
+        <v>19.5</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -35544,17 +35544,17 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -35564,117 +35564,117 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 1 games: 1/4, 0 HR</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>93.25</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>98.1432</t>
+          <t>97.149</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>0.2346</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.1049</t>
+          <t>0.1041</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.2994</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>71.46</t>
+          <t>66.22</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>17.81</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>40.28</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.0869</t>
+          <t>0.0054</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.3436</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr">
         <is>
-          <t>214 deg</t>
+          <t>242 deg</t>
         </is>
       </c>
       <c r="BH116" t="inlineStr">
@@ -35684,27 +35684,27 @@
       </c>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=32.7073&amp;lon=-117.1573</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BK116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL116" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM116" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BN116" t="inlineStr"/>
@@ -35715,27 +35715,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>543760</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-10T23:15:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -35745,17 +35745,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -35764,7 +35764,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -35778,26 +35778,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>26.6</v>
+        <v>17.5</v>
       </c>
       <c r="Q117" t="n">
-        <v>40.9</v>
+        <v>32.4</v>
       </c>
       <c r="R117" t="n">
-        <v>50.4</v>
+        <v>47.1</v>
       </c>
       <c r="S117" t="n">
-        <v>59.8</v>
+        <v>95.5</v>
       </c>
       <c r="T117" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U117" t="n">
-        <v>56.2</v>
+        <v>16.6</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -35858,22 +35858,22 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -35883,102 +35883,102 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>87.11</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>97.7128</t>
+          <t>98.1432</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.3978</t>
+          <t>0.332</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1049</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.2994</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>71.46</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>17.81</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>22.51</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1445</t>
+          <t>0.0869</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>8.46</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.4067</t>
+          <t>0.3436</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.1554</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr">
         <is>
-          <t>344 deg</t>
+          <t>214 deg</t>
         </is>
       </c>
       <c r="BH117" t="inlineStr">
@@ -35988,27 +35988,27 @@
       </c>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=32.7073&amp;lon=-117.1573</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BK117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BL117" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BM117" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BN117" t="inlineStr"/>
@@ -36019,27 +36019,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>703607</t>
+          <t>543760</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:15:00Z</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -36049,17 +36049,17 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -36068,7 +36068,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -36086,22 +36086,22 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>37.2</v>
+        <v>26.6</v>
       </c>
       <c r="Q118" t="n">
-        <v>33.1</v>
+        <v>40.9</v>
       </c>
       <c r="R118" t="n">
-        <v>62.9</v>
+        <v>50.4</v>
       </c>
       <c r="S118" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T118" t="n">
         <v>50</v>
       </c>
       <c r="U118" t="n">
-        <v>37.8</v>
+        <v>56.2</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -36140,7 +36140,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr"/>
@@ -36157,27 +36157,27 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -36187,102 +36187,102 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>87.11</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>104.2571</t>
+          <t>97.7128</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.3978</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>31.93</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1445</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.4067</t>
         </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="BG118" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>344 deg</t>
         </is>
       </c>
       <c r="BH118" t="inlineStr">
@@ -36292,27 +36292,27 @@
       </c>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BK118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BL118" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BM118" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BN118" t="inlineStr"/>
@@ -36323,27 +36323,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>808982</t>
+          <t>703607</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jung Hoo Lee</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -36353,17 +36353,17 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -36372,7 +36372,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -36386,26 +36386,26 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>10.8</v>
+        <v>37.2</v>
       </c>
       <c r="Q119" t="n">
-        <v>29.4</v>
+        <v>33.1</v>
       </c>
       <c r="R119" t="n">
-        <v>45.3</v>
+        <v>62.9</v>
       </c>
       <c r="S119" t="n">
-        <v>95.5</v>
+        <v>40.2</v>
       </c>
       <c r="T119" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U119" t="n">
-        <v>63.1</v>
+        <v>37.8</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -36444,7 +36444,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -36461,27 +36461,27 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
@@ -36491,102 +36491,102 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>96.629</t>
+          <t>104.2571</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.3808</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.0947</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.3147</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>0.4346</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>225 deg</t>
         </is>
       </c>
       <c r="BH119" t="inlineStr">
@@ -36596,27 +36596,27 @@
       </c>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BK119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL119" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM119" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN119" t="inlineStr"/>
@@ -36627,27 +36627,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>643446</t>
+          <t>808982</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jeff McNeil</t>
+          <t>Jung Hoo Lee</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -36657,17 +36657,17 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -36676,7 +36676,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -36690,26 +36690,26 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q120" t="n">
-        <v>33.1</v>
+        <v>29.4</v>
       </c>
       <c r="R120" t="n">
-        <v>62.9</v>
+        <v>45.3</v>
       </c>
       <c r="S120" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T120" t="n">
         <v>80</v>
       </c>
       <c r="U120" t="n">
-        <v>24.9</v>
+        <v>63.1</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -36765,27 +36765,27 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -36795,102 +36795,102 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>29.97</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>96.5924</t>
+          <t>96.629</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.3649</t>
+          <t>0.3808</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.0964</t>
+          <t>0.0947</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.3104</t>
+          <t>0.3147</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>69.09</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.4346</t>
         </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>18.23</t>
         </is>
       </c>
       <c r="BG120" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>286 deg</t>
         </is>
       </c>
       <c r="BH120" t="inlineStr">
@@ -36900,27 +36900,27 @@
       </c>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BK120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BL120" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BM120" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BN120" t="inlineStr"/>
@@ -36931,22 +36931,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>643446</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Jeff McNeil</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -36961,17 +36961,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -36980,7 +36980,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>40.7</v>
+        <v>41.1</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -36994,26 +36994,26 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P121" t="n">
-        <v>23.3</v>
+        <v>11.5</v>
       </c>
       <c r="Q121" t="n">
-        <v>35.7</v>
+        <v>33.1</v>
       </c>
       <c r="R121" t="n">
-        <v>58.2</v>
+        <v>62.9</v>
       </c>
       <c r="S121" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T121" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U121" t="n">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -37069,12 +37069,12 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -37084,12 +37084,12 @@
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -37099,102 +37099,102 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>99.5961</t>
+          <t>96.5924</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.3649</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>0.1152</t>
+          <t>0.0964</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.3104</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>69.09</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>0.1224</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD121" t="inlineStr">
         <is>
-          <t>0.3909</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr">
         <is>
-          <t>280 deg</t>
+          <t>225 deg</t>
         </is>
       </c>
       <c r="BH121" t="inlineStr">
@@ -37204,12 +37204,12 @@
       </c>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BK121" t="inlineStr">
@@ -37219,12 +37219,12 @@
       </c>
       <c r="BL121" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM121" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN121" t="inlineStr"/>
@@ -37235,27 +37235,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>664770</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-10T23:07:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -37265,17 +37265,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>543243</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -37284,7 +37284,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>40.4</v>
+        <v>40.7</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -37298,26 +37298,26 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>9.300000000000001</v>
+        <v>23.3</v>
       </c>
       <c r="Q122" t="n">
-        <v>36.2</v>
+        <v>35.7</v>
       </c>
       <c r="R122" t="n">
-        <v>48.9</v>
+        <v>58.2</v>
       </c>
       <c r="S122" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T122" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U122" t="n">
-        <v>34.2</v>
+        <v>24</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -37378,22 +37378,22 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/31, 1 HR</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 15.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
@@ -37403,102 +37403,102 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>86.99</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>96.7915</t>
+          <t>99.5961</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>0.3479</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1152</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>34.01</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.1224</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD122" t="inlineStr">
         <is>
-          <t>0.3859</t>
+          <t>0.3909</t>
         </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
-          <t>0.1369</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG122" t="inlineStr">
         <is>
-          <t>169 deg</t>
+          <t>280 deg</t>
         </is>
       </c>
       <c r="BH122" t="inlineStr">
@@ -37508,12 +37508,12 @@
       </c>
       <c r="BI122" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=43.6414&amp;lon=-79.3894</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
         </is>
       </c>
       <c r="BJ122" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>19</t>
         </is>
       </c>
       <c r="BK122" t="inlineStr">
@@ -37523,12 +37523,12 @@
       </c>
       <c r="BL122" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>110</t>
         </is>
       </c>
       <c r="BM122" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BN122" t="inlineStr"/>
@@ -37539,24 +37539,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>657136</t>
+          <t>664770</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>BOS</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
       <c r="F123" t="inlineStr">
         <is>
           <t>2026-08-10T23:07:00Z</t>
@@ -37569,17 +37569,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Jameson Taillon</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>592791</t>
+          <t>543243</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -37588,7 +37588,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -37602,26 +37602,26 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P123" t="n">
-        <v>15.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q123" t="n">
-        <v>69.09999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="R123" t="n">
         <v>48.9</v>
       </c>
       <c r="S123" t="n">
-        <v>40.2</v>
+        <v>88.7</v>
       </c>
       <c r="T123" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U123" t="n">
-        <v>18.3</v>
+        <v>34.2</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -37677,12 +37677,12 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -37692,112 +37692,112 @@
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 1 HR</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL123" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.1% barrel, 25.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 15.9 HR allowed</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>86.27</t>
+          <t>86.99</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>99.0481</t>
+          <t>96.7915</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3479</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>0.1027</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr">
         <is>
-          <t>0.2877</t>
+          <t>0.294</t>
         </is>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>34.01</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>20.81</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>0.1005</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="BD123" t="inlineStr">
         <is>
-          <t>0.5073</t>
+          <t>0.3859</t>
         </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
-          <t>0.2502</t>
+          <t>0.1369</t>
         </is>
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="BG123" t="inlineStr">
@@ -37843,27 +37843,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>657136</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-10T23:07:00Z</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -37873,17 +37873,17 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Hunter Dobbins</t>
+          <t>Jameson Taillon</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>690928</t>
+          <t>592791</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -37906,26 +37906,26 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>7.4</v>
+        <v>15.9</v>
       </c>
       <c r="Q124" t="n">
-        <v>33.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="R124" t="n">
-        <v>55.1</v>
+        <v>48.9</v>
       </c>
       <c r="S124" t="n">
-        <v>90.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T124" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U124" t="n">
-        <v>33.1</v>
+        <v>18.3</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -37981,12 +37981,12 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -37996,117 +37996,117 @@
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/32, 1 HR</t>
+          <t>Last 7 games: 2/20, 1 HR</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.1% barrel, 25.4 HR allowed</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>86.73</t>
+          <t>86.27</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>93.9815</t>
+          <t>99.0481</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>0.3693</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>0.0851</t>
+          <t>0.1027</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2877</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>62.99</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>39.89</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>0.1147</t>
+          <t>0.1005</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>0.3821</t>
+          <t>0.5073</t>
         </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.2502</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr">
         <is>
-          <t>188 deg</t>
+          <t>169 deg</t>
         </is>
       </c>
       <c r="BH124" t="inlineStr">
@@ -38116,12 +38116,12 @@
       </c>
       <c r="BI124" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=43.6414&amp;lon=-79.3894</t>
         </is>
       </c>
       <c r="BJ124" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BK124" t="inlineStr">
@@ -38131,12 +38131,12 @@
       </c>
       <c r="BL124" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BM124" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BN124" t="inlineStr"/>
@@ -38147,27 +38147,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>650333</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -38177,17 +38177,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Hunter Dobbins</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>690928</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -38196,7 +38196,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>39.4</v>
+        <v>40.2</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -38210,26 +38210,26 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>42.2</v>
+        <v>7.4</v>
       </c>
       <c r="Q125" t="n">
-        <v>18.6</v>
+        <v>33.1</v>
       </c>
       <c r="R125" t="n">
-        <v>45.3</v>
+        <v>55.1</v>
       </c>
       <c r="S125" t="n">
-        <v>40.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T125" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U125" t="n">
-        <v>81.7</v>
+        <v>33.1</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -38285,27 +38285,27 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/32, 1 HR</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
@@ -38315,102 +38315,102 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>86.73</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>101.5346</t>
+          <t>93.9815</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.3693</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.0851</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>62.99</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>68.11</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1147</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>87.08</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>0.3709</t>
+          <t>0.3821</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>0.1229</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>188 deg</t>
         </is>
       </c>
       <c r="BH125" t="inlineStr">
@@ -38420,27 +38420,27 @@
       </c>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BK125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL125" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM125" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BN125" t="inlineStr"/>
@@ -38451,27 +38451,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>665966</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Carlos Narvaez</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -38486,12 +38486,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -38500,7 +38500,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -38514,17 +38514,17 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>33.3</v>
+        <v>42.2</v>
       </c>
       <c r="Q126" t="n">
-        <v>43.4</v>
+        <v>18.6</v>
       </c>
       <c r="R126" t="n">
-        <v>51.6</v>
+        <v>45.3</v>
       </c>
       <c r="S126" t="n">
         <v>40.2</v>
@@ -38533,7 +38533,7 @@
         <v>50</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>81.7</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -38589,132 +38589,132 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>91.24</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>100.2964</t>
+          <t>101.5346</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>0.3446</t>
+          <t>0.418</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>0.1382</t>
+          <t>0.1753</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>0.3215</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>19.81</t>
+          <t>68.11</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>31.81</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>0.1094</t>
+          <t>0.1542</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>87.61</t>
+          <t>87.08</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>0.4431</t>
+          <t>0.3709</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>0.1974</t>
+          <t>0.1229</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr">
         <is>
-          <t>24 deg</t>
+          <t>286 deg</t>
         </is>
       </c>
       <c r="BH126" t="inlineStr">
@@ -38724,27 +38724,27 @@
       </c>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="BK126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL126" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="BK126" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BL126" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="BM126" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BN126" t="inlineStr"/>
@@ -38755,27 +38755,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>678662</t>
+          <t>665966</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Carlos Narvaez</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -38790,12 +38790,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>28.3</v>
+        <v>33.3</v>
       </c>
       <c r="Q127" t="n">
-        <v>35.7</v>
+        <v>43.4</v>
       </c>
       <c r="R127" t="n">
-        <v>58.2</v>
+        <v>51.6</v>
       </c>
       <c r="S127" t="n">
         <v>40.2</v>
@@ -38837,7 +38837,7 @@
         <v>50</v>
       </c>
       <c r="U127" t="n">
-        <v>50.3</v>
+        <v>0</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -38893,67 +38893,67 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.24</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>98.9141</t>
+          <t>100.2964</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.3808</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.1382</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.2854</t>
+          <t>0.279</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
@@ -38963,62 +38963,62 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>31.81</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>29.43</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1316</t>
+          <t>0.1094</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>34.89</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>87.61</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.3909</t>
+          <t>0.4431</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1974</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>34.98</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr">
         <is>
-          <t>280 deg</t>
+          <t>24 deg</t>
         </is>
       </c>
       <c r="BH127" t="inlineStr">
@@ -39028,27 +39028,27 @@
       </c>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BK127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BL127" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM127" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BN127" t="inlineStr"/>
@@ -39059,27 +39059,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>678662</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -39089,17 +39089,17 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -39122,26 +39122,26 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>31</v>
+        <v>28.3</v>
       </c>
       <c r="Q128" t="n">
-        <v>18.6</v>
+        <v>35.7</v>
       </c>
       <c r="R128" t="n">
-        <v>45.3</v>
+        <v>58.2</v>
       </c>
       <c r="S128" t="n">
-        <v>88.7</v>
+        <v>40.2</v>
       </c>
       <c r="T128" t="n">
         <v>50</v>
       </c>
       <c r="U128" t="n">
-        <v>18.3</v>
+        <v>50.3</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -39197,12 +39197,12 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
@@ -39212,12 +39212,12 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 1 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -39227,102 +39227,102 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>100.0961</t>
+          <t>98.9141</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.4369</t>
+          <t>0.3808</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.1508</t>
+          <t>0.1506</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.3445</t>
+          <t>0.2854</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>72.02</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>46.06</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>29.43</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.1849</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>87.08</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD128" t="inlineStr">
         <is>
-          <t>0.3709</t>
+          <t>0.3909</t>
         </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
-          <t>0.1229</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG128" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>280 deg</t>
         </is>
       </c>
       <c r="BH128" t="inlineStr">
@@ -39332,27 +39332,27 @@
       </c>
       <c r="BI128" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
         </is>
       </c>
       <c r="BJ128" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>19</t>
         </is>
       </c>
       <c r="BK128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL128" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>110</t>
         </is>
       </c>
       <c r="BM128" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BN128" t="inlineStr"/>
@@ -39363,27 +39363,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>668885</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Jeremy Pena</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -39398,21 +39398,21 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -39426,26 +39426,26 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>10.5</v>
+        <v>31</v>
       </c>
       <c r="Q129" t="n">
-        <v>35.6</v>
+        <v>18.6</v>
       </c>
       <c r="R129" t="n">
-        <v>51.6</v>
+        <v>45.3</v>
       </c>
       <c r="S129" t="n">
         <v>88.7</v>
       </c>
       <c r="T129" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U129" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -39501,27 +39501,27 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 0 HR</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 1.9 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
@@ -39531,102 +39531,102 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>86.69</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>97.1877</t>
+          <t>100.0961</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.3421</t>
+          <t>0.4369</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.0918</t>
+          <t>0.1508</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.3198</t>
+          <t>0.3445</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>68.83</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>46.06</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.0788</t>
+          <t>0.1849</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>87.08</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3709</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.1229</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr">
         <is>
-          <t>24 deg</t>
+          <t>286 deg</t>
         </is>
       </c>
       <c r="BH129" t="inlineStr">
@@ -39636,27 +39636,27 @@
       </c>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="BK129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL129" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="BK129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BL129" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="BM129" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BN129" t="inlineStr"/>
@@ -39667,27 +39667,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>668885</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Austin Martin</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -39697,26 +39697,26 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -39730,26 +39730,26 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q130" t="n">
-        <v>43.2</v>
+        <v>35.6</v>
       </c>
       <c r="R130" t="n">
-        <v>55.1</v>
+        <v>51.6</v>
       </c>
       <c r="S130" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T130" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U130" t="n">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -39788,7 +39788,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr"/>
@@ -39805,12 +39805,12 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
@@ -39820,12 +39820,12 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -39835,102 +39835,102 @@
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>86.69</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>98.6827</t>
+          <t>97.1877</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.3386</t>
+          <t>0.3421</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.0888</t>
+          <t>0.0918</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.3198</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>68.83</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>21.04</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.0897</t>
+          <t>0.0788</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>41.68</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr">
         <is>
-          <t>188 deg</t>
+          <t>24 deg</t>
         </is>
       </c>
       <c r="BH130" t="inlineStr">
@@ -39940,27 +39940,27 @@
       </c>
       <c r="BI130" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BJ130" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BK130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BL130" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM130" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BN130" t="inlineStr"/>
@@ -39971,27 +39971,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -40006,21 +40006,21 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>38.7</v>
+        <v>39</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -40034,26 +40034,26 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>13.3</v>
+        <v>15.5</v>
       </c>
       <c r="Q131" t="n">
-        <v>21.5</v>
+        <v>43.2</v>
       </c>
       <c r="R131" t="n">
-        <v>62.9</v>
+        <v>55.1</v>
       </c>
       <c r="S131" t="n">
         <v>71.7</v>
       </c>
       <c r="T131" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U131" t="n">
-        <v>52.8</v>
+        <v>14.6</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr"/>
@@ -40114,127 +40114,127 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 13.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>85.32</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>97.3793</t>
+          <t>98.6827</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.3521</t>
+          <t>0.3386</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.0888</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.2761</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.04</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.1629</t>
+          <t>0.0897</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>85.92</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.3368</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.1261</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>188 deg</t>
         </is>
       </c>
       <c r="BH131" t="inlineStr">
@@ -40244,12 +40244,12 @@
       </c>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BK131" t="inlineStr">
@@ -40259,12 +40259,12 @@
       </c>
       <c r="BL131" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM131" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BN131" t="inlineStr"/>
@@ -40275,27 +40275,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-11T02:10:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -40305,17 +40305,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -40324,7 +40324,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -40342,22 +40342,22 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>23.8</v>
+        <v>13.3</v>
       </c>
       <c r="Q132" t="n">
-        <v>26.8</v>
+        <v>21.5</v>
       </c>
       <c r="R132" t="n">
-        <v>56.6</v>
+        <v>62.9</v>
       </c>
       <c r="S132" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T132" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U132" t="n">
-        <v>12</v>
+        <v>52.8</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -40418,157 +40418,157 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Hot streak: 2 HR in last 7 games</t>
+        </is>
+      </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 13.6 HR allowed</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+        </is>
+      </c>
+      <c r="AN132" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>30.96</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>85.32</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>97.3793</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>0.3521</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr">
+        <is>
+          <t>0.2761</t>
+        </is>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>72.89</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>30.55</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>46.44</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>22.34</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>0.1629</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>31.66</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>85.92</t>
+        </is>
+      </c>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>0.3368</t>
+        </is>
+      </c>
+      <c r="BE132" t="inlineStr">
+        <is>
+          <t>0.1261</t>
+        </is>
+      </c>
+      <c r="BF132" t="inlineStr">
+        <is>
+          <t>32.41</t>
+        </is>
+      </c>
+      <c r="BG132" t="inlineStr">
+        <is>
+          <t>225 deg</t>
+        </is>
+      </c>
+      <c r="BH132" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BI132" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+        </is>
+      </c>
+      <c r="BJ132" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BK132" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
-        </is>
-      </c>
-      <c r="AL132" t="inlineStr">
-        <is>
-          <t>switch hitter; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>5.32</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>40.16</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>88.59</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>100.0202</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>0.3401</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>0.1018</t>
-        </is>
-      </c>
-      <c r="AT132" t="inlineStr">
-        <is>
-          <t>0.3108</t>
-        </is>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>73.33</t>
-        </is>
-      </c>
-      <c r="AV132" t="inlineStr">
-        <is>
-          <t>30.34</t>
-        </is>
-      </c>
-      <c r="AW132" t="inlineStr">
-        <is>
-          <t>40.54</t>
-        </is>
-      </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>26.16</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t>6.9</t>
-        </is>
-      </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>0.134</t>
-        </is>
-      </c>
-      <c r="BA132" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="BB132" t="inlineStr">
-        <is>
-          <t>34.26</t>
-        </is>
-      </c>
-      <c r="BC132" t="inlineStr">
-        <is>
-          <t>86.66</t>
-        </is>
-      </c>
-      <c r="BD132" t="inlineStr">
-        <is>
-          <t>0.3468</t>
-        </is>
-      </c>
-      <c r="BE132" t="inlineStr">
-        <is>
-          <t>0.1268</t>
-        </is>
-      </c>
-      <c r="BF132" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
-      </c>
-      <c r="BG132" t="inlineStr">
-        <is>
-          <t>249 deg</t>
-        </is>
-      </c>
-      <c r="BH132" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BI132" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BJ132" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="BK132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BL132" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM132" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN132" t="inlineStr"/>
@@ -40579,27 +40579,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-10T23:15:00Z</t>
+          <t>2026-08-11T02:10:00Z</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -40609,26 +40609,26 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Christian Scott</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>681035</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -40646,22 +40646,22 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>16.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q133" t="n">
-        <v>23.9</v>
+        <v>26.8</v>
       </c>
       <c r="R133" t="n">
-        <v>50.4</v>
+        <v>56.6</v>
       </c>
       <c r="S133" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T133" t="n">
         <v>75</v>
       </c>
       <c r="U133" t="n">
-        <v>27.6</v>
+        <v>12</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -40700,7 +40700,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr"/>
@@ -40717,27 +40717,27 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
@@ -40747,102 +40747,102 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>40.16</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>87.01</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>96.7422</t>
+          <t>100.0202</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.3401</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>0.1251</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>0.2878</t>
+          <t>0.3108</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>46.42</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>26.16</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>0.1586</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.66</t>
         </is>
       </c>
       <c r="BD133" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3468</t>
         </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BG133" t="inlineStr">
         <is>
-          <t>344 deg</t>
+          <t>249 deg</t>
         </is>
       </c>
       <c r="BH133" t="inlineStr">
@@ -40852,27 +40852,27 @@
       </c>
       <c r="BI133" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BJ133" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>36</t>
         </is>
       </c>
       <c r="BK133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL133" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM133" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BN133" t="inlineStr"/>
@@ -40883,27 +40883,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-10T23:15:00Z</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -40913,22 +40913,22 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Christian Scott</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>681035</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -40950,22 +40950,22 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>11</v>
+        <v>16.7</v>
       </c>
       <c r="Q134" t="n">
-        <v>35.6</v>
+        <v>23.9</v>
       </c>
       <c r="R134" t="n">
-        <v>51.6</v>
+        <v>50.4</v>
       </c>
       <c r="S134" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T134" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U134" t="n">
-        <v>63.1</v>
+        <v>27.6</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
@@ -41004,7 +41004,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr"/>
@@ -41021,27 +41021,27 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM134" t="inlineStr">
@@ -41051,102 +41051,102 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>28.74</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>85.08</t>
+          <t>87.01</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>96.5933</t>
+          <t>96.7422</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>0.3549</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.1251</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>0.3107</t>
+          <t>0.2878</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>46.42</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>31.97</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>0.1108</t>
+          <t>0.1586</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD134" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr">
         <is>
-          <t>24 deg</t>
+          <t>344 deg</t>
         </is>
       </c>
       <c r="BH134" t="inlineStr">
@@ -41156,27 +41156,27 @@
       </c>
       <c r="BI134" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
         </is>
       </c>
       <c r="BJ134" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BK134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BL134" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BM134" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BN134" t="inlineStr"/>
@@ -41187,27 +41187,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>622268</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -41222,21 +41222,21 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -41254,22 +41254,22 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>14.3</v>
+        <v>11</v>
       </c>
       <c r="Q135" t="n">
-        <v>33.1</v>
+        <v>35.6</v>
       </c>
       <c r="R135" t="n">
-        <v>62.9</v>
+        <v>51.6</v>
       </c>
       <c r="S135" t="n">
         <v>59.8</v>
       </c>
       <c r="T135" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U135" t="n">
-        <v>12</v>
+        <v>63.1</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -41325,27 +41325,27 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/10, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
@@ -41355,102 +41355,102 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>85.08</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>97.8166</t>
+          <t>96.5933</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>0.3576</t>
+          <t>0.3549</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>0.0977</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>0.2992</t>
+          <t>0.3107</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>26.97</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1108</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>41.68</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD135" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>24 deg</t>
         </is>
       </c>
       <c r="BH135" t="inlineStr">
@@ -41460,27 +41460,27 @@
       </c>
       <c r="BI135" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BJ135" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BK135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BL135" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM135" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BN135" t="inlineStr"/>
@@ -41491,27 +41491,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>593871</t>
+          <t>622268</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-10T23:15:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -41521,17 +41521,17 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -41540,7 +41540,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -41558,22 +41558,22 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>21.1</v>
+        <v>14.3</v>
       </c>
       <c r="Q136" t="n">
-        <v>38.9</v>
+        <v>33.1</v>
       </c>
       <c r="R136" t="n">
-        <v>50.4</v>
+        <v>62.9</v>
       </c>
       <c r="S136" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T136" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U136" t="n">
-        <v>18.3</v>
+        <v>12</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
@@ -41634,22 +41634,22 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 2/10, 0 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
@@ -41659,102 +41659,102 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>98.3169</t>
+          <t>97.8166</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.3366</t>
+          <t>0.3576</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.1301</t>
+          <t>0.0977</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.2639</t>
+          <t>0.2992</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.4067</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.1554</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr">
         <is>
-          <t>344 deg</t>
+          <t>225 deg</t>
         </is>
       </c>
       <c r="BH136" t="inlineStr">
@@ -41764,27 +41764,27 @@
       </c>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BK136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL136" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM136" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN136" t="inlineStr"/>
@@ -41795,27 +41795,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>593871</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:15:00Z</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -41825,17 +41825,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -41844,7 +41844,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -41858,26 +41858,26 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>21.7</v>
+        <v>21.1</v>
       </c>
       <c r="Q137" t="n">
-        <v>32.4</v>
+        <v>38.9</v>
       </c>
       <c r="R137" t="n">
-        <v>47.1</v>
+        <v>50.4</v>
       </c>
       <c r="S137" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T137" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U137" t="n">
-        <v>32</v>
+        <v>18.3</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -41933,7 +41933,7 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
@@ -41943,17 +41943,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.6% barrel, 20.5 HR allowed</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
@@ -41963,102 +41963,102 @@
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>99.068</t>
+          <t>98.3169</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>0.3025</t>
+          <t>0.3366</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>0.1057</t>
+          <t>0.1301</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>0.2976</t>
+          <t>0.2639</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>0.1274</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>8.46</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>41.49</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>0.3436</t>
+          <t>0.4067</t>
         </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr">
         <is>
-          <t>214 deg</t>
+          <t>344 deg</t>
         </is>
       </c>
       <c r="BH137" t="inlineStr">
@@ -42068,27 +42068,27 @@
       </c>
       <c r="BI137" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=32.7073&amp;lon=-117.1573</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
         </is>
       </c>
       <c r="BJ137" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BK137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BL137" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BM137" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BN137" t="inlineStr"/>
@@ -42099,27 +42099,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>664761</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -42129,17 +42129,17 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Hunter Dobbins</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>690928</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -42148,7 +42148,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -42166,22 +42166,22 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>29.2</v>
+        <v>21.7</v>
       </c>
       <c r="Q138" t="n">
-        <v>33.1</v>
+        <v>32.4</v>
       </c>
       <c r="R138" t="n">
-        <v>55.1</v>
+        <v>47.1</v>
       </c>
       <c r="S138" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T138" t="n">
         <v>50</v>
       </c>
       <c r="U138" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y138" t="inlineStr">
@@ -42237,7 +42237,7 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
@@ -42252,12 +42252,12 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 5.8 HR allowed</t>
         </is>
       </c>
       <c r="AM138" t="inlineStr">
@@ -42267,102 +42267,102 @@
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>40.29</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>90.59</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>100.1407</t>
+          <t>99.068</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>0.3899</t>
+          <t>0.3025</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1057</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr">
         <is>
-          <t>0.3114</t>
+          <t>0.2976</t>
         </is>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>71.07</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1274</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.46</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="BD138" t="inlineStr">
         <is>
-          <t>0.3821</t>
+          <t>0.3436</t>
         </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF138" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BG138" t="inlineStr">
         <is>
-          <t>188 deg</t>
+          <t>214 deg</t>
         </is>
       </c>
       <c r="BH138" t="inlineStr">
@@ -42372,27 +42372,27 @@
       </c>
       <c r="BI138" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=32.7073&amp;lon=-117.1573</t>
         </is>
       </c>
       <c r="BJ138" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BK138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BL138" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BM138" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BN138" t="inlineStr"/>
@@ -42403,27 +42403,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>679845</t>
+          <t>664761</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Nick Loftin</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-11T02:10:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -42433,26 +42433,26 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Hunter Dobbins</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>690928</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>37.7</v>
+        <v>38</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
@@ -42466,26 +42466,26 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P139" t="n">
-        <v>16.3</v>
+        <v>29.2</v>
       </c>
       <c r="Q139" t="n">
-        <v>28.2</v>
+        <v>33.1</v>
       </c>
       <c r="R139" t="n">
-        <v>56.6</v>
+        <v>55.1</v>
       </c>
       <c r="S139" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T139" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U139" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="V139" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -42541,12 +42541,12 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
@@ -42556,12 +42556,12 @@
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL139" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
@@ -42571,102 +42571,102 @@
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>87.15</t>
+          <t>90.59</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>96.8364</t>
+          <t>100.1407</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>0.3506</t>
+          <t>0.3899</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>0.1158</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>0.2982</t>
+          <t>0.3114</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>71.07</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD139" t="inlineStr">
         <is>
-          <t>0.3468</t>
+          <t>0.3821</t>
         </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BG139" t="inlineStr">
         <is>
-          <t>249 deg</t>
+          <t>188 deg</t>
         </is>
       </c>
       <c r="BH139" t="inlineStr">
@@ -42676,12 +42676,12 @@
       </c>
       <c r="BI139" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
         </is>
       </c>
       <c r="BJ139" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BK139" t="inlineStr">
@@ -42691,12 +42691,12 @@
       </c>
       <c r="BL139" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM139" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BN139" t="inlineStr"/>
@@ -42707,27 +42707,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>687597</t>
+          <t>679845</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Jordan Beck</t>
+          <t>Nick Loftin</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T02:10:00Z</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -42737,26 +42737,26 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>37.2</v>
+        <v>37.7</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -42770,26 +42770,26 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>21.4</v>
+        <v>16.3</v>
       </c>
       <c r="Q140" t="n">
-        <v>35.7</v>
+        <v>28.2</v>
       </c>
       <c r="R140" t="n">
-        <v>58.2</v>
+        <v>56.6</v>
       </c>
       <c r="S140" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T140" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U140" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
@@ -42845,12 +42845,12 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
@@ -42860,12 +42860,12 @@
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM140" t="inlineStr">
@@ -42875,102 +42875,102 @@
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>31.57</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>87.15</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
-          <t>98.2982</t>
+          <t>96.8364</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>0.3506</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>0.1171</t>
+          <t>0.1158</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr">
         <is>
-          <t>0.2667</t>
+          <t>0.2982</t>
         </is>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>34.87</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>0.1433</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>86.66</t>
         </is>
       </c>
       <c r="BD140" t="inlineStr">
         <is>
-          <t>0.3909</t>
+          <t>0.3468</t>
         </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BG140" t="inlineStr">
         <is>
-          <t>280 deg</t>
+          <t>249 deg</t>
         </is>
       </c>
       <c r="BH140" t="inlineStr">
@@ -42980,12 +42980,12 @@
       </c>
       <c r="BI140" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BJ140" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>36</t>
         </is>
       </c>
       <c r="BK140" t="inlineStr">
@@ -42995,12 +42995,12 @@
       </c>
       <c r="BL140" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM140" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BN140" t="inlineStr"/>
@@ -43011,27 +43011,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>687597</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Jordan Beck</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-10T23:40:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -43046,21 +43046,21 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -43074,26 +43074,26 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P141" t="n">
-        <v>18.6</v>
+        <v>21.4</v>
       </c>
       <c r="Q141" t="n">
-        <v>34.6</v>
+        <v>35.7</v>
       </c>
       <c r="R141" t="n">
-        <v>51.6</v>
+        <v>58.2</v>
       </c>
       <c r="S141" t="n">
         <v>47.9</v>
       </c>
       <c r="T141" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U141" t="n">
-        <v>28.1</v>
+        <v>32</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
@@ -43149,27 +43149,27 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL141" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
@@ -43179,102 +43179,102 @@
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>31.57</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>97.4679</t>
+          <t>98.2982</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>0.3404</t>
+          <t>0.339</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.1171</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.2667</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>34.87</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>27.97</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.1433</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD141" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3909</t>
         </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG141" t="inlineStr">
         <is>
-          <t>24 deg</t>
+          <t>280 deg</t>
         </is>
       </c>
       <c r="BH141" t="inlineStr">
@@ -43284,27 +43284,27 @@
       </c>
       <c r="BI141" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.4455&amp;lon=-112.0667</t>
         </is>
       </c>
       <c r="BJ141" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>19</t>
         </is>
       </c>
       <c r="BK141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL141" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>110</t>
         </is>
       </c>
       <c r="BM141" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BN141" t="inlineStr"/>
@@ -43315,27 +43315,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>805779</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Jacob Wilson</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-10T23:40:00Z</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -43345,22 +43345,22 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L142" t="n">
@@ -43378,26 +43378,26 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>3</v>
+        <v>18.6</v>
       </c>
       <c r="Q142" t="n">
-        <v>33.1</v>
+        <v>34.6</v>
       </c>
       <c r="R142" t="n">
-        <v>62.9</v>
+        <v>51.6</v>
       </c>
       <c r="S142" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T142" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U142" t="n">
-        <v>14.1</v>
+        <v>28.1</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -43453,27 +43453,27 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -43483,102 +43483,102 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>84.25</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>95.5238</t>
+          <t>97.4679</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.3549</t>
+          <t>0.3404</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>0.0849</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0.2914</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>64.36</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>41.68</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="BG142" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>24 deg</t>
         </is>
       </c>
       <c r="BH142" t="inlineStr">
@@ -43588,27 +43588,27 @@
       </c>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BK142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BL142" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM142" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BN142" t="inlineStr"/>
@@ -43619,27 +43619,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>805779</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Jacob Wilson</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-11T01:38:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -43649,26 +43649,26 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -43682,26 +43682,26 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>12.1</v>
+        <v>3</v>
       </c>
       <c r="Q143" t="n">
-        <v>47</v>
+        <v>33.1</v>
       </c>
       <c r="R143" t="n">
-        <v>58.7</v>
+        <v>62.9</v>
       </c>
       <c r="S143" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T143" t="n">
         <v>50</v>
       </c>
       <c r="U143" t="n">
-        <v>54.3</v>
+        <v>14.1</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -43740,7 +43740,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr"/>
@@ -43757,27 +43757,27 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 17.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -43787,102 +43787,102 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.25</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>96.3933</t>
+          <t>95.5238</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.3549</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.0849</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>0.2914</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>64.36</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>42.91</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>0.3898</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
-          <t>0.1537</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG143" t="inlineStr">
         <is>
-          <t>242 deg</t>
+          <t>225 deg</t>
         </is>
       </c>
       <c r="BH143" t="inlineStr">
@@ -43892,12 +43892,12 @@
       </c>
       <c r="BI143" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BJ143" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BK143" t="inlineStr">
@@ -43907,12 +43907,12 @@
       </c>
       <c r="BL143" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM143" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN143" t="inlineStr"/>
@@ -43923,27 +43923,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>663494</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-10T23:45:00Z</t>
+          <t>2026-08-11T01:38:00Z</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -43958,21 +43958,21 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -43986,26 +43986,26 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>14.9</v>
+        <v>12.1</v>
       </c>
       <c r="Q144" t="n">
-        <v>43.2</v>
+        <v>47</v>
       </c>
       <c r="R144" t="n">
-        <v>55.1</v>
+        <v>58.7</v>
       </c>
       <c r="S144" t="n">
         <v>40.2</v>
       </c>
       <c r="T144" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U144" t="n">
-        <v>5.7</v>
+        <v>54.3</v>
       </c>
       <c r="V144" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr"/>
@@ -44061,162 +44061,162 @@
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Contact streak: 9/25 over last 7 games</t>
+        </is>
+      </c>
+      <c r="AL144" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 17.2 HR allowed</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AN144" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>96.3933</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>0.109</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr">
+        <is>
+          <t>0.314</t>
+        </is>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>0.111</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>9.48</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>42.91</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>89.56</t>
+        </is>
+      </c>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>0.3898</t>
+        </is>
+      </c>
+      <c r="BE144" t="inlineStr">
+        <is>
+          <t>0.1537</t>
+        </is>
+      </c>
+      <c r="BF144" t="inlineStr">
+        <is>
+          <t>27.65</t>
+        </is>
+      </c>
+      <c r="BG144" t="inlineStr">
+        <is>
+          <t>242 deg</t>
+        </is>
+      </c>
+      <c r="BH144" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BI144" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+        </is>
+      </c>
+      <c r="BJ144" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="BK144" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
-        </is>
-      </c>
-      <c r="AL144" t="inlineStr">
-        <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>28.7</t>
-        </is>
-      </c>
-      <c r="AP144" t="inlineStr">
-        <is>
-          <t>86.7</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>96.2048</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>0.135</t>
-        </is>
-      </c>
-      <c r="AT144" t="inlineStr">
-        <is>
-          <t>0.293</t>
-        </is>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="AV144" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="AW144" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>0.167</t>
-        </is>
-      </c>
-      <c r="BA144" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="BB144" t="inlineStr">
-        <is>
-          <t>35.2</t>
-        </is>
-      </c>
-      <c r="BC144" t="inlineStr">
-        <is>
-          <t>87.1</t>
-        </is>
-      </c>
-      <c r="BD144" t="inlineStr">
-        <is>
-          <t>0.456</t>
-        </is>
-      </c>
-      <c r="BE144" t="inlineStr">
-        <is>
-          <t>0.186</t>
-        </is>
-      </c>
-      <c r="BF144" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
-      <c r="BG144" t="inlineStr">
-        <is>
-          <t>188 deg</t>
-        </is>
-      </c>
-      <c r="BH144" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BI144" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
-        </is>
-      </c>
-      <c r="BJ144" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="BK144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BL144" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM144" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BN144" t="inlineStr"/>
@@ -44227,27 +44227,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>687551</t>
+          <t>663494</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Drew Gilbert</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-11T01:45:00Z</t>
+          <t>2026-08-10T23:45:00Z</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -44257,17 +44257,17 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -44276,7 +44276,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -44294,22 +44294,22 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
       <c r="Q145" t="n">
-        <v>29.4</v>
+        <v>43.2</v>
       </c>
       <c r="R145" t="n">
-        <v>45.3</v>
+        <v>55.1</v>
       </c>
       <c r="S145" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T145" t="n">
         <v>80</v>
       </c>
       <c r="U145" t="n">
-        <v>15.3</v>
+        <v>5.7</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -44348,7 +44348,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr"/>
@@ -44365,12 +44365,12 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
@@ -44380,12 +44380,12 @@
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -44395,102 +44395,102 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>86.25</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>97.6637</t>
+          <t>96.2048</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.1069</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.1285</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.4346</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>188 deg</t>
         </is>
       </c>
       <c r="BH145" t="inlineStr">
@@ -44500,27 +44500,27 @@
       </c>
       <c r="BI145" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
         </is>
       </c>
       <c r="BJ145" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BK145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BL145" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM145" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BN145" t="inlineStr"/>
@@ -44531,27 +44531,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>687551</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Drew Gilbert</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-11T01:38:00Z</t>
+          <t>2026-08-11T01:45:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -44561,26 +44561,26 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -44594,26 +44594,26 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>21.6</v>
+        <v>13.5</v>
       </c>
       <c r="Q146" t="n">
-        <v>42.1</v>
+        <v>29.4</v>
       </c>
       <c r="R146" t="n">
-        <v>58.7</v>
+        <v>45.3</v>
       </c>
       <c r="S146" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T146" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U146" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -44669,162 +44669,162 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Last 7 games: 4/18, 0 HR</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 2.1 HR allowed</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AN146" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>34.05</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>86.25</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>97.6637</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>0.1069</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr">
+        <is>
+          <t>0.298</t>
+        </is>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>70.52</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>10.13</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>19.48</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>0.1285</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>5.18</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>40.63</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>88.79</t>
+        </is>
+      </c>
+      <c r="BD146" t="inlineStr">
+        <is>
+          <t>0.4346</t>
+        </is>
+      </c>
+      <c r="BE146" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF146" t="inlineStr">
+        <is>
+          <t>18.23</t>
+        </is>
+      </c>
+      <c r="BG146" t="inlineStr">
+        <is>
+          <t>286 deg</t>
+        </is>
+      </c>
+      <c r="BH146" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BI146" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=37.7786&amp;lon=-122.3893</t>
+        </is>
+      </c>
+      <c r="BJ146" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="BK146" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Last 7 games: 1/20, 0 HR</t>
-        </is>
-      </c>
-      <c r="AL146" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AN146" t="inlineStr">
-        <is>
-          <t>5.83</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>35.93</t>
-        </is>
-      </c>
-      <c r="AP146" t="inlineStr">
-        <is>
-          <t>87.26</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>98.744</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>0.3376</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>0.1239</t>
-        </is>
-      </c>
-      <c r="AT146" t="inlineStr">
-        <is>
-          <t>0.2975</t>
-        </is>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>71.02</t>
-        </is>
-      </c>
-      <c r="AV146" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="AW146" t="inlineStr">
-        <is>
-          <t>39.12</t>
-        </is>
-      </c>
-      <c r="AX146" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="AZ146" t="inlineStr">
-        <is>
-          <t>0.1366</t>
-        </is>
-      </c>
-      <c r="BA146" t="inlineStr">
-        <is>
-          <t>8.55</t>
-        </is>
-      </c>
-      <c r="BB146" t="inlineStr">
-        <is>
-          <t>39.93</t>
-        </is>
-      </c>
-      <c r="BC146" t="inlineStr">
-        <is>
-          <t>90.1</t>
-        </is>
-      </c>
-      <c r="BD146" t="inlineStr">
-        <is>
-          <t>0.3721</t>
-        </is>
-      </c>
-      <c r="BE146" t="inlineStr">
-        <is>
-          <t>0.1481</t>
-        </is>
-      </c>
-      <c r="BF146" t="inlineStr">
-        <is>
-          <t>28.69</t>
-        </is>
-      </c>
-      <c r="BG146" t="inlineStr">
-        <is>
-          <t>242 deg</t>
-        </is>
-      </c>
-      <c r="BH146" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BI146" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
-        </is>
-      </c>
-      <c r="BJ146" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="BK146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BL146" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BM146" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BN146" t="inlineStr"/>
@@ -44835,27 +44835,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-11T01:40:00Z</t>
+          <t>2026-08-11T01:38:00Z</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -44865,26 +44865,26 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -44902,22 +44902,22 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>11.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q147" t="n">
-        <v>33.1</v>
+        <v>42.1</v>
       </c>
       <c r="R147" t="n">
-        <v>62.9</v>
+        <v>58.7</v>
       </c>
       <c r="S147" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T147" t="n">
         <v>50</v>
       </c>
       <c r="U147" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -44956,7 +44956,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr"/>
@@ -44973,12 +44973,12 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -44988,12 +44988,12 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Last 7 games: 1/20, 0 HR</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -45003,102 +45003,102 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>87.26</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>97.3267</t>
+          <t>98.744</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>0.1239</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.2975</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>17.79</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.1366</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="BE147" t="inlineStr">
         <is>
-          <t>0.1396</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr">
         <is>
-          <t>225 deg</t>
+          <t>242 deg</t>
         </is>
       </c>
       <c r="BH147" t="inlineStr">
@@ -45108,12 +45108,12 @@
       </c>
       <c r="BI147" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BJ147" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>51</t>
         </is>
       </c>
       <c r="BK147" t="inlineStr">
@@ -45123,12 +45123,12 @@
       </c>
       <c r="BL147" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM147" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BN147" t="inlineStr"/>
@@ -45139,27 +45139,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>681146</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Jonah Bride</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-11T01:38:00Z</t>
+          <t>2026-08-11T01:40:00Z</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -45169,26 +45169,26 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -45202,26 +45202,26 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>6.7</v>
+        <v>11.8</v>
       </c>
       <c r="Q148" t="n">
-        <v>42.1</v>
+        <v>33.1</v>
       </c>
       <c r="R148" t="n">
-        <v>58.7</v>
+        <v>62.9</v>
       </c>
       <c r="S148" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T148" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U148" t="n">
-        <v>19.5</v>
+        <v>4.2</v>
       </c>
       <c r="V148" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
@@ -45260,7 +45260,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>H:2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr"/>
@@ -45272,17 +45272,17 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
@@ -45292,12 +45292,12 @@
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Last 1 games: 1/4, 0 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 13.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 19.6 HR allowed</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
@@ -45307,57 +45307,57 @@
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>96.7651</t>
+          <t>97.3267</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.082</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -45367,42 +45367,42 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD148" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="BE148" t="inlineStr">
         <is>
-          <t>0.1481</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="BF148" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="BG148" t="inlineStr">
         <is>
-          <t>242 deg</t>
+          <t>225 deg</t>
         </is>
       </c>
       <c r="BH148" t="inlineStr">
@@ -45412,12 +45412,12 @@
       </c>
       <c r="BI148" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BJ148" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BK148" t="inlineStr">
@@ -45427,12 +45427,12 @@
       </c>
       <c r="BL148" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101</t>
         </is>
       </c>
       <c r="BM148" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BN148" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -11149,27 +11149,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>691718</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-11T23:45:00Z</t>
+          <t>2026-08-11T22:45:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -11179,26 +11179,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Cristopher Sánchez</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>650911</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -11212,33 +11200,31 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>55.6</v>
+        <v>54.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>33.3</v>
+        <v>41.2</v>
       </c>
       <c r="R34" t="n">
-        <v>51.1</v>
+        <v>44.7</v>
       </c>
       <c r="S34" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T34" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U34" t="n">
-        <v>51.9</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V34" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="W34" t="n">
-        <v>55</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
           <t>No</t>
@@ -11251,7 +11237,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -11276,7 +11262,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr"/>
@@ -11293,132 +11279,108 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Contact streak: 11/32 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>90.06</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>104.7741</t>
+          <t>101.6338</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.4498</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>0.1942</t>
+          <t>0.2211</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.3319</t>
+          <t>0.3518</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>83.05</t>
+          <t>43.13</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>49.67</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.1708</t>
-        </is>
-      </c>
-      <c r="BC34" t="inlineStr">
-        <is>
-          <t>7.17</t>
-        </is>
-      </c>
-      <c r="BD34" t="inlineStr">
-        <is>
-          <t>41.83</t>
-        </is>
-      </c>
-      <c r="BE34" t="inlineStr">
-        <is>
-          <t>89.28</t>
-        </is>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>0.3569</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>0.1242</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
-      </c>
+          <t>0.2508</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>143 deg</t>
+          <t>278 deg</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
@@ -11428,80 +11390,40 @@
       </c>
       <c r="BK34" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.8730&amp;lon=-77.0074</t>
         </is>
       </c>
       <c r="BL34" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr"/>
-      <c r="BQ34" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="BR34" t="inlineStr">
-        <is>
-          <t>0.144</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="BT34" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BU34" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="BV34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BX34" t="inlineStr">
-        <is>
-          <t>7.62</t>
-        </is>
-      </c>
-      <c r="BY34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BZ34" t="inlineStr">
-        <is>
-          <t>Volume support but ISO modest</t>
-        </is>
-      </c>
+      <c r="BQ34" t="inlineStr"/>
+      <c r="BR34" t="inlineStr"/>
+      <c r="BS34" t="inlineStr"/>
+      <c r="BT34" t="inlineStr"/>
+      <c r="BU34" t="inlineStr"/>
+      <c r="BV34" t="inlineStr"/>
+      <c r="BW34" t="inlineStr"/>
+      <c r="BX34" t="inlineStr"/>
+      <c r="BY34" t="inlineStr"/>
+      <c r="BZ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -11509,27 +11431,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>691718</t>
+          <t>665052</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>Griffin Conine</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-11T22:45:00Z</t>
+          <t>2026-08-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -11539,14 +11461,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>694973</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L35" t="n">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -11560,26 +11494,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>54.1</v>
+        <v>59.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>41.2</v>
+        <v>28.6</v>
       </c>
       <c r="R35" t="n">
-        <v>44.7</v>
+        <v>47</v>
       </c>
       <c r="S35" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T35" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>70.40000000000001</v>
+        <v>48.7</v>
       </c>
       <c r="V35" t="n">
         <v>50</v>
@@ -11597,7 +11531,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -11622,7 +11556,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr"/>
@@ -11639,12 +11573,12 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
@@ -11659,88 +11593,112 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>90.06</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>101.6338</t>
+          <t>103.5826</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.4698</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>0.2211</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.3518</t>
+          <t>0.3461</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.26</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>49.67</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.2508</t>
-        </is>
-      </c>
-      <c r="BC35" t="inlineStr"/>
-      <c r="BD35" t="inlineStr"/>
-      <c r="BE35" t="inlineStr"/>
-      <c r="BF35" t="inlineStr"/>
-      <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="inlineStr"/>
+          <t>0.2448</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>6.71</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>88.16</t>
+        </is>
+      </c>
+      <c r="BF35" t="inlineStr">
+        <is>
+          <t>0.3273</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>0.1211</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>24.06</t>
+        </is>
+      </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>278 deg</t>
+          <t>83 deg</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
@@ -11750,27 +11708,27 @@
       </c>
       <c r="BK35" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.8730&amp;lon=-77.0074</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=25.7781&amp;lon=-80.2197</t>
         </is>
       </c>
       <c r="BL35" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BM35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BO35" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BP35" t="inlineStr"/>
@@ -11791,27 +11749,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>665052</t>
+          <t>641933</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Griffin Conine</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-11T22:40:00Z</t>
+          <t>2026-08-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -11826,12 +11784,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>694973</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -11840,7 +11798,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>55.7</v>
+        <v>55.4</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -11854,31 +11812,33 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>59.7</v>
+        <v>48.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>28.6</v>
+        <v>50.6</v>
       </c>
       <c r="R36" t="n">
-        <v>47</v>
+        <v>51.6</v>
       </c>
       <c r="S36" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U36" t="n">
-        <v>48.7</v>
+        <v>78.7</v>
       </c>
       <c r="V36" t="n">
-        <v>50</v>
-      </c>
-      <c r="W36" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="W36" t="n">
+        <v>42</v>
+      </c>
       <c r="X36" t="inlineStr">
         <is>
           <t>No</t>
@@ -11938,127 +11898,127 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 12.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.1% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.43</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>103.5826</t>
+          <t>100.3792</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.4698</t>
+          <t>0.4404</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.2212</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.3461</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>74.26</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>45.37</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.2448</t>
+          <t>0.1909</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>88.16</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>0.3273</t>
+          <t>0.4501</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>0.1211</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>24.06</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>83 deg</t>
+          <t>45 deg</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
@@ -12068,12 +12028,12 @@
       </c>
       <c r="BK36" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=25.7781&amp;lon=-80.2197</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL36" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>47</t>
         </is>
       </c>
       <c r="BM36" t="inlineStr">
@@ -12088,20 +12048,60 @@
       </c>
       <c r="BO36" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP36" t="inlineStr"/>
-      <c r="BQ36" t="inlineStr"/>
-      <c r="BR36" t="inlineStr"/>
-      <c r="BS36" t="inlineStr"/>
-      <c r="BT36" t="inlineStr"/>
-      <c r="BU36" t="inlineStr"/>
-      <c r="BV36" t="inlineStr"/>
-      <c r="BW36" t="inlineStr"/>
-      <c r="BX36" t="inlineStr"/>
-      <c r="BY36" t="inlineStr"/>
-      <c r="BZ36" t="inlineStr"/>
+      <c r="BQ36" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="BR36" t="inlineStr">
+        <is>
+          <t>0.182</t>
+        </is>
+      </c>
+      <c r="BS36" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="BT36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU36" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="BV36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW36" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="BX36" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BY36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BZ36" t="inlineStr">
+        <is>
+          <t>Moderate profile</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -12109,27 +12109,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>641933</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-11T23:40:00Z</t>
+          <t>2026-08-11T23:45:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -12139,22 +12139,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -12172,32 +12172,32 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>48.6</v>
+        <v>55.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>50.6</v>
+        <v>33.3</v>
       </c>
       <c r="R37" t="n">
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
       <c r="S37" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T37" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U37" t="n">
-        <v>78.7</v>
+        <v>51.9</v>
       </c>
       <c r="V37" t="n">
-        <v>18</v>
+        <v>32.9</v>
       </c>
       <c r="W37" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -12253,188 +12253,188 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Contact streak: 11/32 over last 7 games</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>12.58</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>92.58</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>104.7741</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>0.4498</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>0.1942</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>0.3319</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>78.87</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>83.05</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>38.59</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>23.42</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>0.1708</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>41.83</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>89.28</t>
+        </is>
+      </c>
+      <c r="BF37" t="inlineStr">
+        <is>
+          <t>0.3569</t>
+        </is>
+      </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>0.1242</t>
+        </is>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>16.97</t>
+        </is>
+      </c>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>143 deg</t>
+        </is>
+      </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+        </is>
+      </c>
+      <c r="BL37" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="BM37" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 18.8 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
-        </is>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>89.43</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr">
-        <is>
-          <t>100.3792</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr">
-        <is>
-          <t>0.4404</t>
-        </is>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>0.2212</t>
-        </is>
-      </c>
-      <c r="AV37" t="inlineStr">
-        <is>
-          <t>0.325</t>
-        </is>
-      </c>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>72.81</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>23.12</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>45.37</t>
-        </is>
-      </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>39.91</t>
-        </is>
-      </c>
-      <c r="BA37" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="BB37" t="inlineStr">
-        <is>
-          <t>0.1909</t>
-        </is>
-      </c>
-      <c r="BC37" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BD37" t="inlineStr">
-        <is>
-          <t>34.9</t>
-        </is>
-      </c>
-      <c r="BE37" t="inlineStr">
-        <is>
-          <t>88.62</t>
-        </is>
-      </c>
-      <c r="BF37" t="inlineStr">
-        <is>
-          <t>0.4501</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="BH37" t="inlineStr">
-        <is>
-          <t>31.06</t>
-        </is>
-      </c>
-      <c r="BI37" t="inlineStr">
-        <is>
-          <t>45 deg</t>
-        </is>
-      </c>
-      <c r="BJ37" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK37" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
-        </is>
-      </c>
-      <c r="BL37" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="BM37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN37" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BO37" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BP37" t="inlineStr"/>
       <c r="BQ37" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="BR37" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BS37" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BT37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BU37" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>264</t>
         </is>
       </c>
       <c r="BV37" t="inlineStr">
@@ -12444,22 +12444,22 @@
       </c>
       <c r="BW37" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BX37" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BY37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BZ37" t="inlineStr">
         <is>
-          <t>Moderate profile</t>
+          <t>Volume support but ISO modest</t>
         </is>
       </c>
     </row>
@@ -25901,27 +25901,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>673357</t>
+          <t>671056</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Luis Robert</t>
+          <t>Ivan Herrera</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-11T23:15:00Z</t>
+          <t>2026-08-11T23:45:00Z</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -25931,17 +25931,17 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -25968,22 +25968,22 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>32.3</v>
+        <v>34.9</v>
       </c>
       <c r="Q80" t="n">
-        <v>39.5</v>
+        <v>33.3</v>
       </c>
       <c r="R80" t="n">
-        <v>53.9</v>
+        <v>51.1</v>
       </c>
       <c r="S80" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T80" t="n">
         <v>78</v>
       </c>
       <c r="U80" t="n">
-        <v>44.1</v>
+        <v>58.4</v>
       </c>
       <c r="V80" t="n">
         <v>50</v>
@@ -26001,7 +26001,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -26043,12 +26043,12 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Contact streak: 12/31 over last 7 games</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -26073,102 +26073,102 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>101.5476</t>
+          <t>101.478</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>0.3819</t>
+          <t>0.4107</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.1541</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>0.3028</t>
+          <t>0.3421</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>88.06</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>0.4185</t>
+          <t>0.3569</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>228 deg</t>
+          <t>143 deg</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr">
@@ -26178,27 +26178,27 @@
       </c>
       <c r="BK80" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
         </is>
       </c>
       <c r="BL80" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BM80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BN80" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BO80" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BP80" t="inlineStr"/>
@@ -26219,27 +26219,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>673357</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Luis Robert</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-11T23:40:00Z</t>
+          <t>2026-08-11T23:15:00Z</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -26249,22 +26249,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -26286,29 +26286,27 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>28.5</v>
+        <v>32.3</v>
       </c>
       <c r="Q81" t="n">
-        <v>50.6</v>
+        <v>39.5</v>
       </c>
       <c r="R81" t="n">
-        <v>51.6</v>
+        <v>53.9</v>
       </c>
       <c r="S81" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T81" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U81" t="n">
-        <v>37.8</v>
+        <v>44.1</v>
       </c>
       <c r="V81" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="W81" t="n">
-        <v>55</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr">
         <is>
           <t>No</t>
@@ -26321,7 +26319,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -26363,7 +26361,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -26378,117 +26376,117 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.1% barrel, 18.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>98.3612</t>
+          <t>101.5476</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3819</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>0.1448</t>
+          <t>0.1506</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>0.3182</t>
+          <t>0.3028</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>0.1414</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>88.06</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>0.4501</t>
+          <t>0.4185</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>45 deg</t>
+          <t>228 deg</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr">
@@ -26498,80 +26496,40 @@
       </c>
       <c r="BK81" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
         </is>
       </c>
       <c r="BL81" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BM81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="BN81" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BO81" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BP81" t="inlineStr"/>
-      <c r="BQ81" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="BR81" t="inlineStr">
-        <is>
-          <t>0.227</t>
-        </is>
-      </c>
-      <c r="BS81" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="BT81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BU81" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="BV81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW81" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="BX81" t="inlineStr">
-        <is>
-          <t>5.43</t>
-        </is>
-      </c>
-      <c r="BY81" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BZ81" t="inlineStr">
-        <is>
-          <t>Best BAL full sheet line but park neutral-negative</t>
-        </is>
-      </c>
+      <c r="BQ81" t="inlineStr"/>
+      <c r="BR81" t="inlineStr"/>
+      <c r="BS81" t="inlineStr"/>
+      <c r="BT81" t="inlineStr"/>
+      <c r="BU81" t="inlineStr"/>
+      <c r="BV81" t="inlineStr"/>
+      <c r="BW81" t="inlineStr"/>
+      <c r="BX81" t="inlineStr"/>
+      <c r="BY81" t="inlineStr"/>
+      <c r="BZ81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -26579,27 +26537,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>671056</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ivan Herrera</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-11T23:45:00Z</t>
+          <t>2026-08-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -26614,21 +26572,21 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -26646,27 +26604,29 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>34.9</v>
+        <v>28.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>33.3</v>
+        <v>50.6</v>
       </c>
       <c r="R82" t="n">
-        <v>51.1</v>
+        <v>51.6</v>
       </c>
       <c r="S82" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T82" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U82" t="n">
-        <v>58.4</v>
+        <v>37.8</v>
       </c>
       <c r="V82" t="n">
-        <v>50</v>
-      </c>
-      <c r="W82" t="inlineStr"/>
+        <v>28.9</v>
+      </c>
+      <c r="W82" t="n">
+        <v>55</v>
+      </c>
       <c r="X82" t="inlineStr">
         <is>
           <t>No</t>
@@ -26721,12 +26681,12 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
@@ -26736,117 +26696,117 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Contact streak: 12/31 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>101.478</t>
+          <t>98.3612</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.4107</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>0.1541</t>
+          <t>0.1448</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>0.3421</t>
+          <t>0.3182</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>0.1548</t>
+          <t>0.1414</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>0.3569</t>
+          <t>0.4501</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="BI82" t="inlineStr">
         <is>
-          <t>143 deg</t>
+          <t>45 deg</t>
         </is>
       </c>
       <c r="BJ82" t="inlineStr">
@@ -26856,40 +26816,80 @@
       </c>
       <c r="BK82" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL82" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>47</t>
         </is>
       </c>
       <c r="BM82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN82" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BO82" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP82" t="inlineStr"/>
-      <c r="BQ82" t="inlineStr"/>
-      <c r="BR82" t="inlineStr"/>
-      <c r="BS82" t="inlineStr"/>
-      <c r="BT82" t="inlineStr"/>
-      <c r="BU82" t="inlineStr"/>
-      <c r="BV82" t="inlineStr"/>
-      <c r="BW82" t="inlineStr"/>
-      <c r="BX82" t="inlineStr"/>
-      <c r="BY82" t="inlineStr"/>
-      <c r="BZ82" t="inlineStr"/>
+      <c r="BQ82" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="BR82" t="inlineStr">
+        <is>
+          <t>0.227</t>
+        </is>
+      </c>
+      <c r="BS82" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="BT82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BU82" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="BV82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW82" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="BX82" t="inlineStr">
+        <is>
+          <t>5.43</t>
+        </is>
+      </c>
+      <c r="BY82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BZ82" t="inlineStr">
+        <is>
+          <t>Best BAL full sheet line but park neutral-negative</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>63.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1235,7 +1235,7 @@
         <v>55.6</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1249,39 +1249,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1502,7 +1498,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1744,7 +1740,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2138,7 +2134,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2380,7 +2376,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3404,7 +3400,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3646,7 +3642,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -4040,7 +4036,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4282,7 +4278,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -5297,24 +5293,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-08-14T02:10:00Z</t>
@@ -5322,31 +5318,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5360,26 +5356,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>36.7</v>
+        <v>36.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>54.8</v>
+        <v>35.4</v>
       </c>
       <c r="R16" t="n">
         <v>55.6</v>
       </c>
       <c r="S16" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>46.5</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5387,42 +5383,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5439,12 +5431,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5454,12 +5446,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5469,102 +5461,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>101.4213</t>
+          <t>99.849</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.4336</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3294</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>73.27</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1855</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5615,32 +5607,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5650,12 +5642,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5664,7 +5656,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5678,26 +5670,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>50.4</v>
+        <v>36.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.5</v>
+        <v>54.8</v>
       </c>
       <c r="R17" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="S17" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5740,7 +5732,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5757,132 +5749,132 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>102.1801</t>
+          <t>101.4213</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3553</t>
+          <t>0.3294</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5892,7 +5884,7 @@
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL17" t="inlineStr">
@@ -5907,12 +5899,12 @@
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr"/>
@@ -5933,27 +5925,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5963,22 +5955,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -5996,26 +5988,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>36.2</v>
+        <v>50.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="R18" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="S18" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>46.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6033,7 +6025,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -6075,7 +6067,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -6085,122 +6077,122 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.849</t>
+          <t>102.1801</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.4336</t>
+          <t>0.475</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.3553</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1855</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>241 deg</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6210,7 +6202,7 @@
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL18" t="inlineStr">
@@ -6225,12 +6217,12 @@
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr"/>
@@ -6276,7 +6268,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6518,7 +6510,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6871,27 +6863,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6901,26 +6893,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6934,26 +6926,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>33.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="R21" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="S21" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>81.7</v>
+        <v>56.2</v>
       </c>
       <c r="V21" t="n">
         <v>50</v>
@@ -6971,7 +6963,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -7013,12 +7005,12 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -7033,7 +7025,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -7043,102 +7035,102 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>98.539</t>
+          <t>102.0363</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4441</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>0.1588</t>
+          <t>0.1985</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.3328</t>
+          <t>0.3451</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>41.99</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.2254</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>241 deg</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -7148,7 +7140,7 @@
       </c>
       <c r="BK21" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL21" t="inlineStr">
@@ -7163,12 +7155,12 @@
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr"/>
@@ -7189,56 +7181,56 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>50.5</v>
+        <v>49.8</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -7252,26 +7244,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>50.1</v>
+        <v>42.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>13.5</v>
+        <v>35.4</v>
       </c>
       <c r="R22" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="S22" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U22" t="n">
-        <v>56.2</v>
+        <v>18</v>
       </c>
       <c r="V22" t="n">
         <v>50</v>
@@ -7279,39 +7271,35 @@
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7331,27 +7319,27 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -7361,102 +7349,102 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>102.0363</t>
+          <t>100.4673</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.4441</t>
+          <t>0.4824</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>0.1985</t>
+          <t>0.1923</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.3451</t>
+          <t>0.3689</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>41.99</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>0.2254</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -7466,7 +7454,7 @@
       </c>
       <c r="BK22" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL22" t="inlineStr">
@@ -7481,12 +7469,12 @@
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr"/>
@@ -7825,12 +7813,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -7850,12 +7838,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -7874,7 +7862,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -7888,11 +7876,11 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>42.4</v>
+        <v>41.4</v>
       </c>
       <c r="Q24" t="n">
         <v>35.4</v>
@@ -7901,13 +7889,13 @@
         <v>55.6</v>
       </c>
       <c r="S24" t="n">
-        <v>92.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>50</v>
@@ -7915,39 +7903,35 @@
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7967,12 +7951,12 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -7982,12 +7966,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -7997,67 +7981,67 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>100.4673</t>
+          <t>100.8738</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.4824</t>
+          <t>0.4221</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>0.1923</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.3689</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>30.01</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -8092,7 +8076,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -8168,7 +8152,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8410,7 +8394,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -10347,27 +10331,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>666139</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -10377,26 +10361,26 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -10414,22 +10398,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>41.4</v>
+        <v>34.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>35.4</v>
+        <v>50.8</v>
       </c>
       <c r="R32" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="S32" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T32" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V32" t="n">
         <v>50</v>
@@ -10447,7 +10431,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -10472,7 +10456,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr"/>
@@ -10494,7 +10478,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -10504,12 +10488,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -10519,102 +10503,102 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>38.83</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>100.8738</t>
+          <t>99.4278</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.4221</t>
+          <t>0.3868</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>30.01</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1404</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1679</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>241 deg</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
@@ -10624,7 +10608,7 @@
       </c>
       <c r="BK32" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL32" t="inlineStr">
@@ -10639,12 +10623,12 @@
       </c>
       <c r="BN32" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr"/>
@@ -10665,56 +10649,56 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>666139</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>45.8</v>
+        <v>45.6</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -10728,26 +10712,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>34.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>50.8</v>
+        <v>34.4</v>
       </c>
       <c r="R33" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="S33" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T33" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U33" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="V33" t="n">
         <v>50</v>
@@ -10755,42 +10739,38 @@
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr"/>
@@ -10807,12 +10787,12 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -10822,12 +10802,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -10837,102 +10817,102 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>99.4278</t>
+          <t>99.655</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3868</t>
+          <t>0.3886</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.3196</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.1404</t>
+          <t>0.1367</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>0.1679</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
@@ -10942,7 +10922,7 @@
       </c>
       <c r="BK33" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL33" t="inlineStr">
@@ -10957,12 +10937,12 @@
       </c>
       <c r="BN33" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr"/>
@@ -11301,56 +11281,56 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>664761</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Alec Bohm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-13T23:30:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>671737</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -11364,26 +11344,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>23.7</v>
+        <v>29.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>34.4</v>
+        <v>46.8</v>
       </c>
       <c r="R35" t="n">
-        <v>55.6</v>
+        <v>42.6</v>
       </c>
       <c r="S35" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T35" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>10.8</v>
+        <v>29.4</v>
       </c>
       <c r="V35" t="n">
         <v>50</v>
@@ -11391,42 +11371,38 @@
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr"/>
@@ -11443,12 +11419,12 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
@@ -11458,12 +11434,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 6/19, 0 HR</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 17.6 HR allowed</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -11473,132 +11449,120 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>43.04</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>99.655</t>
+          <t>100.1087</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3886</t>
+          <t>0.3948</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1348</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.3196</t>
+          <t>0.3149</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>71.14</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>21.88</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.1367</t>
+          <t>0.1276</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1561</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
         <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK35" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
-        </is>
-      </c>
-      <c r="BL35" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="BM35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>MLB Stats API weather feed</t>
+        </is>
+      </c>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
       <c r="BN35" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO35" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Field of Dreams</t>
         </is>
       </c>
       <c r="BP35" t="inlineStr"/>
@@ -11619,27 +11583,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>664761</t>
+          <t>571771</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alec Bohm</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-13T23:30:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -11649,26 +11613,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>671737</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>44.6</v>
+        <v>44.3</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -11682,26 +11646,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>29.6</v>
+        <v>39.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>46.8</v>
+        <v>35.4</v>
       </c>
       <c r="R36" t="n">
-        <v>42.6</v>
+        <v>55.6</v>
       </c>
       <c r="S36" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U36" t="n">
-        <v>29.4</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>50</v>
@@ -11719,7 +11683,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -11740,7 +11704,7 @@
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr"/>
@@ -11757,12 +11721,12 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
@@ -11772,12 +11736,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 0 HR</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 17.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -11787,120 +11751,132 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>100.1087</t>
+          <t>99.5161</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3948</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>0.1348</t>
+          <t>0.1744</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.3149</t>
+          <t>0.3024</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>71.14</t>
+          <t>70.47</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.1276</t>
+          <t>0.2155</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>0.1561</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
         <is>
-          <t>MLB Stats API weather feed</t>
-        </is>
-      </c>
-      <c r="BK36" t="inlineStr"/>
-      <c r="BL36" t="inlineStr"/>
-      <c r="BM36" t="inlineStr"/>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+        </is>
+      </c>
+      <c r="BL36" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="BM36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="BN36" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BO36" t="inlineStr">
         <is>
-          <t>Field of Dreams</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP36" t="inlineStr"/>
@@ -12239,12 +12215,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -12254,7 +12230,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -12264,7 +12240,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -12288,7 +12264,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -12302,11 +12278,11 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>34</v>
+        <v>19.2</v>
       </c>
       <c r="Q38" t="n">
         <v>35.4</v>
@@ -12315,55 +12291,49 @@
         <v>55.6</v>
       </c>
       <c r="S38" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T38" t="n">
+        <v>78</v>
+      </c>
+      <c r="U38" t="n">
+        <v>32</v>
+      </c>
+      <c r="V38" t="n">
         <v>50</v>
       </c>
-      <c r="U38" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="V38" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>57</v>
-      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12383,27 +12353,27 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 6/18 over last 7 games</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -12413,67 +12383,67 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>35.54</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>87.32</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>98.8348</t>
+          <t>98.1514</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3937</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>0.1563</t>
+          <t>0.1146</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.3461</t>
+          <t>0.3154</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>36.57</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>32.98</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.1588</t>
+          <t>0.1294</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -12508,7 +12478,7 @@
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr">
@@ -12542,56 +12512,16 @@
         </is>
       </c>
       <c r="BP38" t="inlineStr"/>
-      <c r="BQ38" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="BR38" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="BS38" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="BT38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU38" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="BV38" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="BW38" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BX38" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="BY38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BZ38" t="inlineStr">
-        <is>
-          <t>Park/split help but hitter sheet not loud</t>
-        </is>
-      </c>
+      <c r="BQ38" t="inlineStr"/>
+      <c r="BR38" t="inlineStr"/>
+      <c r="BS38" t="inlineStr"/>
+      <c r="BT38" t="inlineStr"/>
+      <c r="BU38" t="inlineStr"/>
+      <c r="BV38" t="inlineStr"/>
+      <c r="BW38" t="inlineStr"/>
+      <c r="BX38" t="inlineStr"/>
+      <c r="BY38" t="inlineStr"/>
+      <c r="BZ38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -13235,12 +13165,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>571771</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -13260,12 +13190,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -13284,7 +13214,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -13298,11 +13228,11 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>39.7</v>
+        <v>34</v>
       </c>
       <c r="Q41" t="n">
         <v>35.4</v>
@@ -13311,55 +13241,51 @@
         <v>55.6</v>
       </c>
       <c r="S41" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T41" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V41" t="n">
-        <v>19.5</v>
+        <v>27.1</v>
       </c>
       <c r="W41" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -13379,27 +13305,27 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/12, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -13409,67 +13335,67 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>99.5161</t>
+          <t>98.8348</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>0.4164</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>0.1744</t>
+          <t>0.1563</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.3024</t>
+          <t>0.3461</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>70.47</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>32.98</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.2155</t>
+          <t>0.1588</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -13504,7 +13430,7 @@
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
@@ -13545,12 +13471,12 @@
       </c>
       <c r="BR41" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="BS41" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BT41" t="inlineStr">
@@ -13560,12 +13486,12 @@
       </c>
       <c r="BU41" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BV41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="BW41" t="inlineStr">
@@ -13575,17 +13501,17 @@
       </c>
       <c r="BX41" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="BY41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BZ41" t="inlineStr">
         <is>
-          <t>Tiny sample; park helps but not core parlay leg</t>
+          <t>Park/split help but hitter sheet not loud</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14754,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -15070,7 +14996,7 @@
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr">
@@ -15146,7 +15072,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -15388,7 +15314,7 @@
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr">
@@ -17340,7 +17266,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -17364,7 +17290,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>29.3</v>
+        <v>29.9</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -17378,7 +17304,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -17391,7 +17317,7 @@
         <v>55.6</v>
       </c>
       <c r="S54" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T54" t="n">
         <v>50</v>
@@ -17405,39 +17331,35 @@
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -17582,7 +17504,7 @@
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr">
@@ -18726,7 +18648,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -18750,7 +18672,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>63.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -18764,7 +18686,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -18777,7 +18699,7 @@
         <v>55.6</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -18791,39 +18713,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -18968,7 +18886,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -19044,7 +18962,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -19286,7 +19204,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -19680,7 +19598,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -19922,7 +19840,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -20946,7 +20864,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21188,7 +21106,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -21582,7 +21500,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21824,7 +21742,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -22839,24 +22757,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-08-14T02:10:00Z</t>
@@ -22864,31 +22782,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -22902,26 +22820,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>36.7</v>
+        <v>36.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>54.8</v>
+        <v>35.4</v>
       </c>
       <c r="R16" t="n">
         <v>55.6</v>
       </c>
       <c r="S16" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>18.3</v>
+        <v>46.5</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -22929,42 +22847,38 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -22981,12 +22895,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -22996,12 +22910,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -23011,102 +22925,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>40.98</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>101.4213</t>
+          <t>99.849</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.4196</t>
+          <t>0.4336</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3294</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>73.27</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>35.11</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1855</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -23157,32 +23071,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-14T02:07:00Z</t>
+          <t>2026-08-14T02:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23192,12 +23106,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -23206,7 +23120,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -23220,26 +23134,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>50.4</v>
+        <v>36.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.5</v>
+        <v>54.8</v>
       </c>
       <c r="R17" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="S17" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -23282,7 +23196,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -23299,132 +23213,132 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>102.1801</t>
+          <t>101.4213</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.4196</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3553</t>
+          <t>0.3294</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>35.11</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.1698</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.4223</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>241 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -23434,7 +23348,7 @@
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL17" t="inlineStr">
@@ -23449,12 +23363,12 @@
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr"/>
@@ -23475,27 +23389,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -23505,22 +23419,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -23538,26 +23452,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>36.2</v>
+        <v>50.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="R18" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="S18" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>46.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -23575,7 +23489,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -23617,7 +23531,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -23627,122 +23541,122 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>40.98</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.849</t>
+          <t>102.1801</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.4336</t>
+          <t>0.475</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.3553</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>25.84</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1855</t>
+          <t>0.1698</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>241 deg</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -23752,7 +23666,7 @@
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL18" t="inlineStr">
@@ -23767,12 +23681,12 @@
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr"/>
@@ -23818,7 +23732,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -24060,7 +23974,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -24413,27 +24327,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14T02:10:00Z</t>
+          <t>2026-08-14T02:07:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -24443,26 +24357,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -24476,26 +24390,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>33.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>35.4</v>
+        <v>13.5</v>
       </c>
       <c r="R21" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="S21" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U21" t="n">
-        <v>81.7</v>
+        <v>56.2</v>
       </c>
       <c r="V21" t="n">
         <v>50</v>
@@ -24513,7 +24427,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -24555,12 +24469,12 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -24575,7 +24489,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -24585,102 +24499,102 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>48.72</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>98.539</t>
+          <t>102.0363</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4441</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>0.1588</t>
+          <t>0.1985</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.3328</t>
+          <t>0.3451</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>41.99</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.2254</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>251 deg</t>
+          <t>241 deg</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -24690,7 +24604,7 @@
       </c>
       <c r="BK21" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL21" t="inlineStr">
@@ -24705,12 +24619,12 @@
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ180"/>
+  <dimension ref="A1:BZ181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4128,28 +4128,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4758,34 +4762,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6648,28 +6648,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14994,34 +14998,30 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23062,34 +23062,30 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC71" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD71" t="inlineStr"/>
       <c r="AE71" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25268,34 +25264,30 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC78" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD78" t="inlineStr"/>
       <c r="AE78" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26532,34 +26524,30 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC82" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD82" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -41804,34 +41792,30 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC130" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD130" t="inlineStr"/>
       <c r="AE130" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48955,27 +48939,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>680716</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Jonathan Ornelas</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -48985,17 +48969,17 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Jesús Luzardo</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>666200</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -49004,7 +48988,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -49022,22 +49006,22 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="Q153" t="n">
-        <v>20.8</v>
+        <v>45</v>
       </c>
       <c r="R153" t="n">
-        <v>62.6</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S153" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T153" t="n">
         <v>78</v>
       </c>
       <c r="U153" t="n">
-        <v>48.1</v>
+        <v>7</v>
       </c>
       <c r="V153" t="n">
         <v>50</v>
@@ -49055,7 +49039,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -49088,32 +49072,32 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 1 HR</t>
+          <t>Last 6 games: 2/12, 0 HR</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -49123,102 +49107,102 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>86.24</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>96.6715</t>
+          <t>97.2612</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.3563</t>
+          <t>0.1434</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>0.1104</t>
+          <t>0.0155</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>0.3142</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>72.44</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>29.54</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>0.1164</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.4192</t>
         </is>
       </c>
       <c r="BG153" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="BH153" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr">
@@ -49228,27 +49212,27 @@
       </c>
       <c r="BK153" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL153" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>62</t>
         </is>
       </c>
       <c r="BM153" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN153" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BO153" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP153" t="inlineStr"/>
@@ -49269,12 +49253,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -49299,7 +49283,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -49318,7 +49302,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -49336,22 +49320,22 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>18.3</v>
+        <v>11.3</v>
       </c>
       <c r="Q154" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="R154" t="n">
         <v>62.6</v>
       </c>
       <c r="S154" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T154" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U154" t="n">
-        <v>46.9</v>
+        <v>48.1</v>
       </c>
       <c r="V154" t="n">
         <v>50</v>
@@ -49369,7 +49353,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -49407,12 +49391,12 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
@@ -49422,12 +49406,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/29, 1 HR</t>
+          <t>Last 7 games: 7/22, 1 HR</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -49437,67 +49421,67 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>97.4122</t>
+          <t>96.6715</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>0.3425</t>
+          <t>0.3563</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>0.1155</t>
+          <t>0.1104</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>0.2764</t>
+          <t>0.3142</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>0.1627</t>
+          <t>0.1164</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
@@ -49583,22 +49567,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>666023</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Freddy Fermin</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -49613,17 +49597,17 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Jesús Luzardo</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>666200</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -49632,7 +49616,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -49650,22 +49634,22 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>15.3</v>
+        <v>18.3</v>
       </c>
       <c r="Q155" t="n">
-        <v>38.6</v>
+        <v>19.4</v>
       </c>
       <c r="R155" t="n">
-        <v>50.1</v>
+        <v>62.6</v>
       </c>
       <c r="S155" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T155" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U155" t="n">
-        <v>57.5</v>
+        <v>46.9</v>
       </c>
       <c r="V155" t="n">
         <v>50</v>
@@ -49683,7 +49667,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -49721,12 +49705,12 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
@@ -49736,12 +49720,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>Contact streak: 8/21 over last 7 games</t>
+          <t>Last 7 games: 9/29, 1 HR</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 13.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -49751,102 +49735,102 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>29.69</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>88.05</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>97.1872</t>
+          <t>97.4122</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>0.3217</t>
+          <t>0.3425</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>0.1058</t>
+          <t>0.1155</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2764</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>69.78</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>42.48</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>28.02</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>0.1627</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
           <t>6.07</t>
         </is>
       </c>
-      <c r="AY155" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AZ155" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
-      </c>
-      <c r="BA155" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="BB155" t="inlineStr">
-        <is>
-          <t>0.1125</t>
-        </is>
-      </c>
-      <c r="BC155" t="inlineStr">
-        <is>
-          <t>8.11</t>
-        </is>
-      </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>32.83</t>
         </is>
       </c>
       <c r="BE155" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>0.3756</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="BG155" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BH155" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BI155" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ155" t="inlineStr">
@@ -49856,27 +49840,27 @@
       </c>
       <c r="BK155" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL155" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BM155" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BN155" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BO155" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP155" t="inlineStr"/>
@@ -49897,27 +49881,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>666023</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Freddy Fermin</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-15T22:10:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -49927,26 +49911,26 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -49960,26 +49944,26 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q156" t="n">
-        <v>34</v>
+        <v>38.6</v>
       </c>
       <c r="R156" t="n">
-        <v>48.1</v>
+        <v>50.1</v>
       </c>
       <c r="S156" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T156" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U156" t="n">
-        <v>50.3</v>
+        <v>57.5</v>
       </c>
       <c r="V156" t="n">
         <v>50</v>
@@ -49997,7 +49981,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -50040,7 +50024,7 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
@@ -50050,12 +50034,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Contact streak: 8/21 over last 7 games</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -50065,102 +50049,102 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>29.69</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>85.25</t>
+          <t>88.05</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>97.3292</t>
+          <t>97.1872</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>0.3563</t>
+          <t>0.3217</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>0.1047</t>
+          <t>0.1058</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>0.2796</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>73.03</t>
+          <t>69.78</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>0.1622</t>
+          <t>0.1125</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BD156" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BE156" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>0.3634</t>
+          <t>0.3756</t>
         </is>
       </c>
       <c r="BG156" t="inlineStr">
         <is>
-          <t>0.1366</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="BH156" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BI156" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ156" t="inlineStr">
@@ -50170,27 +50154,27 @@
       </c>
       <c r="BK156" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
         </is>
       </c>
       <c r="BL156" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BM156" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN156" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO156" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BP156" t="inlineStr"/>
@@ -50211,27 +50195,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>668952</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T22:10:00Z</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -50241,26 +50225,26 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Jesús Luzardo</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>666200</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>38</v>
+        <v>38.3</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -50274,26 +50258,26 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>25.4</v>
+        <v>13.2</v>
       </c>
       <c r="Q157" t="n">
-        <v>20.8</v>
+        <v>34</v>
       </c>
       <c r="R157" t="n">
-        <v>62.6</v>
+        <v>48.1</v>
       </c>
       <c r="S157" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T157" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U157" t="n">
-        <v>10.6</v>
+        <v>50.3</v>
       </c>
       <c r="V157" t="n">
         <v>50</v>
@@ -50311,7 +50295,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -50349,27 +50333,27 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -50379,102 +50363,102 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.25</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>99.1033</t>
+          <t>97.3292</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3563</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>0.1322</t>
+          <t>0.1047</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>0.2731</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.03</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>0.1022</t>
+          <t>0.1622</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="BD157" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="BE157" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>88.47</t>
         </is>
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.3634</t>
         </is>
       </c>
       <c r="BG157" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1366</t>
         </is>
       </c>
       <c r="BH157" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="BI157" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ157" t="inlineStr">
@@ -50484,27 +50468,27 @@
       </c>
       <c r="BK157" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
         </is>
       </c>
       <c r="BL157" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM157" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BN157" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO157" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BP157" t="inlineStr"/>
@@ -50525,27 +50509,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>668952</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-15T22:10:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -50555,26 +50539,26 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Jesús Luzardo</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>666200</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>37.7</v>
+        <v>38</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -50592,22 +50576,22 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q158" t="n">
-        <v>34</v>
+        <v>20.8</v>
       </c>
       <c r="R158" t="n">
-        <v>48.1</v>
+        <v>62.6</v>
       </c>
       <c r="S158" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T158" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U158" t="n">
-        <v>42</v>
+        <v>10.6</v>
       </c>
       <c r="V158" t="n">
         <v>50</v>
@@ -50625,7 +50609,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -50663,12 +50647,12 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL158" t="inlineStr">
@@ -50678,12 +50662,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>Contact streak: 12/30 over last 7 games</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -50693,102 +50677,102 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="AR158" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>92.9205</t>
+          <t>99.1033</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>0.0389</t>
+          <t>0.1322</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>0.2753</t>
+          <t>0.2731</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>27.71</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>0.0549</t>
+          <t>0.1022</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BD158" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>32.83</t>
         </is>
       </c>
       <c r="BE158" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BF158" t="inlineStr">
         <is>
-          <t>0.3634</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="BG158" t="inlineStr">
         <is>
-          <t>0.1366</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BH158" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BI158" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ158" t="inlineStr">
@@ -50798,27 +50782,27 @@
       </c>
       <c r="BK158" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL158" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BM158" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BN158" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BO158" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP158" t="inlineStr"/>
@@ -50839,12 +50823,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -50869,7 +50853,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -50906,7 +50890,7 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>15.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q159" t="n">
         <v>34</v>
@@ -50915,13 +50899,13 @@
         <v>48.1</v>
       </c>
       <c r="S159" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T159" t="n">
         <v>80</v>
       </c>
       <c r="U159" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="V159" t="n">
         <v>50</v>
@@ -50939,7 +50923,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -50977,12 +50961,12 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AL159" t="inlineStr">
@@ -50992,7 +50976,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>Contact streak: 8/18 over last 7 games</t>
+          <t>Contact streak: 12/30 over last 7 games</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
@@ -51007,67 +50991,67 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>96.9541</t>
+          <t>92.9205</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>0.3667</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>0.1011</t>
+          <t>0.0389</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2753</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>27.71</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.0549</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
@@ -51153,27 +51137,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>655316</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Andruw Monasterio</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-15T22:10:00Z</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -51188,12 +51172,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -51202,7 +51186,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>36.7</v>
+        <v>37.7</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
@@ -51216,26 +51200,26 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P160" t="n">
-        <v>26.4</v>
+        <v>15.1</v>
       </c>
       <c r="Q160" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="R160" t="n">
-        <v>32.3</v>
+        <v>48.1</v>
       </c>
       <c r="S160" t="n">
         <v>52.4</v>
       </c>
       <c r="T160" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U160" t="n">
-        <v>19.5</v>
+        <v>45</v>
       </c>
       <c r="V160" t="n">
         <v>50</v>
@@ -51274,7 +51258,7 @@
       <c r="AD160" t="inlineStr"/>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr"/>
@@ -51291,12 +51275,12 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL160" t="inlineStr">
@@ -51306,12 +51290,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Contact streak: 8/18 over last 7 games</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -51321,102 +51305,102 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>87.98</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>97.7733</t>
+          <t>96.9541</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.3667</t>
         </is>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>0.1418</t>
+          <t>0.1011</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>0.3031</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>69.24</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="BD160" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="BE160" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.47</t>
         </is>
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>0.3634</t>
         </is>
       </c>
       <c r="BG160" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1366</t>
         </is>
       </c>
       <c r="BH160" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="BI160" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ160" t="inlineStr">
@@ -51426,27 +51410,27 @@
       </c>
       <c r="BK160" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
         </is>
       </c>
       <c r="BL160" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM160" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BN160" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO160" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BP160" t="inlineStr"/>
@@ -51467,47 +51451,47 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>655316</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Andruw Monasterio</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-16T01:40:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -51516,7 +51500,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
@@ -51530,26 +51514,26 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="Q161" t="n">
-        <v>30.2</v>
+        <v>40</v>
       </c>
       <c r="R161" t="n">
-        <v>56.4</v>
+        <v>32.3</v>
       </c>
       <c r="S161" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T161" t="n">
         <v>50</v>
       </c>
       <c r="U161" t="n">
-        <v>9.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="V161" t="n">
         <v>50</v>
@@ -51557,42 +51541,38 @@
       <c r="W161" t="inlineStr"/>
       <c r="X161" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr"/>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr"/>
@@ -51614,7 +51594,7 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL161" t="inlineStr">
@@ -51624,12 +51604,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -51639,102 +51619,102 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>34.47</t>
         </is>
       </c>
       <c r="AR161" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>87.98</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>98.7601</t>
+          <t>97.7733</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>0.3552</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1418</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>0.2869</t>
+          <t>0.3031</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>69.24</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>35.73</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>0.1418</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BD161" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="BE161" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BF161" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BG161" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BH161" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="BI161" t="inlineStr">
         <is>
-          <t>214 deg</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BJ161" t="inlineStr">
@@ -51744,12 +51724,12 @@
       </c>
       <c r="BK161" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL161" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM161" t="inlineStr">
@@ -51759,12 +51739,12 @@
       </c>
       <c r="BN161" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO161" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP161" t="inlineStr"/>
@@ -51785,12 +51765,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -51815,7 +51795,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -51852,7 +51832,7 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>25.6</v>
+        <v>20.4</v>
       </c>
       <c r="Q162" t="n">
         <v>30.2</v>
@@ -51861,13 +51841,13 @@
         <v>56.4</v>
       </c>
       <c r="S162" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T162" t="n">
         <v>50</v>
       </c>
       <c r="U162" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V162" t="n">
         <v>50</v>
@@ -51885,7 +51865,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -51927,12 +51907,12 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
@@ -51942,7 +51922,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Last 7 games: 5/27, 0 HR</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
@@ -51957,67 +51937,67 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>87.21</t>
+          <t>87.68</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>99.6402</t>
+          <t>98.7601</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>0.3459</t>
+          <t>0.3552</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>0.1264</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>0.2617</t>
+          <t>0.2869</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>24.52</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>35.73</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>0.1515</t>
+          <t>0.1418</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
@@ -52103,24 +52083,24 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>675961</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Alika Williams</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
           <t>ATH</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F163" t="inlineStr">
         <is>
           <t>2026-08-16T01:40:00Z</t>
@@ -52133,22 +52113,22 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -52166,26 +52146,26 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P163" t="n">
-        <v>8.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q163" t="n">
-        <v>46.8</v>
+        <v>30.2</v>
       </c>
       <c r="R163" t="n">
         <v>56.4</v>
       </c>
       <c r="S163" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T163" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U163" t="n">
-        <v>16.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V163" t="n">
         <v>50</v>
@@ -52203,7 +52183,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -52228,7 +52208,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr"/>
@@ -52245,12 +52225,12 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
@@ -52260,12 +52240,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 17.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.2 HR allowed</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -52275,97 +52255,97 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AQ163" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>87.21</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>97.3169</t>
+          <t>99.6402</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.3459</t>
         </is>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.1264</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>0.2617</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1515</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD163" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="BE163" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>0.3677</t>
         </is>
       </c>
       <c r="BG163" t="inlineStr">
         <is>
-          <t>0.1523</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BH163" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="BI163" t="inlineStr">
@@ -52421,47 +52401,47 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>675961</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Alika Williams</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-16T01:40:00Z</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Wandy Peralta</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>593974</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -52470,7 +52450,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>36.1</v>
+        <v>36.5</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
@@ -52484,26 +52464,26 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P164" t="n">
-        <v>29.6</v>
+        <v>8.5</v>
       </c>
       <c r="Q164" t="n">
-        <v>17.5</v>
+        <v>46.8</v>
       </c>
       <c r="R164" t="n">
-        <v>50.1</v>
+        <v>56.4</v>
       </c>
       <c r="S164" t="n">
-        <v>52.4</v>
+        <v>40.2</v>
       </c>
       <c r="T164" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U164" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="V164" t="n">
         <v>50</v>
@@ -52511,38 +52491,42 @@
       <c r="W164" t="inlineStr"/>
       <c r="X164" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y164" t="inlineStr">
+      <c r="AB164" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr"/>
@@ -52559,12 +52543,12 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL164" t="inlineStr">
@@ -52574,12 +52558,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 17.9 HR allowed</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -52589,102 +52573,102 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
         <is>
-          <t>89.67</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>99.3565</t>
+          <t>97.3169</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr">
         <is>
-          <t>0.3652</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>0.2822</t>
+          <t>0.243</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>33.83</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>0.1065</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BD164" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="BE164" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="BF164" t="inlineStr">
         <is>
-          <t>0.3759</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BG164" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.1523</t>
         </is>
       </c>
       <c r="BH164" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BI164" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>214 deg</t>
         </is>
       </c>
       <c r="BJ164" t="inlineStr">
@@ -52694,12 +52678,12 @@
       </c>
       <c r="BK164" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BL164" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>47</t>
         </is>
       </c>
       <c r="BM164" t="inlineStr">
@@ -52709,12 +52693,12 @@
       </c>
       <c r="BN164" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO164" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BP164" t="inlineStr"/>
@@ -52735,32 +52719,32 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>686475</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tyler Tolbert</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-08-16T01:38:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -52770,12 +52754,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Wandy Peralta</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>593974</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -52798,26 +52782,26 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P165" t="n">
-        <v>9.699999999999999</v>
+        <v>29.6</v>
       </c>
       <c r="Q165" t="n">
-        <v>41</v>
+        <v>17.5</v>
       </c>
       <c r="R165" t="n">
-        <v>54.7</v>
+        <v>50.1</v>
       </c>
       <c r="S165" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T165" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U165" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V165" t="n">
         <v>50</v>
@@ -52825,39 +52809,35 @@
       <c r="W165" t="inlineStr"/>
       <c r="X165" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr"/>
       <c r="AE165" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -52882,7 +52862,7 @@
       </c>
       <c r="AK165" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL165" t="inlineStr">
@@ -52892,12 +52872,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/10, 0 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -52907,102 +52887,102 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AQ165" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="AR165" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>89.67</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>97.085</t>
+          <t>99.3565</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr">
         <is>
-          <t>0.3416</t>
+          <t>0.3652</t>
         </is>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>0.0809</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>0.3116</t>
+          <t>0.2822</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>69.32</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>33.83</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>0.1392</t>
+          <t>0.1065</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BD165" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="BE165" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>87.04</t>
         </is>
       </c>
       <c r="BF165" t="inlineStr">
         <is>
-          <t>0.3686</t>
+          <t>0.3759</t>
         </is>
       </c>
       <c r="BG165" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="BH165" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="BI165" t="inlineStr">
         <is>
-          <t>230 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ165" t="inlineStr">
@@ -53012,12 +52992,12 @@
       </c>
       <c r="BK165" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
         </is>
       </c>
       <c r="BL165" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BM165" t="inlineStr">
@@ -53027,12 +53007,12 @@
       </c>
       <c r="BN165" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO165" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BP165" t="inlineStr"/>
@@ -53053,47 +53033,47 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>686475</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Tyler Tolbert</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-16T01:38:00Z</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Jesús Luzardo</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>666200</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -53102,7 +53082,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
@@ -53116,26 +53096,26 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P166" t="n">
-        <v>19.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q166" t="n">
-        <v>20.8</v>
+        <v>41</v>
       </c>
       <c r="R166" t="n">
-        <v>62.6</v>
+        <v>54.7</v>
       </c>
       <c r="S166" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T166" t="n">
         <v>78</v>
       </c>
       <c r="U166" t="n">
-        <v>26.8</v>
+        <v>12</v>
       </c>
       <c r="V166" t="n">
         <v>50</v>
@@ -53143,38 +53123,42 @@
       <c r="W166" t="inlineStr"/>
       <c r="X166" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y166" t="inlineStr">
+      <c r="AB166" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr"/>
@@ -53186,32 +53170,32 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>Last 5 games: 3/17, 1 HR</t>
+          <t>Last 7 games: 2/10, 0 HR</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -53221,102 +53205,102 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>96.3696</t>
+          <t>97.085</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.3416</t>
         </is>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.0809</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>0.3116</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>69.32</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>35.69</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.1392</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BD166" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BE166" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="BF166" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.3686</t>
         </is>
       </c>
       <c r="BG166" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BH166" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI166" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>230 deg</t>
         </is>
       </c>
       <c r="BJ166" t="inlineStr">
@@ -53326,27 +53310,27 @@
       </c>
       <c r="BK166" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL166" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BM166" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN166" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO166" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP166" t="inlineStr"/>
@@ -53367,22 +53351,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>645302</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Victor Robles</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -53397,26 +53381,26 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Jesús Luzardo</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>666200</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>35.6</v>
+        <v>36</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -53430,26 +53414,26 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P167" t="n">
-        <v>3.4</v>
+        <v>19.6</v>
       </c>
       <c r="Q167" t="n">
-        <v>46.9</v>
+        <v>20.8</v>
       </c>
       <c r="R167" t="n">
-        <v>56.6</v>
+        <v>62.6</v>
       </c>
       <c r="S167" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T167" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U167" t="n">
-        <v>39.7</v>
+        <v>26.8</v>
       </c>
       <c r="V167" t="n">
         <v>50</v>
@@ -53467,7 +53451,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -53488,7 +53472,7 @@
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr"/>
@@ -53500,32 +53484,32 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>Contact streak: 5/13 over last 7 games</t>
+          <t>Last 5 games: 3/17, 1 HR</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 3.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -53535,102 +53519,102 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>94.474</t>
+          <t>96.3696</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>0.3095</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>0.0855</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.251</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>67.77</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>0.0549</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BD167" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>32.83</t>
         </is>
       </c>
       <c r="BE167" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BF167" t="inlineStr">
         <is>
-          <t>0.4563</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="BG167" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BH167" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BI167" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ167" t="inlineStr">
@@ -53640,27 +53624,27 @@
       </c>
       <c r="BK167" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=29.7573&amp;lon=-95.3555</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL167" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BM167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BN167" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BO167" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP167" t="inlineStr"/>
@@ -53681,27 +53665,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>702332</t>
+          <t>645302</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Victor Robles</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -53711,17 +53695,17 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -53730,7 +53714,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>34.4</v>
+        <v>35.6</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -53748,22 +53732,22 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q168" t="n">
-        <v>40</v>
+        <v>46.9</v>
       </c>
       <c r="R168" t="n">
-        <v>32.3</v>
+        <v>56.6</v>
       </c>
       <c r="S168" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T168" t="n">
         <v>50</v>
       </c>
       <c r="U168" t="n">
-        <v>37.8</v>
+        <v>39.7</v>
       </c>
       <c r="V168" t="n">
         <v>50</v>
@@ -53781,7 +53765,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -53802,7 +53786,7 @@
       <c r="AD168" t="inlineStr"/>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr"/>
@@ -53819,162 +53803,162 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL168" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>Contact streak: 5/13 over last 7 games</t>
+        </is>
+      </c>
+      <c r="AN168" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 3.5 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>20.12</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>84.21</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>94.474</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr">
+        <is>
+          <t>0.3095</t>
+        </is>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>0.0855</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>0.258</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>67.77</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>27.43</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>0.0549</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>9.38</t>
+        </is>
+      </c>
+      <c r="BD168" t="inlineStr">
+        <is>
+          <t>40.14</t>
+        </is>
+      </c>
+      <c r="BE168" t="inlineStr">
+        <is>
+          <t>89.49</t>
+        </is>
+      </c>
+      <c r="BF168" t="inlineStr">
+        <is>
+          <t>0.4563</t>
+        </is>
+      </c>
+      <c r="BG168" t="inlineStr">
+        <is>
+          <t>0.1823</t>
+        </is>
+      </c>
+      <c r="BH168" t="inlineStr">
+        <is>
+          <t>26.98</t>
+        </is>
+      </c>
+      <c r="BI168" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BJ168" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK168" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=29.7573&amp;lon=-95.3555</t>
+        </is>
+      </c>
+      <c r="BL168" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="BM168" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
-        </is>
-      </c>
-      <c r="AN168" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP168" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>26.69</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>84.22</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>95.8483</t>
-        </is>
-      </c>
-      <c r="AT168" t="inlineStr">
-        <is>
-          <t>0.3354</t>
-        </is>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>0.0937</t>
-        </is>
-      </c>
-      <c r="AV168" t="inlineStr">
-        <is>
-          <t>0.2952</t>
-        </is>
-      </c>
-      <c r="AW168" t="inlineStr">
-        <is>
-          <t>68.88</t>
-        </is>
-      </c>
-      <c r="AX168" t="inlineStr">
-        <is>
-          <t>5.44</t>
-        </is>
-      </c>
-      <c r="AY168" t="inlineStr">
-        <is>
-          <t>41.72</t>
-        </is>
-      </c>
-      <c r="AZ168" t="inlineStr">
-        <is>
-          <t>19.26</t>
-        </is>
-      </c>
-      <c r="BA168" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="BB168" t="inlineStr">
-        <is>
-          <t>0.1485</t>
-        </is>
-      </c>
-      <c r="BC168" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="BD168" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
-      </c>
-      <c r="BE168" t="inlineStr">
-        <is>
-          <t>89.5</t>
-        </is>
-      </c>
-      <c r="BF168" t="inlineStr">
-        <is>
-          <t>0.387</t>
-        </is>
-      </c>
-      <c r="BG168" t="inlineStr">
-        <is>
-          <t>0.167</t>
-        </is>
-      </c>
-      <c r="BH168" t="inlineStr">
-        <is>
-          <t>26.4</t>
-        </is>
-      </c>
-      <c r="BI168" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BJ168" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK168" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
-        </is>
-      </c>
-      <c r="BL168" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="BM168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN168" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BO168" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BP168" t="inlineStr"/>
@@ -53995,56 +53979,56 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>702332</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-16T01:38:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
@@ -54058,26 +54042,26 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P169" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="Q169" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R169" t="n">
-        <v>54.7</v>
+        <v>32.3</v>
       </c>
       <c r="S169" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T169" t="n">
         <v>50</v>
       </c>
       <c r="U169" t="n">
-        <v>18.3</v>
+        <v>37.8</v>
       </c>
       <c r="V169" t="n">
         <v>50</v>
@@ -54085,42 +54069,38 @@
       <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr"/>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr"/>
@@ -54137,12 +54117,12 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL169" t="inlineStr">
@@ -54152,12 +54132,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -54167,102 +54147,102 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
         <is>
-          <t>88.43</t>
+          <t>84.22</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>99.1098</t>
+          <t>95.8483</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr">
         <is>
-          <t>0.3019</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>0.0763</t>
+          <t>0.0937</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>0.2587</t>
+          <t>0.2952</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>68.88</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.1485</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BD169" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="BE169" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BF169" t="inlineStr">
         <is>
-          <t>0.3686</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BG169" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BH169" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="BI169" t="inlineStr">
         <is>
-          <t>230 deg</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BJ169" t="inlineStr">
@@ -54272,12 +54252,12 @@
       </c>
       <c r="BK169" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL169" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM169" t="inlineStr">
@@ -54287,12 +54267,12 @@
       </c>
       <c r="BN169" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO169" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP169" t="inlineStr"/>
@@ -54313,47 +54293,47 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-16T01:38:00Z</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Wandy Peralta</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>593974</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -54362,7 +54342,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -54376,26 +54356,26 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.4</v>
+        <v>13</v>
       </c>
       <c r="Q170" t="n">
-        <v>18.1</v>
+        <v>41</v>
       </c>
       <c r="R170" t="n">
-        <v>50.1</v>
+        <v>54.7</v>
       </c>
       <c r="S170" t="n">
-        <v>93.2</v>
+        <v>40.2</v>
       </c>
       <c r="T170" t="n">
         <v>50</v>
       </c>
       <c r="U170" t="n">
-        <v>52.1</v>
+        <v>18.3</v>
       </c>
       <c r="V170" t="n">
         <v>50</v>
@@ -54403,35 +54383,39 @@
       <c r="W170" t="inlineStr"/>
       <c r="X170" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y170" t="inlineStr">
+      <c r="AB170" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE170" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -54451,12 +54435,12 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL170" t="inlineStr">
@@ -54466,12 +54450,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 2/22, 1 HR</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -54481,102 +54465,102 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>88.43</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>92.4903</t>
+          <t>99.1098</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr">
         <is>
-          <t>0.3457</t>
+          <t>0.3019</t>
         </is>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>0.0713</t>
+          <t>0.0763</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>0.3212</t>
+          <t>0.2587</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>0.0733</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BD170" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BE170" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="BF170" t="inlineStr">
         <is>
-          <t>0.3759</t>
+          <t>0.3686</t>
         </is>
       </c>
       <c r="BG170" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BH170" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI170" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>230 deg</t>
         </is>
       </c>
       <c r="BJ170" t="inlineStr">
@@ -54586,12 +54570,12 @@
       </c>
       <c r="BK170" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL170" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BM170" t="inlineStr">
@@ -54601,12 +54585,12 @@
       </c>
       <c r="BN170" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO170" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP170" t="inlineStr"/>
@@ -54627,27 +54611,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>663968</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -54657,26 +54641,26 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Wandy Peralta</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>543243</t>
+          <t>593974</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -54690,26 +54674,26 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P171" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q171" t="n">
-        <v>34.2</v>
+        <v>18.1</v>
       </c>
       <c r="R171" t="n">
-        <v>32.3</v>
+        <v>50.1</v>
       </c>
       <c r="S171" t="n">
-        <v>64.3</v>
+        <v>93.2</v>
       </c>
       <c r="T171" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U171" t="n">
-        <v>43.2</v>
+        <v>52.1</v>
       </c>
       <c r="V171" t="n">
         <v>50</v>
@@ -54727,7 +54711,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -54765,12 +54749,12 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL171" t="inlineStr">
@@ -54780,12 +54764,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.4% barrel, 16.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -54795,102 +54779,102 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>85.97</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>96.7417</t>
+          <t>92.4903</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3457</t>
         </is>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>0.0822</t>
+          <t>0.0713</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>0.2837</t>
+          <t>0.3212</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>67.58</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>0.0867</t>
+          <t>0.0733</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BD171" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="BE171" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>87.04</t>
         </is>
       </c>
       <c r="BF171" t="inlineStr">
         <is>
-          <t>0.3824</t>
+          <t>0.3759</t>
         </is>
       </c>
       <c r="BG171" t="inlineStr">
         <is>
-          <t>0.1362</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="BH171" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="BI171" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ171" t="inlineStr">
@@ -54900,12 +54884,12 @@
       </c>
       <c r="BK171" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
         </is>
       </c>
       <c r="BL171" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BM171" t="inlineStr">
@@ -54915,12 +54899,12 @@
       </c>
       <c r="BN171" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO171" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BP171" t="inlineStr"/>
@@ -54941,27 +54925,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>663968</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-15T22:10:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -54971,17 +54955,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>543243</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -54990,7 +54974,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -55008,22 +54992,22 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q172" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="R172" t="n">
-        <v>48.1</v>
+        <v>32.3</v>
       </c>
       <c r="S172" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T172" t="n">
         <v>75</v>
       </c>
       <c r="U172" t="n">
-        <v>59.6</v>
+        <v>43.2</v>
       </c>
       <c r="V172" t="n">
         <v>50</v>
@@ -55041,7 +55025,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -55079,27 +55063,27 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.4% barrel, 16.6 HR allowed</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -55109,102 +55093,102 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>85.88</t>
+          <t>85.97</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>95.367</t>
+          <t>96.7417</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>0.2691</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>0.0759</t>
+          <t>0.0822</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>0.2512</t>
+          <t>0.2837</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>67.58</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>0.0871</t>
+          <t>0.0867</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD172" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="BE172" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>0.3634</t>
+          <t>0.3824</t>
         </is>
       </c>
       <c r="BG172" t="inlineStr">
         <is>
-          <t>0.1366</t>
+          <t>0.1362</t>
         </is>
       </c>
       <c r="BH172" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="BI172" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BJ172" t="inlineStr">
@@ -55214,27 +55198,27 @@
       </c>
       <c r="BK172" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL172" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM172" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN172" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO172" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP172" t="inlineStr"/>
@@ -55255,27 +55239,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T22:10:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -55285,26 +55269,26 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Wandy Peralta</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>593974</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>33.2</v>
+        <v>33.8</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -55318,26 +55302,26 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>20.9</v>
+        <v>5.6</v>
       </c>
       <c r="Q173" t="n">
-        <v>18.1</v>
+        <v>33</v>
       </c>
       <c r="R173" t="n">
-        <v>50.1</v>
+        <v>48.1</v>
       </c>
       <c r="S173" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T173" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U173" t="n">
-        <v>0.8</v>
+        <v>59.6</v>
       </c>
       <c r="V173" t="n">
         <v>50</v>
@@ -55355,7 +55339,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -55376,7 +55360,7 @@
       <c r="AD173" t="inlineStr"/>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr"/>
@@ -55393,27 +55377,27 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -55423,102 +55407,102 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>85.88</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>98.5438</t>
+          <t>95.367</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.2691</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0759</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2512</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.35</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>37.56</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.0871</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="BE173" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>88.47</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>0.3759</t>
+          <t>0.3634</t>
         </is>
       </c>
       <c r="BG173" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.1366</t>
         </is>
       </c>
       <c r="BH173" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr">
@@ -55528,27 +55512,27 @@
       </c>
       <c r="BK173" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
         </is>
       </c>
       <c r="BL173" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BN173" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO173" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BP173" t="inlineStr"/>
@@ -55569,27 +55553,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>669707</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -55599,22 +55583,22 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Wandy Peralta</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>543243</t>
+          <t>593974</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -55636,22 +55620,22 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>17</v>
+        <v>20.9</v>
       </c>
       <c r="Q174" t="n">
-        <v>35.9</v>
+        <v>18.1</v>
       </c>
       <c r="R174" t="n">
-        <v>32.3</v>
+        <v>50.1</v>
       </c>
       <c r="S174" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T174" t="n">
         <v>50</v>
       </c>
       <c r="U174" t="n">
-        <v>47.2</v>
+        <v>0.8</v>
       </c>
       <c r="V174" t="n">
         <v>50</v>
@@ -55669,7 +55653,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -55690,7 +55674,7 @@
       <c r="AD174" t="inlineStr"/>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr"/>
@@ -55707,27 +55691,27 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/16, 1 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -55737,102 +55721,102 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>98.6923</t>
+          <t>98.5438</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>0.0978</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>0.2981</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>0.0905</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="BE174" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>87.04</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>0.3824</t>
+          <t>0.3759</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr">
         <is>
-          <t>0.1362</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="BH174" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr">
@@ -55842,12 +55826,12 @@
       </c>
       <c r="BK174" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
         </is>
       </c>
       <c r="BL174" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BM174" t="inlineStr">
@@ -55857,12 +55841,12 @@
       </c>
       <c r="BN174" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO174" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BP174" t="inlineStr"/>
@@ -55883,27 +55867,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>543877</t>
+          <t>669707</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Christian Vázquez</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -55918,12 +55902,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Emerson Hancock</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>676106</t>
+          <t>543243</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -55932,7 +55916,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -55950,13 +55934,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>3.4</v>
+        <v>17</v>
       </c>
       <c r="Q175" t="n">
-        <v>46.2</v>
+        <v>35.9</v>
       </c>
       <c r="R175" t="n">
-        <v>56.6</v>
+        <v>32.3</v>
       </c>
       <c r="S175" t="n">
         <v>44.8</v>
@@ -55965,7 +55949,7 @@
         <v>50</v>
       </c>
       <c r="U175" t="n">
-        <v>13.6</v>
+        <v>47.2</v>
       </c>
       <c r="V175" t="n">
         <v>50</v>
@@ -56021,162 +56005,162 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>Last 7 games: 5/16, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN175" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.6 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>37.43</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>88.09</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>98.6923</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr">
+        <is>
+          <t>0.341</t>
+        </is>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>0.0978</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>0.2981</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>70.9</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>7.79</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>37.99</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>21.03</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>0.0905</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>7.42</t>
+        </is>
+      </c>
+      <c r="BD175" t="inlineStr">
+        <is>
+          <t>38.53</t>
+        </is>
+      </c>
+      <c r="BE175" t="inlineStr">
+        <is>
+          <t>89.11</t>
+        </is>
+      </c>
+      <c r="BF175" t="inlineStr">
+        <is>
+          <t>0.3824</t>
+        </is>
+      </c>
+      <c r="BG175" t="inlineStr">
+        <is>
+          <t>0.1362</t>
+        </is>
+      </c>
+      <c r="BH175" t="inlineStr">
+        <is>
+          <t>22.99</t>
+        </is>
+      </c>
+      <c r="BI175" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BJ175" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK175" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+        </is>
+      </c>
+      <c r="BL175" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="BM175" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN175" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP175" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>24.25</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>85.83</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr">
-        <is>
-          <t>95.4798</t>
-        </is>
-      </c>
-      <c r="AT175" t="inlineStr">
-        <is>
-          <t>0.2762</t>
-        </is>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>0.076</t>
-        </is>
-      </c>
-      <c r="AV175" t="inlineStr">
-        <is>
-          <t>0.2451</t>
-        </is>
-      </c>
-      <c r="AW175" t="inlineStr">
-        <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="AX175" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr">
-        <is>
-          <t>33.72</t>
-        </is>
-      </c>
-      <c r="AZ175" t="inlineStr">
-        <is>
-          <t>25.75</t>
-        </is>
-      </c>
-      <c r="BA175" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="BB175" t="inlineStr">
-        <is>
-          <t>0.0997</t>
-        </is>
-      </c>
-      <c r="BC175" t="inlineStr">
-        <is>
-          <t>8.26</t>
-        </is>
-      </c>
-      <c r="BD175" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BE175" t="inlineStr">
-        <is>
-          <t>89.35</t>
-        </is>
-      </c>
-      <c r="BF175" t="inlineStr">
-        <is>
-          <t>0.4316</t>
-        </is>
-      </c>
-      <c r="BG175" t="inlineStr">
-        <is>
-          <t>0.1717</t>
-        </is>
-      </c>
-      <c r="BH175" t="inlineStr">
-        <is>
-          <t>28.52</t>
-        </is>
-      </c>
-      <c r="BI175" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BJ175" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK175" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=29.7573&amp;lon=-95.3555</t>
-        </is>
-      </c>
-      <c r="BL175" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="BM175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="BN175" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO175" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP175" t="inlineStr"/>
@@ -56197,32 +56181,32 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>623168</t>
+          <t>543877</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tyler Heineman</t>
+          <t>Christian Vázquez</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-16T01:38:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -56232,12 +56216,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Emerson Hancock</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>676106</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -56246,7 +56230,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>31.4</v>
+        <v>33.1</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
@@ -56260,26 +56244,26 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q176" t="n">
-        <v>34.4</v>
+        <v>46.2</v>
       </c>
       <c r="R176" t="n">
-        <v>54.7</v>
+        <v>56.6</v>
       </c>
       <c r="S176" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T176" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U176" t="n">
-        <v>32</v>
+        <v>13.6</v>
       </c>
       <c r="V176" t="n">
         <v>50</v>
@@ -56287,39 +56271,35 @@
       <c r="W176" t="inlineStr"/>
       <c r="X176" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD176" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr"/>
       <c r="AE176" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -56344,7 +56324,7 @@
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL176" t="inlineStr">
@@ -56354,12 +56334,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>Contact streak: 4/12 over last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -56369,102 +56349,102 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>92.7282</t>
+          <t>95.4798</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>0.2832</t>
+          <t>0.2762</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>0.0573</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>0.2604</t>
+          <t>0.2451</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>65.68</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>0.0766</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="BD176" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BE176" t="inlineStr">
         <is>
-          <t>91.74</t>
+          <t>89.35</t>
         </is>
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>0.4227</t>
+          <t>0.4316</t>
         </is>
       </c>
       <c r="BG176" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BH176" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="BI176" t="inlineStr">
         <is>
-          <t>230 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ176" t="inlineStr">
@@ -56474,27 +56454,27 @@
       </c>
       <c r="BK176" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=29.7573&amp;lon=-95.3555</t>
         </is>
       </c>
       <c r="BL176" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>69</t>
         </is>
       </c>
       <c r="BM176" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BN176" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BO176" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BP176" t="inlineStr"/>
@@ -56515,32 +56495,32 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>686765</t>
+          <t>623168</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Nick Sogard</t>
+          <t>Tyler Heineman</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-16T01:38:00Z</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -56550,12 +56530,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -56564,7 +56544,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -56578,26 +56558,26 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P177" t="n">
-        <v>4.8</v>
+        <v>0.3</v>
       </c>
       <c r="Q177" t="n">
-        <v>38.9</v>
+        <v>34.4</v>
       </c>
       <c r="R177" t="n">
-        <v>32.3</v>
+        <v>54.7</v>
       </c>
       <c r="S177" t="n">
-        <v>44.8</v>
+        <v>40.2</v>
       </c>
       <c r="T177" t="n">
         <v>75</v>
       </c>
       <c r="U177" t="n">
-        <v>26.4</v>
+        <v>32</v>
       </c>
       <c r="V177" t="n">
         <v>50</v>
@@ -56605,38 +56585,42 @@
       <c r="W177" t="inlineStr"/>
       <c r="X177" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y177" t="inlineStr">
+      <c r="AB177" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr"/>
@@ -56653,12 +56637,12 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
@@ -56668,12 +56652,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Contact streak: 4/12 over last 7 games</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -56683,102 +56667,102 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
         <is>
-          <t>84.95</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>95.108</t>
+          <t>92.7282</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>0.3337</t>
+          <t>0.2832</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>0.0778</t>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>0.3118</t>
+          <t>0.2604</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>65.68</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>44.33</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>0.0777</t>
+          <t>0.0766</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="BD177" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BE177" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.74</t>
         </is>
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>0.4227</t>
         </is>
       </c>
       <c r="BG177" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BH177" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="BI177" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>230 deg</t>
         </is>
       </c>
       <c r="BJ177" t="inlineStr">
@@ -56788,12 +56772,12 @@
       </c>
       <c r="BK177" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL177" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BM177" t="inlineStr">
@@ -56803,12 +56787,12 @@
       </c>
       <c r="BN177" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO177" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP177" t="inlineStr"/>
@@ -56829,32 +56813,32 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>670032</t>
+          <t>686765</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Nick Sogard</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-08-16T01:40:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -56864,12 +56848,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -56878,7 +56862,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>30.1</v>
+        <v>31.1</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -56892,26 +56876,26 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="Q178" t="n">
-        <v>30.2</v>
+        <v>38.9</v>
       </c>
       <c r="R178" t="n">
-        <v>56.4</v>
+        <v>32.3</v>
       </c>
       <c r="S178" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T178" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U178" t="n">
-        <v>2</v>
+        <v>26.4</v>
       </c>
       <c r="V178" t="n">
         <v>50</v>
@@ -56919,42 +56903,38 @@
       <c r="W178" t="inlineStr"/>
       <c r="X178" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr"/>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr"/>
@@ -56971,12 +56951,12 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL178" t="inlineStr">
@@ -56986,12 +56966,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 0 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 14.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -57001,102 +56981,102 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>26.37</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>84.95</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>95.108</t>
+        </is>
+      </c>
+      <c r="AT178" t="inlineStr">
+        <is>
+          <t>0.3337</t>
+        </is>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>0.0778</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>0.3118</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>68.92</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>44.33</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>22.06</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>84.52</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>95.1609</t>
-        </is>
-      </c>
-      <c r="AT178" t="inlineStr">
-        <is>
-          <t>0.2571</t>
-        </is>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>0.0391</t>
-        </is>
-      </c>
-      <c r="AV178" t="inlineStr">
-        <is>
-          <t>0.2498</t>
-        </is>
-      </c>
-      <c r="AW178" t="inlineStr">
-        <is>
-          <t>66.58</t>
-        </is>
-      </c>
-      <c r="AX178" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="AY178" t="inlineStr">
-        <is>
-          <t>33.59</t>
-        </is>
-      </c>
-      <c r="AZ178" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="BA178" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>0.0294</t>
+          <t>0.0777</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BD178" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="BE178" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BG178" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BH178" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="BI178" t="inlineStr">
         <is>
-          <t>214 deg</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BJ178" t="inlineStr">
@@ -57106,12 +57086,12 @@
       </c>
       <c r="BK178" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL178" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM178" t="inlineStr">
@@ -57121,12 +57101,12 @@
       </c>
       <c r="BN178" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO178" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP178" t="inlineStr"/>
@@ -57147,47 +57127,47 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>669743</t>
+          <t>670032</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Alex Call</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-16T01:40:00Z</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -57196,7 +57176,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>29.2</v>
+        <v>30.1</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
@@ -57210,26 +57190,26 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="Q179" t="n">
-        <v>18.2</v>
+        <v>30.2</v>
       </c>
       <c r="R179" t="n">
-        <v>68.09999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="S179" t="n">
-        <v>52.4</v>
+        <v>40.2</v>
       </c>
       <c r="T179" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U179" t="n">
-        <v>15.3</v>
+        <v>2</v>
       </c>
       <c r="V179" t="n">
         <v>50</v>
@@ -57237,35 +57217,39 @@
       <c r="W179" t="inlineStr"/>
       <c r="X179" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y179" t="inlineStr">
+      <c r="AB179" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE179" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57290,7 +57274,7 @@
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AL179" t="inlineStr">
@@ -57300,12 +57284,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/9, 0 HR</t>
+          <t>Last 7 games: 2/15, 0 HR</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 11.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 14.2 HR allowed</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -57315,102 +57299,102 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
         <is>
-          <t>85.33</t>
+          <t>84.52</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>94.5569</t>
+          <t>95.1609</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>0.2955</t>
+          <t>0.2571</t>
         </is>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>0.0784</t>
+          <t>0.0391</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>0.2888</t>
+          <t>0.2498</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>66.66</t>
+          <t>66.58</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>35.74</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>0.0907</t>
+          <t>0.0294</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD179" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="BE179" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.3677</t>
         </is>
       </c>
       <c r="BG179" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BH179" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="BI179" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>214 deg</t>
         </is>
       </c>
       <c r="BJ179" t="inlineStr">
@@ -57420,12 +57404,12 @@
       </c>
       <c r="BK179" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BL179" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="BM179" t="inlineStr">
@@ -57435,12 +57419,12 @@
       </c>
       <c r="BN179" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO179" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BP179" t="inlineStr"/>
@@ -57461,27 +57445,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>669743</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Alex Call</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -57491,26 +57475,26 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Wandy Peralta</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>593974</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -57528,22 +57512,22 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Q180" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="R180" t="n">
-        <v>50.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S180" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T180" t="n">
         <v>50</v>
       </c>
       <c r="U180" t="n">
-        <v>42</v>
+        <v>15.3</v>
       </c>
       <c r="V180" t="n">
         <v>50</v>
@@ -57561,7 +57545,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -57599,12 +57583,12 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
@@ -57614,117 +57598,117 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>Contact streak: 6/15 over last 7 games</t>
+          <t>Last 7 games: 2/9, 0 HR</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>85.33</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>93.5097</t>
+          <t>94.5569</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.2955</t>
         </is>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>0.0938</t>
+          <t>0.0784</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>0.2783</t>
+          <t>0.2888</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>66.66</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>35.74</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>35.22</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BD180" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BE180" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>0.3759</t>
+          <t>0.274</t>
         </is>
       </c>
       <c r="BG180" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="BH180" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BI180" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ180" t="inlineStr">
@@ -57734,12 +57718,12 @@
       </c>
       <c r="BK180" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL180" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="BM180" t="inlineStr">
@@ -57749,12 +57733,12 @@
       </c>
       <c r="BN180" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BO180" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP180" t="inlineStr"/>
@@ -57768,6 +57752,320 @@
       <c r="BX180" t="inlineStr"/>
       <c r="BY180" t="inlineStr"/>
       <c r="BZ180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>690984</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Petey Halpin</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-08-15T23:10:00Z</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Pre-Game</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Wandy Peralta</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>593974</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>No major boost</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="R181" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="S181" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="T181" t="n">
+        <v>50</v>
+      </c>
+      <c r="U181" t="n">
+        <v>42</v>
+      </c>
+      <c r="V181" t="n">
+        <v>50</v>
+      </c>
+      <c r="W181" t="inlineStr"/>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr"/>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>H:2026/2025 P:2026/2025</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="inlineStr"/>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>Direct BvP not yet weighted; 2026/2025 Statcast baseline active</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AL181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>Contact streak: 6/15 over last 7 games</t>
+        </is>
+      </c>
+      <c r="AN181" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>5.11</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>81.45</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>93.5097</t>
+        </is>
+      </c>
+      <c r="AT181" t="inlineStr">
+        <is>
+          <t>0.308</t>
+        </is>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>0.0938</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t>0.2783</t>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>70.22</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>5.81</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>39.78</t>
+        </is>
+      </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>35.22</t>
+        </is>
+      </c>
+      <c r="BA181" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="BB181" t="inlineStr">
+        <is>
+          <t>0.0721</t>
+        </is>
+      </c>
+      <c r="BC181" t="inlineStr">
+        <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="BD181" t="inlineStr">
+        <is>
+          <t>33.96</t>
+        </is>
+      </c>
+      <c r="BE181" t="inlineStr">
+        <is>
+          <t>87.04</t>
+        </is>
+      </c>
+      <c r="BF181" t="inlineStr">
+        <is>
+          <t>0.3759</t>
+        </is>
+      </c>
+      <c r="BG181" t="inlineStr">
+        <is>
+          <t>0.1169</t>
+        </is>
+      </c>
+      <c r="BH181" t="inlineStr">
+        <is>
+          <t>16.92</t>
+        </is>
+      </c>
+      <c r="BI181" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BJ181" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK181" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+        </is>
+      </c>
+      <c r="BL181" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="BM181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN181" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="BO181" t="inlineStr">
+        <is>
+          <t>Progressive Field</t>
+        </is>
+      </c>
+      <c r="BP181" t="inlineStr"/>
+      <c r="BQ181" t="inlineStr"/>
+      <c r="BR181" t="inlineStr"/>
+      <c r="BS181" t="inlineStr"/>
+      <c r="BT181" t="inlineStr"/>
+      <c r="BU181" t="inlineStr"/>
+      <c r="BV181" t="inlineStr"/>
+      <c r="BW181" t="inlineStr"/>
+      <c r="BX181" t="inlineStr"/>
+      <c r="BY181" t="inlineStr"/>
+      <c r="BZ181" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -61494,28 +61792,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -62124,34 +62426,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -64014,28 +64312,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>54.7</v>
+        <v>55.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1205,7 +1205,7 @@
         <v>56.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1219,39 +1219,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1761,24 +1757,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -1791,17 +1787,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1824,26 +1820,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>42.7</v>
+        <v>46.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R5" t="n">
         <v>56.1</v>
       </c>
       <c r="S5" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>21.8</v>
+        <v>34.9</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1861,7 +1857,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1899,12 +1895,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1914,12 +1910,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1929,97 +1925,97 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.5695</t>
+          <t>102.6546</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4056</t>
+          <t>0.4692</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.195</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3482</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>43.41</t>
+          <t>67.06</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.2054</t>
+          <t>0.179</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2075,24 +2071,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -2105,17 +2101,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2124,7 +2120,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2138,26 +2134,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.7</v>
+        <v>42.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R6" t="n">
         <v>56.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>45.5</v>
+        <v>21.8</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2165,39 +2161,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2217,27 +2209,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/21, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2247,97 +2239,97 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.09</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.0625</t>
+          <t>101.5695</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.4056</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>43.41</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>33.07</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1789</t>
+          <t>0.2054</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2393,12 +2385,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2423,7 +2415,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2442,7 +2434,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2456,11 +2448,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>46.1</v>
+        <v>39.7</v>
       </c>
       <c r="Q7" t="n">
         <v>22.3</v>
@@ -2469,13 +2461,13 @@
         <v>56.1</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>34.9</v>
+        <v>45.5</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2483,39 +2475,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2535,22 +2523,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -2565,67 +2553,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>91.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6546</t>
+          <t>101.0625</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4692</t>
+          <t>0.417</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3482</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>67.06</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>33.07</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>0.1789</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -2711,24 +2699,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -2741,17 +2729,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2760,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.1</v>
+        <v>47</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2774,26 +2762,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>29.3</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R8" t="n">
         <v>56.1</v>
       </c>
       <c r="S8" t="n">
-        <v>93.2</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2811,7 +2799,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -2849,12 +2837,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2864,112 +2852,112 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/31, 0 HR</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>99.8917</t>
+          <t>100.7149</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.4161</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1793</t>
+          <t>0.1971</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3025,24 +3013,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>801126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Brock Rodden</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -3055,17 +3043,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3074,7 +3062,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.8</v>
+        <v>46.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3088,26 +3076,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>18.7</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R9" t="n">
         <v>56.1</v>
       </c>
       <c r="S9" t="n">
-        <v>96.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>53.9</v>
+        <v>19.5</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3125,7 +3113,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3146,7 +3134,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -3158,132 +3146,132 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 2 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>96.9468</t>
+          <t>98.2126</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3772</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3214</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>67.81</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1767</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3339,24 +3327,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>801126</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brock Rodden</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -3369,17 +3357,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3388,7 +3376,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3402,26 +3390,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>57.3</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.2</v>
+        <v>41.2</v>
       </c>
       <c r="R10" t="n">
         <v>56.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>19.5</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3429,42 +3417,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -3476,17 +3460,17 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3496,112 +3480,112 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 2 games: 2/8, 0 HR</t>
+          <t>Last 7 games: 4/31, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>98.2126</t>
+          <t>99.8917</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1793</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3657,24 +3641,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -3687,17 +3671,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3706,7 +3690,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>44.9</v>
+        <v>45.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3720,26 +3704,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>24.9</v>
+        <v>18.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
         <v>56.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>37.8</v>
+        <v>53.9</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3747,39 +3731,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3799,7 +3779,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3814,12 +3794,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3829,97 +3809,97 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>36.63</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>88.51</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>99.0446</t>
+          <t>96.9468</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3772</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.3214</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>52.28</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1767</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3975,12 +3955,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4005,7 +3985,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4024,7 +4004,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>44.7</v>
+        <v>45.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4038,26 +4018,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>54</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="R12" t="n">
         <v>56.1</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>78.7</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4065,39 +4045,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4117,97 +4093,97 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.7149</t>
+          <t>99.1945</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4161</t>
+          <t>0.4068</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1971</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -4293,24 +4269,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -4323,17 +4299,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4342,7 +4318,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.5</v>
+        <v>42.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4356,26 +4332,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24.7</v>
+        <v>14.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R13" t="n">
         <v>56.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>78.7</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4383,39 +4359,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4435,27 +4407,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4465,97 +4437,97 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.1945</t>
+          <t>96.9722</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.4068</t>
+          <t>0.3483</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1197</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2839</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4611,24 +4583,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -4641,17 +4613,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4660,7 +4632,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4674,26 +4646,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14.3</v>
+        <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R14" t="n">
         <v>56.1</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>21.1</v>
+        <v>37.8</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4711,7 +4683,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -4749,27 +4721,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4779,97 +4751,97 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>36.63</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>88.51</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>96.9722</t>
+          <t>99.0446</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3483</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1197</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2839</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4925,12 +4897,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>680977</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Brendan Donovan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4974,7 +4946,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.3</v>
+        <v>40.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4988,11 +4960,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.2</v>
+        <v>15.9</v>
       </c>
       <c r="Q15" t="n">
         <v>22.3</v>
@@ -5001,13 +4973,13 @@
         <v>56.1</v>
       </c>
       <c r="S15" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>7.9</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5015,39 +4987,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5067,12 +5035,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5082,12 +5050,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5097,67 +5065,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>86.62</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>99.4443</t>
+          <t>97.0553</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3975</t>
+          <t>0.3741</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1546</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5871,12 +5839,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680977</t>
+          <t>642215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brendan Donovan</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5901,7 +5869,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5920,7 +5888,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5934,11 +5902,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q18" t="n">
         <v>22.3</v>
@@ -5947,13 +5915,13 @@
         <v>56.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>20.9</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5961,39 +5929,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6013,27 +5977,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6043,67 +6007,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.62</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.0553</t>
+          <t>98.4627</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3741</t>
+          <t>0.3311</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1298</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.281</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>72.64</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -7253,7 +7217,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7272,7 +7236,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>54.7</v>
+        <v>55.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7286,7 +7250,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7299,7 +7263,7 @@
         <v>56.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -7313,39 +7277,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7855,24 +7815,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -7885,17 +7845,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7918,26 +7878,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>42.7</v>
+        <v>46.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R5" t="n">
         <v>56.1</v>
       </c>
       <c r="S5" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>21.8</v>
+        <v>34.9</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -7955,7 +7915,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7993,12 +7953,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -8008,12 +7968,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -8023,97 +7983,97 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>101.5695</t>
+          <t>102.6546</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4056</t>
+          <t>0.4692</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.195</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.3482</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>43.41</t>
+          <t>67.06</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.2054</t>
+          <t>0.179</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -8169,24 +8129,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -8199,17 +8159,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -8218,7 +8178,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8232,26 +8192,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.7</v>
+        <v>42.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R6" t="n">
         <v>56.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>45.5</v>
+        <v>21.8</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8259,39 +8219,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8311,27 +8267,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/21, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8341,97 +8297,97 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.09</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.0625</t>
+          <t>101.5695</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.4056</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>43.41</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>33.07</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1789</t>
+          <t>0.2054</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -8487,12 +8443,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Julio Rodriguez</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8517,7 +8473,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8536,7 +8492,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8550,11 +8506,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>46.1</v>
+        <v>39.7</v>
       </c>
       <c r="Q7" t="n">
         <v>22.3</v>
@@ -8563,13 +8519,13 @@
         <v>56.1</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>34.9</v>
+        <v>45.5</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8577,39 +8533,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8629,22 +8581,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -8659,67 +8611,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>91.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6546</t>
+          <t>101.0625</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4692</t>
+          <t>0.417</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3482</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>67.06</t>
+          <t>24.66</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>33.07</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>0.1789</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -8805,24 +8757,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>663728</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>Cal Raleigh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -8835,17 +8787,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -8854,7 +8806,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.1</v>
+        <v>47</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8868,26 +8820,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>29.3</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R8" t="n">
         <v>56.1</v>
       </c>
       <c r="S8" t="n">
-        <v>93.2</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -8905,7 +8857,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -8943,12 +8895,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -8958,112 +8910,112 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/31, 0 HR</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>99.8917</t>
+          <t>100.7149</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.4161</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.2236</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1793</t>
+          <t>0.1971</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -9119,24 +9071,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>801126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Brock Rodden</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -9149,17 +9101,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9168,7 +9120,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.8</v>
+        <v>46.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9182,26 +9134,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>18.7</v>
+        <v>57.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>21.2</v>
       </c>
       <c r="R9" t="n">
         <v>56.1</v>
       </c>
       <c r="S9" t="n">
-        <v>96.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>53.9</v>
+        <v>19.5</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -9219,7 +9171,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -9240,7 +9192,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -9252,132 +9204,132 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 2 games: 2/8, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>96.9468</t>
+          <t>98.2126</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3772</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3214</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>67.81</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1767</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -9433,24 +9385,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>801126</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brock Rodden</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -9463,17 +9415,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9482,7 +9434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9496,26 +9448,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>57.3</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.2</v>
+        <v>41.2</v>
       </c>
       <c r="R10" t="n">
         <v>56.1</v>
       </c>
       <c r="S10" t="n">
-        <v>40.2</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>19.5</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9523,42 +9475,38 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -9570,17 +9518,17 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -9590,112 +9538,112 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 2 games: 2/8, 0 HR</t>
+          <t>Last 7 games: 4/31, 0 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>98.2126</t>
+          <t>99.8917</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1793</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -9751,24 +9699,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -9781,17 +9729,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9800,7 +9748,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>44.9</v>
+        <v>45.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9814,26 +9762,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>24.9</v>
+        <v>18.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
         <v>56.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>37.8</v>
+        <v>53.9</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9841,39 +9789,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9893,7 +9837,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -9908,12 +9852,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -9923,97 +9867,97 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>36.63</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>88.51</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>99.0446</t>
+          <t>96.9468</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3772</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3166</t>
+          <t>0.3214</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>52.28</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1767</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -10069,12 +10013,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663728</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cal Raleigh</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10099,7 +10043,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -10118,7 +10062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>44.7</v>
+        <v>45.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10132,26 +10076,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>54</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="R12" t="n">
         <v>56.1</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>78.7</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10159,39 +10103,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10211,97 +10151,97 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.7149</t>
+          <t>99.1945</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.4161</t>
+          <t>0.4068</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.2236</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1971</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -10387,24 +10327,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -10417,17 +10357,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -10436,7 +10376,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.5</v>
+        <v>42.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10450,26 +10390,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>24.7</v>
+        <v>14.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.3</v>
+        <v>41.2</v>
       </c>
       <c r="R13" t="n">
         <v>56.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>78.7</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10477,39 +10417,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10529,27 +10465,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10559,97 +10495,97 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.1945</t>
+          <t>96.9722</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.4068</t>
+          <t>0.3483</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1197</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.2839</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>85.82</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -10705,24 +10641,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-16T23:20:00Z</t>
@@ -10735,17 +10671,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10754,7 +10690,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>42.6</v>
+        <v>42.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10768,26 +10704,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14.3</v>
+        <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="R14" t="n">
         <v>56.1</v>
       </c>
       <c r="S14" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>21.1</v>
+        <v>37.8</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10805,7 +10741,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -10843,27 +10779,27 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -10873,97 +10809,97 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>36.63</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>88.51</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>96.9722</t>
+          <t>99.0446</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3483</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1197</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2839</t>
+          <t>0.3166</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>85.82</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1297</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -11019,12 +10955,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>680977</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Brendan Donovan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11068,7 +11004,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.3</v>
+        <v>40.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11082,11 +11018,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.2</v>
+        <v>15.9</v>
       </c>
       <c r="Q15" t="n">
         <v>22.3</v>
@@ -11095,13 +11031,13 @@
         <v>56.1</v>
       </c>
       <c r="S15" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>7.9</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11109,39 +11045,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11161,12 +11093,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11176,12 +11108,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11191,67 +11123,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>86.62</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>99.4443</t>
+          <t>97.0553</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3975</t>
+          <t>0.3741</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1546</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.67</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11965,12 +11897,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680977</t>
+          <t>642215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brendan Donovan</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11995,7 +11927,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12014,7 +11946,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.2</v>
+        <v>35.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12028,11 +11960,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>15.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q18" t="n">
         <v>22.3</v>
@@ -12041,13 +11973,13 @@
         <v>56.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>20.9</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12055,39 +11987,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12107,27 +12035,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12137,67 +12065,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.62</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.0553</t>
+          <t>98.4627</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3741</t>
+          <t>0.3311</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1298</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.281</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>72.64</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>47.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -33185,32 +33185,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>665877</t>
+          <t>605170</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>José Fermín</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-17T17:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -33220,12 +33220,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Kent Emanuel</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>592288</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -33234,7 +33234,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -33248,26 +33248,26 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="Q102" t="n">
-        <v>41.2</v>
+        <v>37.9</v>
       </c>
       <c r="R102" t="n">
-        <v>78.3</v>
+        <v>52.6</v>
       </c>
       <c r="S102" t="n">
-        <v>86.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T102" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U102" t="n">
-        <v>28.9</v>
+        <v>10.6</v>
       </c>
       <c r="V102" t="n">
         <v>50</v>
@@ -33275,42 +33275,42 @@
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
+      <c r="AB102" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 9</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr"/>
@@ -33327,12 +33327,12 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
@@ -33342,12 +33342,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/16, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -33357,78 +33357,102 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>96.749</t>
+          <t>99.0024</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>0.3544</t>
+          <t>0.3963</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>0.0934</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>0.3124</t>
+          <t>0.3234</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>68.07</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>48.53</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>24.04</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>0.1207</t>
-        </is>
-      </c>
-      <c r="BC102" t="inlineStr"/>
-      <c r="BD102" t="inlineStr"/>
-      <c r="BE102" t="inlineStr"/>
-      <c r="BF102" t="inlineStr"/>
-      <c r="BG102" t="inlineStr"/>
-      <c r="BH102" t="inlineStr"/>
+          <t>0.1177</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>8.42</t>
+        </is>
+      </c>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BE102" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="BF102" t="inlineStr">
+        <is>
+          <t>0.4157</t>
+        </is>
+      </c>
+      <c r="BG102" t="inlineStr">
+        <is>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BH102" t="inlineStr">
+        <is>
+          <t>24.27</t>
+        </is>
+      </c>
       <c r="BI102" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>330 deg</t>
         </is>
       </c>
       <c r="BJ102" t="inlineStr">
@@ -33438,27 +33462,27 @@
       </c>
       <c r="BK102" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL102" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>43</t>
         </is>
       </c>
       <c r="BM102" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN102" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO102" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP102" t="inlineStr"/>
@@ -33479,32 +33503,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>665877</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>José Fermín</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T17:40:00Z</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -33514,21 +33538,21 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Kent Emanuel</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>592288</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -33542,26 +33566,26 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>17.2</v>
+        <v>11</v>
       </c>
       <c r="Q103" t="n">
-        <v>53.5</v>
+        <v>41.2</v>
       </c>
       <c r="R103" t="n">
-        <v>52.6</v>
+        <v>78.3</v>
       </c>
       <c r="S103" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T103" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U103" t="n">
-        <v>18.3</v>
+        <v>28.9</v>
       </c>
       <c r="V103" t="n">
         <v>50</v>
@@ -33569,17 +33593,17 @@
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -33594,17 +33618,17 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 9</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr"/>
@@ -33621,132 +33645,108 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 1 HR</t>
+          <t>Last 7 games: 5/16, 0 HR</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.7% barrel, 20.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>87.08</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>96.7609</t>
+          <t>96.749</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.3544</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>0.1272</t>
+          <t>0.0934</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>0.2892</t>
+          <t>0.3124</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>68.07</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>48.53</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>0.1579</t>
-        </is>
-      </c>
-      <c r="BC103" t="inlineStr">
-        <is>
-          <t>10.69</t>
-        </is>
-      </c>
-      <c r="BD103" t="inlineStr">
-        <is>
-          <t>36.23</t>
-        </is>
-      </c>
-      <c r="BE103" t="inlineStr">
-        <is>
-          <t>88.83</t>
-        </is>
-      </c>
-      <c r="BF103" t="inlineStr">
-        <is>
-          <t>0.4669</t>
-        </is>
-      </c>
-      <c r="BG103" t="inlineStr">
-        <is>
-          <t>0.2147</t>
-        </is>
-      </c>
-      <c r="BH103" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
-      </c>
+          <t>0.1207</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr"/>
+      <c r="BD103" t="inlineStr"/>
+      <c r="BE103" t="inlineStr"/>
+      <c r="BF103" t="inlineStr"/>
+      <c r="BG103" t="inlineStr"/>
+      <c r="BH103" t="inlineStr"/>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>330 deg</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr">
@@ -33756,27 +33756,27 @@
       </c>
       <c r="BK103" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
         </is>
       </c>
       <c r="BL103" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BM103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BN103" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO103" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BP103" t="inlineStr"/>
@@ -33797,27 +33797,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>672640</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -33827,26 +33827,26 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>45.5</v>
+        <v>45.9</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -33860,26 +33860,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>29.8</v>
+        <v>17.2</v>
       </c>
       <c r="Q104" t="n">
-        <v>32.1</v>
+        <v>53.5</v>
       </c>
       <c r="R104" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="S104" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T104" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U104" t="n">
-        <v>7</v>
+        <v>18.3</v>
       </c>
       <c r="V104" t="n">
         <v>50</v>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -33939,162 +33939,162 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Last 7 games: 2/23, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>switch hitter; pitcher baseline 10.7% barrel, 20.9 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>28.95</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>87.08</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>96.7609</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr">
+        <is>
+          <t>0.3611</t>
+        </is>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>0.1272</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>0.2892</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>68.86</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>46.77</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>32.32</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>0.1579</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>10.69</t>
+        </is>
+      </c>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>36.23</t>
+        </is>
+      </c>
+      <c r="BE104" t="inlineStr">
+        <is>
+          <t>88.83</t>
+        </is>
+      </c>
+      <c r="BF104" t="inlineStr">
+        <is>
+          <t>0.4669</t>
+        </is>
+      </c>
+      <c r="BG104" t="inlineStr">
+        <is>
+          <t>0.2147</t>
+        </is>
+      </c>
+      <c r="BH104" t="inlineStr">
+        <is>
+          <t>31.83</t>
+        </is>
+      </c>
+      <c r="BI104" t="inlineStr">
+        <is>
+          <t>330 deg</t>
+        </is>
+      </c>
+      <c r="BJ104" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK104" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+        </is>
+      </c>
+      <c r="BL104" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="BM104" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Last 7 games: 5/30, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 12.7 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP104" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>40.26</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>88.85</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>100.178</t>
-        </is>
-      </c>
-      <c r="AT104" t="inlineStr">
-        <is>
-          <t>0.4228</t>
-        </is>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>0.1461</t>
-        </is>
-      </c>
-      <c r="AV104" t="inlineStr">
-        <is>
-          <t>0.3237</t>
-        </is>
-      </c>
-      <c r="AW104" t="inlineStr">
-        <is>
-          <t>71.77</t>
-        </is>
-      </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>23.16</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>32.72</t>
-        </is>
-      </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>22.36</t>
-        </is>
-      </c>
-      <c r="BA104" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="BB104" t="inlineStr">
-        <is>
-          <t>0.1374</t>
-        </is>
-      </c>
-      <c r="BC104" t="inlineStr">
-        <is>
-          <t>6.96</t>
-        </is>
-      </c>
-      <c r="BD104" t="inlineStr">
-        <is>
-          <t>41.41</t>
-        </is>
-      </c>
-      <c r="BE104" t="inlineStr">
-        <is>
-          <t>89.14</t>
-        </is>
-      </c>
-      <c r="BF104" t="inlineStr">
-        <is>
-          <t>0.3548</t>
-        </is>
-      </c>
-      <c r="BG104" t="inlineStr">
-        <is>
-          <t>0.1228</t>
-        </is>
-      </c>
-      <c r="BH104" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="BI104" t="inlineStr">
-        <is>
-          <t>106 deg</t>
-        </is>
-      </c>
-      <c r="BJ104" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK104" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.9061&amp;lon=-75.1665</t>
-        </is>
-      </c>
-      <c r="BL104" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="BM104" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="BN104" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO104" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP104" t="inlineStr"/>
@@ -34115,47 +34115,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>672640</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-17T17:40:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Kent Emanuel</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>592288</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -34164,7 +34164,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>45.3</v>
+        <v>45.5</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -34178,26 +34178,26 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>15.7</v>
+        <v>29.8</v>
       </c>
       <c r="Q105" t="n">
-        <v>41.2</v>
+        <v>32.1</v>
       </c>
       <c r="R105" t="n">
-        <v>78.3</v>
+        <v>52.8</v>
       </c>
       <c r="S105" t="n">
-        <v>76.2</v>
+        <v>88.7</v>
       </c>
       <c r="T105" t="n">
         <v>78</v>
       </c>
       <c r="U105" t="n">
-        <v>10.8</v>
+        <v>7</v>
       </c>
       <c r="V105" t="n">
         <v>50</v>
@@ -34205,42 +34205,42 @@
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
+      <c r="AB105" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
@@ -34272,12 +34272,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 5/30, 0 HR</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -34287,78 +34287,102 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.85</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>98.6673</t>
+          <t>100.178</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.3372</t>
+          <t>0.4228</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>0.0895</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>0.2972</t>
+          <t>0.3237</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>32.72</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>0.089</t>
-        </is>
-      </c>
-      <c r="BC105" t="inlineStr"/>
-      <c r="BD105" t="inlineStr"/>
-      <c r="BE105" t="inlineStr"/>
-      <c r="BF105" t="inlineStr"/>
-      <c r="BG105" t="inlineStr"/>
-      <c r="BH105" t="inlineStr"/>
+          <t>0.1374</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>6.96</t>
+        </is>
+      </c>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>41.41</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr">
+        <is>
+          <t>89.14</t>
+        </is>
+      </c>
+      <c r="BF105" t="inlineStr">
+        <is>
+          <t>0.3548</t>
+        </is>
+      </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>0.1228</t>
+        </is>
+      </c>
+      <c r="BH105" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>106 deg</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr">
@@ -34368,27 +34392,27 @@
       </c>
       <c r="BK105" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.9061&amp;lon=-75.1665</t>
         </is>
       </c>
       <c r="BL105" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM105" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="BN105" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BO105" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BP105" t="inlineStr"/>
@@ -34409,47 +34433,47 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>687637</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-17T22:05:00Z</t>
+          <t>2026-08-17T17:40:00Z</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Shane McClanahan</t>
+          <t>Kent Emanuel</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>663556</t>
+          <t>592288</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -34472,26 +34496,26 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>29.2</v>
+        <v>15.7</v>
       </c>
       <c r="Q106" t="n">
         <v>41.2</v>
       </c>
       <c r="R106" t="n">
-        <v>53.1</v>
+        <v>78.3</v>
       </c>
       <c r="S106" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T106" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U106" t="n">
-        <v>26.4</v>
+        <v>10.8</v>
       </c>
       <c r="V106" t="n">
         <v>50</v>
@@ -34499,17 +34523,17 @@
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -34524,17 +34548,17 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr"/>
@@ -34551,27 +34575,27 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 1 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -34581,102 +34605,78 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>99.3636</t>
+          <t>98.6673</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>0.3372</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>0.1467</t>
+          <t>0.0895</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>0.3118</t>
+          <t>0.2972</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>21.32</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>0.1233</t>
-        </is>
-      </c>
-      <c r="BC106" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="BD106" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
-      </c>
-      <c r="BE106" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BF106" t="inlineStr">
-        <is>
-          <t>0.399</t>
-        </is>
-      </c>
-      <c r="BG106" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="BH106" t="inlineStr">
-        <is>
-          <t>27.3</t>
-        </is>
-      </c>
+          <t>0.089</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr"/>
+      <c r="BD106" t="inlineStr"/>
+      <c r="BE106" t="inlineStr"/>
+      <c r="BF106" t="inlineStr"/>
+      <c r="BG106" t="inlineStr"/>
+      <c r="BH106" t="inlineStr"/>
       <c r="BI106" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ106" t="inlineStr">
@@ -34686,27 +34686,27 @@
       </c>
       <c r="BK106" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
         </is>
       </c>
       <c r="BL106" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BM106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BN106" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO106" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BP106" t="inlineStr"/>
@@ -34727,27 +34727,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>678882</t>
+          <t>687637</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-17T23:10:00Z</t>
+          <t>2026-08-17T22:05:00Z</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -34757,17 +34757,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Shane McClanahan</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>683352</t>
+          <t>663556</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -34776,7 +34776,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -34790,26 +34790,26 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>22.5</v>
+        <v>29.2</v>
       </c>
       <c r="Q107" t="n">
-        <v>29.8</v>
+        <v>41.2</v>
       </c>
       <c r="R107" t="n">
-        <v>52.2</v>
+        <v>53.1</v>
       </c>
       <c r="S107" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T107" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U107" t="n">
-        <v>36.5</v>
+        <v>26.4</v>
       </c>
       <c r="V107" t="n">
         <v>50</v>
@@ -34827,7 +34827,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -34869,12 +34869,12 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
@@ -34884,117 +34884,117 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 1 HR</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>34.36</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>97.8335</t>
+          <t>99.3636</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>0.3775</t>
+          <t>0.373</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1467</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.3118</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>35.78</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>0.1741</t>
+          <t>0.1233</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BD107" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="BG107" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="BI107" t="inlineStr">
         <is>
-          <t>186 deg</t>
+          <t>286 deg</t>
         </is>
       </c>
       <c r="BJ107" t="inlineStr">
@@ -35004,27 +35004,27 @@
       </c>
       <c r="BK107" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=42.3467&amp;lon=-71.0972</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
         </is>
       </c>
       <c r="BL107" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BN107" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BO107" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BP107" t="inlineStr"/>
@@ -35045,27 +35045,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>650402</t>
+          <t>678882</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Gleyber Torres</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-17T23:05:00Z</t>
+          <t>2026-08-17T23:10:00Z</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -35075,26 +35075,26 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Carmen Mlodzinski</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>669387</t>
+          <t>683352</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -35108,26 +35108,26 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="Q108" t="n">
-        <v>41.1</v>
+        <v>29.8</v>
       </c>
       <c r="R108" t="n">
-        <v>42.8</v>
+        <v>52.2</v>
       </c>
       <c r="S108" t="n">
-        <v>88.7</v>
+        <v>95.5</v>
       </c>
       <c r="T108" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U108" t="n">
-        <v>52.1</v>
+        <v>36.5</v>
       </c>
       <c r="V108" t="n">
         <v>50</v>
@@ -35145,7 +35145,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -35170,7 +35170,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr"/>
@@ -35187,7 +35187,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -35202,117 +35202,117 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 7/29, 1 HR</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.36</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>97.7198</t>
+          <t>97.8335</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.3775</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>0.1496</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>35.78</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1741</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD108" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>0.4251</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr">
         <is>
-          <t>0.1441</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="BI108" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>186 deg</t>
         </is>
       </c>
       <c r="BJ108" t="inlineStr">
@@ -35322,27 +35322,27 @@
       </c>
       <c r="BK108" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=42.3467&amp;lon=-71.0972</t>
         </is>
       </c>
       <c r="BL108" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>52</t>
         </is>
       </c>
       <c r="BM108" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN108" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO108" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BP108" t="inlineStr"/>
@@ -35363,27 +35363,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>650402</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Gleyber Torres</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-17T22:05:00Z</t>
+          <t>2026-08-17T23:05:00Z</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -35393,26 +35393,26 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Shane McClanahan</t>
+          <t>Carmen Mlodzinski</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>663556</t>
+          <t>669387</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -35430,29 +35430,27 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>27.4</v>
+        <v>25.9</v>
       </c>
       <c r="Q109" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="R109" t="n">
-        <v>53.1</v>
+        <v>42.8</v>
       </c>
       <c r="S109" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T109" t="n">
         <v>50</v>
       </c>
       <c r="U109" t="n">
-        <v>22</v>
+        <v>52.1</v>
       </c>
       <c r="V109" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="W109" t="n">
-        <v>55</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr">
         <is>
           <t>No</t>
@@ -35465,7 +35463,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -35490,7 +35488,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr"/>
@@ -35507,27 +35505,27 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/30, 0 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -35537,102 +35535,102 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>98.1913</t>
+          <t>97.7198</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>0.3809</t>
+          <t>0.406</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>0.1406</t>
+          <t>0.1496</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>0.3168</t>
+          <t>0.342</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>24.89</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>0.1379</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4251</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.1441</t>
         </is>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="BI109" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ109" t="inlineStr">
@@ -35642,80 +35640,40 @@
       </c>
       <c r="BK109" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL109" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BN109" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO109" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP109" t="inlineStr"/>
-      <c r="BQ109" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="BR109" t="inlineStr">
-        <is>
-          <t>0.227</t>
-        </is>
-      </c>
-      <c r="BS109" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="BT109" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BU109" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="BV109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW109" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="BX109" t="inlineStr">
-        <is>
-          <t>5.43</t>
-        </is>
-      </c>
-      <c r="BY109" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BZ109" t="inlineStr">
-        <is>
-          <t>Best BAL full sheet line but park neutral-negative</t>
-        </is>
-      </c>
+      <c r="BQ109" t="inlineStr"/>
+      <c r="BR109" t="inlineStr"/>
+      <c r="BS109" t="inlineStr"/>
+      <c r="BT109" t="inlineStr"/>
+      <c r="BU109" t="inlineStr"/>
+      <c r="BV109" t="inlineStr"/>
+      <c r="BW109" t="inlineStr"/>
+      <c r="BX109" t="inlineStr"/>
+      <c r="BY109" t="inlineStr"/>
+      <c r="BZ109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -35723,27 +35681,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>605170</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Victor Caratini</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T22:05:00Z</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -35753,17 +35711,17 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Shane McClanahan</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>663556</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -35786,31 +35744,33 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>31</v>
+        <v>27.4</v>
       </c>
       <c r="Q110" t="n">
-        <v>37.9</v>
+        <v>41.2</v>
       </c>
       <c r="R110" t="n">
-        <v>52.6</v>
+        <v>53.1</v>
       </c>
       <c r="S110" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T110" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U110" t="n">
-        <v>10.6</v>
+        <v>22</v>
       </c>
       <c r="V110" t="n">
-        <v>50</v>
-      </c>
-      <c r="W110" t="inlineStr"/>
+        <v>28.9</v>
+      </c>
+      <c r="W110" t="n">
+        <v>55</v>
+      </c>
       <c r="X110" t="inlineStr">
         <is>
           <t>No</t>
@@ -35823,7 +35783,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -35848,7 +35808,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr"/>
@@ -35865,175 +35825,215 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Last 7 games: 8/30, 0 HR</t>
+        </is>
+      </c>
+      <c r="AN110" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>87.82</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>98.1913</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr">
+        <is>
+          <t>0.3809</t>
+        </is>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>0.1406</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>0.3168</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>70.6</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>7.27</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>36.25</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>24.89</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>0.1379</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>40.3</t>
+        </is>
+      </c>
+      <c r="BE110" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BF110" t="inlineStr">
+        <is>
+          <t>0.399</t>
+        </is>
+      </c>
+      <c r="BG110" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="BH110" t="inlineStr">
+        <is>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="BI110" t="inlineStr">
+        <is>
+          <t>286 deg</t>
+        </is>
+      </c>
+      <c r="BJ110" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK110" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+        </is>
+      </c>
+      <c r="BL110" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="BM110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN110" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="BO110" t="inlineStr">
+        <is>
+          <t>Tropicana Field</t>
+        </is>
+      </c>
+      <c r="BP110" t="inlineStr"/>
+      <c r="BQ110" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="BR110" t="inlineStr">
+        <is>
+          <t>0.227</t>
+        </is>
+      </c>
+      <c r="BS110" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="BT110" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AL110" t="inlineStr">
+      <c r="BU110" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="BV110" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP110" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>39.86</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>89.33</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>99.0024</t>
-        </is>
-      </c>
-      <c r="AT110" t="inlineStr">
-        <is>
-          <t>0.3963</t>
-        </is>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>0.1539</t>
-        </is>
-      </c>
-      <c r="AV110" t="inlineStr">
-        <is>
-          <t>0.3234</t>
-        </is>
-      </c>
-      <c r="AW110" t="inlineStr">
-        <is>
-          <t>71.39</t>
-        </is>
-      </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>16.29</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t>37.43</t>
-        </is>
-      </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>24.04</t>
-        </is>
-      </c>
-      <c r="BA110" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BB110" t="inlineStr">
-        <is>
-          <t>0.1177</t>
-        </is>
-      </c>
-      <c r="BC110" t="inlineStr">
-        <is>
-          <t>8.42</t>
-        </is>
-      </c>
-      <c r="BD110" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BE110" t="inlineStr">
-        <is>
-          <t>88.2</t>
-        </is>
-      </c>
-      <c r="BF110" t="inlineStr">
-        <is>
-          <t>0.4157</t>
-        </is>
-      </c>
-      <c r="BG110" t="inlineStr">
-        <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BH110" t="inlineStr">
-        <is>
-          <t>24.27</t>
-        </is>
-      </c>
-      <c r="BI110" t="inlineStr">
-        <is>
-          <t>330 deg</t>
-        </is>
-      </c>
-      <c r="BJ110" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK110" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
-        </is>
-      </c>
-      <c r="BL110" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="BM110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN110" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="BO110" t="inlineStr">
-        <is>
-          <t>Target Field</t>
-        </is>
-      </c>
-      <c r="BP110" t="inlineStr"/>
-      <c r="BQ110" t="inlineStr"/>
-      <c r="BR110" t="inlineStr"/>
-      <c r="BS110" t="inlineStr"/>
-      <c r="BT110" t="inlineStr"/>
-      <c r="BU110" t="inlineStr"/>
-      <c r="BV110" t="inlineStr"/>
-      <c r="BW110" t="inlineStr"/>
-      <c r="BX110" t="inlineStr"/>
-      <c r="BY110" t="inlineStr"/>
-      <c r="BZ110" t="inlineStr"/>
+      <c r="BW110" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="BX110" t="inlineStr">
+        <is>
+          <t>5.43</t>
+        </is>
+      </c>
+      <c r="BY110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BZ110" t="inlineStr">
+        <is>
+          <t>Best BAL full sheet line but park neutral-negative</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -39781,47 +39781,47 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>668885</t>
+          <t>680574</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Matt McLain</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T17:40:00Z</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>687273</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -39830,7 +39830,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -39844,26 +39844,26 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P123" t="n">
-        <v>12.2</v>
+        <v>33.7</v>
       </c>
       <c r="Q123" t="n">
-        <v>39</v>
+        <v>7.2</v>
       </c>
       <c r="R123" t="n">
-        <v>52.6</v>
+        <v>78.3</v>
       </c>
       <c r="S123" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T123" t="n">
         <v>78</v>
       </c>
       <c r="U123" t="n">
-        <v>47.7</v>
+        <v>31.6</v>
       </c>
       <c r="V123" t="n">
         <v>50</v>
@@ -39871,17 +39871,17 @@
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -39896,17 +39896,17 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr"/>
@@ -39923,12 +39923,12 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL123" t="inlineStr">
@@ -39938,117 +39938,117 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 1 HR</t>
+          <t>Last 7 games: 5/24, 1 HR</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
         <is>
-          <t>86.76</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>97.3124</t>
+          <t>98.9599</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr">
         <is>
-          <t>0.3491</t>
+          <t>0.3799</t>
         </is>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>0.3212</t>
+          <t>0.3082</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>68.83</t>
+          <t>70.93</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>32.87</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>0.0893</t>
+          <t>0.1447</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BD123" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="BG123" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BI123" t="inlineStr">
         <is>
-          <t>330 deg</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ123" t="inlineStr">
@@ -40058,27 +40058,27 @@
       </c>
       <c r="BK123" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
         </is>
       </c>
       <c r="BL123" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BM123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BN123" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO123" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BP123" t="inlineStr"/>
@@ -40119,12 +40119,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-17T17:40:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -40134,21 +40134,21 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Quinn Mathews</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>687273</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
@@ -40162,23 +40162,23 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P124" t="n">
         <v>33.7</v>
       </c>
       <c r="Q124" t="n">
-        <v>7.2</v>
+        <v>27.2</v>
       </c>
       <c r="R124" t="n">
-        <v>78.3</v>
+        <v>64.8</v>
       </c>
       <c r="S124" t="n">
-        <v>64.3</v>
+        <v>59.8</v>
       </c>
       <c r="T124" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U124" t="n">
         <v>31.6</v>
@@ -40189,42 +40189,42 @@
       <c r="W124" t="inlineStr"/>
       <c r="X124" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
+      <c r="AB124" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
+          <t>lineup projected / unconfirmed; order MLB 7 vs RotoWire 9</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr"/>
@@ -40261,12 +40261,12 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
@@ -40336,37 +40336,37 @@
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.3817</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.1321</t>
         </is>
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BI124" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>288 deg</t>
         </is>
       </c>
       <c r="BJ124" t="inlineStr">
@@ -40417,27 +40417,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>680574</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Matt McLain</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T22:05:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -40447,17 +40447,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -40480,26 +40480,26 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>33.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q125" t="n">
-        <v>27.2</v>
+        <v>40.3</v>
       </c>
       <c r="R125" t="n">
-        <v>64.8</v>
+        <v>53.1</v>
       </c>
       <c r="S125" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T125" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U125" t="n">
-        <v>31.6</v>
+        <v>47.7</v>
       </c>
       <c r="V125" t="n">
         <v>50</v>
@@ -40517,7 +40517,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -40537,7 +40537,7 @@
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed; order MLB 7 vs RotoWire 9</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
@@ -40559,12 +40559,12 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
@@ -40574,12 +40574,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Last 7 games: 6/19, 1 HR</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -40589,102 +40589,102 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>84.81</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>98.9599</t>
+          <t>96.2382</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.3799</t>
+          <t>0.3521</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>0.3082</t>
+          <t>0.3171</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>70.93</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>0.1447</t>
+          <t>0.1424</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>41.36</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.4082</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr">
         <is>
-          <t>0.1321</t>
+          <t>0.1588</t>
         </is>
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>288 deg</t>
+          <t>286 deg</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr">
@@ -40694,27 +40694,27 @@
       </c>
       <c r="BK125" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
         </is>
       </c>
       <c r="BL125" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM125" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BN125" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BO125" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BP125" t="inlineStr"/>
@@ -40735,27 +40735,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-17T22:05:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -40765,26 +40765,26 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -40798,26 +40798,26 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>8.800000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="Q126" t="n">
-        <v>40.3</v>
+        <v>37.9</v>
       </c>
       <c r="R126" t="n">
-        <v>53.1</v>
+        <v>52.6</v>
       </c>
       <c r="S126" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T126" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U126" t="n">
-        <v>47.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V126" t="n">
         <v>50</v>
@@ -40835,7 +40835,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -40877,27 +40877,27 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 12.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -40907,102 +40907,102 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>28.12</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>84.81</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>96.2382</t>
+          <t>97.4055</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.3521</t>
+          <t>0.3411</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.1155</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>0.3171</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>0.1424</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>41.36</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>0.4082</t>
+          <t>0.4157</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr">
         <is>
-          <t>0.1588</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>330 deg</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr">
@@ -41012,27 +41012,27 @@
       </c>
       <c r="BK126" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL126" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>43</t>
         </is>
       </c>
       <c r="BM126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN126" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO126" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP126" t="inlineStr"/>
@@ -46427,27 +46427,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>686780</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Pedro Pages</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -46457,26 +46457,26 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -46490,26 +46490,26 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>22.4</v>
+        <v>11.5</v>
       </c>
       <c r="Q144" t="n">
-        <v>50.9</v>
+        <v>39</v>
       </c>
       <c r="R144" t="n">
-        <v>64.8</v>
+        <v>52.6</v>
       </c>
       <c r="S144" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T144" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U144" t="n">
-        <v>16.6</v>
+        <v>43.2</v>
       </c>
       <c r="V144" t="n">
         <v>50</v>
@@ -46522,24 +46522,24 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
+      <c r="AB144" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC144" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -46552,7 +46552,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr"/>
@@ -46569,162 +46569,162 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL144" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>Last 7 games: 6/21, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN144" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>29.87</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>85.29</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>96.7373</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>0.1104</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>0.3149</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>68.64</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>7.73</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>38.96</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>26.69</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>0.1171</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>8.42</t>
+        </is>
+      </c>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BE144" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="BF144" t="inlineStr">
+        <is>
+          <t>0.4157</t>
+        </is>
+      </c>
+      <c r="BG144" t="inlineStr">
+        <is>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BH144" t="inlineStr">
+        <is>
+          <t>24.27</t>
+        </is>
+      </c>
+      <c r="BI144" t="inlineStr">
+        <is>
+          <t>330 deg</t>
+        </is>
+      </c>
+      <c r="BJ144" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK144" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+        </is>
+      </c>
+      <c r="BL144" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="BM144" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP144" t="inlineStr">
-        <is>
-          <t>5.72</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>86.95</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>99.3673</t>
-        </is>
-      </c>
-      <c r="AT144" t="inlineStr">
-        <is>
-          <t>0.3379</t>
-        </is>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>0.1236</t>
-        </is>
-      </c>
-      <c r="AV144" t="inlineStr">
-        <is>
-          <t>0.2639</t>
-        </is>
-      </c>
-      <c r="AW144" t="inlineStr">
-        <is>
-          <t>72.6</t>
-        </is>
-      </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>24.22</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
-      </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>26.85</t>
-        </is>
-      </c>
-      <c r="BA144" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="BB144" t="inlineStr">
-        <is>
-          <t>0.1176</t>
-        </is>
-      </c>
-      <c r="BC144" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="BD144" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
-      </c>
-      <c r="BE144" t="inlineStr">
-        <is>
-          <t>90.5</t>
-        </is>
-      </c>
-      <c r="BF144" t="inlineStr">
-        <is>
-          <t>0.456</t>
-        </is>
-      </c>
-      <c r="BG144" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="BH144" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="BI144" t="inlineStr">
-        <is>
-          <t>288 deg</t>
-        </is>
-      </c>
-      <c r="BJ144" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK144" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
-        </is>
-      </c>
-      <c r="BL144" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="BM144" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="BN144" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO144" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP144" t="inlineStr"/>
@@ -46745,27 +46745,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>686780</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Pedro Pages</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -46775,17 +46775,17 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Mason Barnett</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>686930</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -46794,7 +46794,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -46808,26 +46808,26 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>23.4</v>
+        <v>22.4</v>
       </c>
       <c r="Q145" t="n">
-        <v>47.7</v>
+        <v>50.9</v>
       </c>
       <c r="R145" t="n">
-        <v>50.7</v>
+        <v>64.8</v>
       </c>
       <c r="S145" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T145" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="V145" t="n">
         <v>50</v>
@@ -46840,12 +46840,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -46870,7 +46870,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr"/>
@@ -46887,12 +46887,12 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
@@ -46902,117 +46902,117 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.3% barrel, 8.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>86.95</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>99.8845</t>
+          <t>99.3673</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.3345</t>
+          <t>0.3379</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>0.1004</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>0.3059</t>
+          <t>0.2639</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>24.22</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>36.41</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>0.4158</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr">
         <is>
-          <t>0.1796</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BH145" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BI145" t="inlineStr">
         <is>
-          <t>354 deg</t>
+          <t>288 deg</t>
         </is>
       </c>
       <c r="BJ145" t="inlineStr">
@@ -47022,17 +47022,17 @@
       </c>
       <c r="BK145" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
         </is>
       </c>
       <c r="BL145" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BM145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BN145" t="inlineStr">
@@ -47042,7 +47042,7 @@
       </c>
       <c r="BO145" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BP145" t="inlineStr"/>
@@ -47063,22 +47063,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -47098,17 +47098,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Mason Barnett</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>686930</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -47126,17 +47126,17 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>18.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q146" t="n">
-        <v>37.9</v>
+        <v>47.7</v>
       </c>
       <c r="R146" t="n">
-        <v>52.6</v>
+        <v>50.7</v>
       </c>
       <c r="S146" t="n">
         <v>47.9</v>
@@ -47145,7 +47145,7 @@
         <v>75</v>
       </c>
       <c r="U146" t="n">
-        <v>70.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="V146" t="n">
         <v>50</v>
@@ -47205,132 +47205,132 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.3% barrel, 8.6 HR allowed</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>97.4055</t>
+          <t>99.8845</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.3411</t>
+          <t>0.3345</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>0.1155</t>
+          <t>0.1004</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.3059</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.78</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.4158</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1796</t>
         </is>
       </c>
       <c r="BH146" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>33.16</t>
         </is>
       </c>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>330 deg</t>
+          <t>354 deg</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr">
@@ -47340,27 +47340,27 @@
       </c>
       <c r="BK146" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
         </is>
       </c>
       <c r="BL146" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BM146" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BN146" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO146" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BP146" t="inlineStr"/>
@@ -48335,27 +48335,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>668952</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -48365,17 +48365,17 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -48402,22 +48402,22 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>31.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q150" t="n">
-        <v>1.1</v>
+        <v>39</v>
       </c>
       <c r="R150" t="n">
-        <v>66.2</v>
+        <v>52.6</v>
       </c>
       <c r="S150" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T150" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U150" t="n">
-        <v>18</v>
+        <v>10.6</v>
       </c>
       <c r="V150" t="n">
         <v>50</v>
@@ -48435,7 +48435,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -48477,12 +48477,12 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
@@ -48492,12 +48492,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -48507,102 +48507,102 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>87.47</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>100.1299</t>
+          <t>99.1033</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.3862</t>
+          <t>0.3418</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.1308</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>0.3067</t>
+          <t>0.2717</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.1001</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.4157</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr">
         <is>
-          <t>0.0651</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BH150" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>144 deg</t>
+          <t>330 deg</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr">
@@ -48612,27 +48612,27 @@
       </c>
       <c r="BK150" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.7559&amp;lon=-104.9942</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL150" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>43</t>
         </is>
       </c>
       <c r="BM150" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN150" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO150" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP150" t="inlineStr"/>
@@ -48653,27 +48653,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -48683,26 +48683,26 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -48720,22 +48720,22 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>24.7</v>
+        <v>31.4</v>
       </c>
       <c r="Q151" t="n">
-        <v>35.4</v>
+        <v>1.1</v>
       </c>
       <c r="R151" t="n">
-        <v>50.7</v>
+        <v>66.2</v>
       </c>
       <c r="S151" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T151" t="n">
         <v>75</v>
       </c>
       <c r="U151" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V151" t="n">
         <v>50</v>
@@ -48753,7 +48753,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -48795,7 +48795,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -48810,12 +48810,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 17.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -48825,102 +48825,102 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>87.47</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>97.9919</t>
+          <t>100.1299</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>0.3726</t>
+          <t>0.3862</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>0.1431</t>
+          <t>0.1533</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>0.2921</t>
+          <t>0.3067</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BD151" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BE151" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>0.4144</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="BG151" t="inlineStr">
         <is>
-          <t>0.1633</t>
+          <t>0.0651</t>
         </is>
       </c>
       <c r="BH151" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BI151" t="inlineStr">
         <is>
-          <t>354 deg</t>
+          <t>144 deg</t>
         </is>
       </c>
       <c r="BJ151" t="inlineStr">
@@ -48930,27 +48930,27 @@
       </c>
       <c r="BK151" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.7559&amp;lon=-104.9942</t>
         </is>
       </c>
       <c r="BL151" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BM151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BN151" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO151" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BP151" t="inlineStr"/>
@@ -48971,27 +48971,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>593871</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-17T23:10:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -49001,17 +49001,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -49020,7 +49020,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -49038,22 +49038,22 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>21.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q152" t="n">
-        <v>40.9</v>
+        <v>35.4</v>
       </c>
       <c r="R152" t="n">
-        <v>49.3</v>
+        <v>50.7</v>
       </c>
       <c r="S152" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T152" t="n">
         <v>75</v>
       </c>
       <c r="U152" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="V152" t="n">
         <v>50</v>
@@ -49071,7 +49071,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -49113,7 +49113,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -49123,17 +49123,17 @@
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 16.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 17.1 HR allowed</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -49143,102 +49143,102 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>87.58</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>98.6767</t>
+          <t>97.9919</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.3359</t>
+          <t>0.3726</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1431</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>0.2646</t>
+          <t>0.2921</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1659</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>0.4164</t>
+          <t>0.4144</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1633</t>
         </is>
       </c>
       <c r="BH152" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>191 deg</t>
+          <t>354 deg</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr">
@@ -49248,27 +49248,27 @@
       </c>
       <c r="BK152" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.7571&amp;lon=-73.8458</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
         </is>
       </c>
       <c r="BL152" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BM152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BN152" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO152" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BP152" t="inlineStr"/>
@@ -49289,27 +49289,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>622268</t>
+          <t>593871</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T23:10:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -49319,17 +49319,17 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -49356,22 +49356,22 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>13.8</v>
+        <v>21.5</v>
       </c>
       <c r="Q153" t="n">
-        <v>37.3</v>
+        <v>40.9</v>
       </c>
       <c r="R153" t="n">
-        <v>50.7</v>
+        <v>49.3</v>
       </c>
       <c r="S153" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T153" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U153" t="n">
-        <v>16.6</v>
+        <v>30.3</v>
       </c>
       <c r="V153" t="n">
         <v>50</v>
@@ -49389,7 +49389,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -49431,27 +49431,27 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 17.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -49461,102 +49461,102 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>36.14</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>88.96</t>
+          <t>87.58</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>97.6604</t>
+          <t>98.6767</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3359</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>0.0942</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.2646</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>19.78</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>0.1099</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>0.4144</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="BG153" t="inlineStr">
         <is>
-          <t>0.1633</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BH153" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>354 deg</t>
+          <t>191 deg</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr">
@@ -49566,27 +49566,27 @@
       </c>
       <c r="BK153" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.7571&amp;lon=-73.8458</t>
         </is>
       </c>
       <c r="BL153" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BN153" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BO153" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BP153" t="inlineStr"/>
@@ -49607,27 +49607,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>669364</t>
+          <t>622268</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -49637,26 +49637,26 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -49670,26 +49670,26 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P154" t="n">
-        <v>9.5</v>
+        <v>13.8</v>
       </c>
       <c r="Q154" t="n">
-        <v>30.8</v>
+        <v>37.3</v>
       </c>
       <c r="R154" t="n">
-        <v>52.8</v>
+        <v>50.7</v>
       </c>
       <c r="S154" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T154" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U154" t="n">
-        <v>18</v>
+        <v>16.6</v>
       </c>
       <c r="V154" t="n">
         <v>50</v>
@@ -49707,7 +49707,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -49749,12 +49749,12 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
@@ -49764,12 +49764,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.0% barrel, 12.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 17.1 HR allowed</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -49779,102 +49779,102 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>88.96</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>96.6117</t>
+          <t>97.6604</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>0.3565</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>0.0928</t>
+          <t>0.0942</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>0.3111</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>37.77</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>19.78</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>0.0917</t>
+          <t>0.1099</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BD154" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="BE154" t="inlineStr">
         <is>
-          <t>89.14</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.4144</t>
         </is>
       </c>
       <c r="BG154" t="inlineStr">
         <is>
-          <t>0.1228</t>
+          <t>0.1633</t>
         </is>
       </c>
       <c r="BH154" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="BI154" t="inlineStr">
         <is>
-          <t>106 deg</t>
+          <t>354 deg</t>
         </is>
       </c>
       <c r="BJ154" t="inlineStr">
@@ -49884,27 +49884,27 @@
       </c>
       <c r="BK154" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.9061&amp;lon=-75.1665</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
         </is>
       </c>
       <c r="BL154" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="BM154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN154" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="BM154" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BN154" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="BO154" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BP154" t="inlineStr"/>
@@ -49925,27 +49925,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>680779</t>
+          <t>669364</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Henry Davis</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-17T23:05:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -49955,17 +49955,17 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>664285</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -49988,26 +49988,26 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>35</v>
+        <v>9.5</v>
       </c>
       <c r="Q155" t="n">
-        <v>35.6</v>
+        <v>30.8</v>
       </c>
       <c r="R155" t="n">
-        <v>42.8</v>
+        <v>52.8</v>
       </c>
       <c r="S155" t="n">
-        <v>40.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T155" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U155" t="n">
-        <v>2.5</v>
+        <v>18</v>
       </c>
       <c r="V155" t="n">
         <v>50</v>
@@ -50025,7 +50025,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -50067,12 +50067,12 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
@@ -50082,12 +50082,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 13.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.0% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -50097,102 +50097,102 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>89.51</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>100.4627</t>
+          <t>96.6117</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>0.3505</t>
+          <t>0.3565</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.0928</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.3111</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>21.91</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.0917</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>44.06</t>
+          <t>41.41</t>
         </is>
       </c>
       <c r="BE155" t="inlineStr">
         <is>
-          <t>90.24</t>
+          <t>89.14</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>0.3548</t>
         </is>
       </c>
       <c r="BG155" t="inlineStr">
         <is>
-          <t>0.1325</t>
+          <t>0.1228</t>
         </is>
       </c>
       <c r="BH155" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="BI155" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>106 deg</t>
         </is>
       </c>
       <c r="BJ155" t="inlineStr">
@@ -50202,27 +50202,27 @@
       </c>
       <c r="BK155" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.9061&amp;lon=-75.1665</t>
         </is>
       </c>
       <c r="BL155" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM155" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
       <c r="BN155" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BO155" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BP155" t="inlineStr"/>
@@ -50243,27 +50243,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>543760</t>
+          <t>680779</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-17T23:10:00Z</t>
+          <t>2026-08-17T23:05:00Z</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -50273,22 +50273,22 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>664285</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -50306,26 +50306,26 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>25.2</v>
+        <v>35</v>
       </c>
       <c r="Q156" t="n">
-        <v>42.7</v>
+        <v>35.6</v>
       </c>
       <c r="R156" t="n">
-        <v>49.3</v>
+        <v>42.8</v>
       </c>
       <c r="S156" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T156" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U156" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="V156" t="n">
         <v>50</v>
@@ -50343,7 +50343,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -50390,7 +50390,7 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
@@ -50400,12 +50400,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 16.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -50415,102 +50415,102 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>89.51</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>97.5774</t>
+          <t>100.4627</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>0.3929</t>
+          <t>0.3505</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>0.1495</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>0.3075</t>
+          <t>0.2853</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>42.63</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BD156" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.06</t>
         </is>
       </c>
       <c r="BE156" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>90.24</t>
         </is>
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>0.4164</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="BG156" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1325</t>
         </is>
       </c>
       <c r="BH156" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="BI156" t="inlineStr">
         <is>
-          <t>191 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ156" t="inlineStr">
@@ -50520,27 +50520,27 @@
       </c>
       <c r="BK156" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.7571&amp;lon=-73.8458</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL156" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM156" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BN156" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO156" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP156" t="inlineStr"/>
@@ -50561,27 +50561,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>543760</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-17T23:10:00Z</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -50591,26 +50591,26 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -50624,26 +50624,26 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>22.2</v>
+        <v>25.2</v>
       </c>
       <c r="Q157" t="n">
-        <v>1.1</v>
+        <v>42.7</v>
       </c>
       <c r="R157" t="n">
-        <v>66.2</v>
+        <v>49.3</v>
       </c>
       <c r="S157" t="n">
-        <v>95.5</v>
+        <v>59.8</v>
       </c>
       <c r="T157" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U157" t="n">
-        <v>21.1</v>
+        <v>0.8</v>
       </c>
       <c r="V157" t="n">
         <v>50</v>
@@ -50661,7 +50661,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -50686,7 +50686,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr"/>
@@ -50703,12 +50703,12 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
@@ -50718,12 +50718,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -50733,102 +50733,102 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>98.1473</t>
+          <t>97.5774</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.3929</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1495</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.3075</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="BD157" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="BE157" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="BG157" t="inlineStr">
         <is>
-          <t>0.0651</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BH157" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="BI157" t="inlineStr">
         <is>
-          <t>144 deg</t>
+          <t>191 deg</t>
         </is>
       </c>
       <c r="BJ157" t="inlineStr">
@@ -50838,27 +50838,27 @@
       </c>
       <c r="BK157" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.7559&amp;lon=-104.9942</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.7571&amp;lon=-73.8458</t>
         </is>
       </c>
       <c r="BL157" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM157" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BN157" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BO157" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BP157" t="inlineStr"/>
@@ -50879,47 +50879,47 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>669911</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Michael Toglia</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-17T17:40:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Quinn Mathews</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>687273</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -50928,7 +50928,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -50942,26 +50942,26 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P158" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="Q158" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="R158" t="n">
-        <v>78.3</v>
+        <v>66.2</v>
       </c>
       <c r="S158" t="n">
-        <v>76.2</v>
+        <v>95.5</v>
       </c>
       <c r="T158" t="n">
         <v>75</v>
       </c>
       <c r="U158" t="n">
-        <v>7</v>
+        <v>21.1</v>
       </c>
       <c r="V158" t="n">
         <v>50</v>
@@ -50969,38 +50969,42 @@
       <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y158" t="inlineStr">
+      <c r="AB158" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr"/>
@@ -51012,17 +51016,17 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL158" t="inlineStr">
@@ -51032,117 +51036,117 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>Last 5 games: 2/12, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AR158" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>97.4919</t>
+          <t>98.1473</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr">
         <is>
-          <t>0.2467</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>0.0638</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>0.2248</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BD158" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BE158" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="BF158" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="BG158" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.0651</t>
         </is>
       </c>
       <c r="BH158" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BI158" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>144 deg</t>
         </is>
       </c>
       <c r="BJ158" t="inlineStr">
@@ -51152,27 +51156,27 @@
       </c>
       <c r="BK158" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.7559&amp;lon=-104.9942</t>
         </is>
       </c>
       <c r="BL158" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BM158" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BN158" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO158" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BP158" t="inlineStr"/>
@@ -51193,52 +51197,52 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>805347</t>
+          <t>669911</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>Michael Toglia</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T17:40:00Z</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>687273</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -51256,26 +51260,26 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P159" t="n">
-        <v>14.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q159" t="n">
-        <v>55.5</v>
+        <v>7.2</v>
       </c>
       <c r="R159" t="n">
-        <v>52.6</v>
+        <v>78.3</v>
       </c>
       <c r="S159" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T159" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U159" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="V159" t="n">
         <v>50</v>
@@ -51283,42 +51287,38 @@
       <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr"/>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr"/>
@@ -51330,7 +51330,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AJ159" t="inlineStr">
@@ -51340,7 +51340,7 @@
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AL159" t="inlineStr">
@@ -51350,117 +51350,117 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 5 games: 2/12, 0 HR</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 20.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>98.5322</t>
+          <t>97.4919</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.2467</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.0638</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.2248</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>35.62</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BD159" t="inlineStr">
         <is>
-          <t>36.23</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="BE159" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="BF159" t="inlineStr">
         <is>
-          <t>0.4669</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="BG159" t="inlineStr">
         <is>
-          <t>0.2147</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="BH159" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BI159" t="inlineStr">
         <is>
-          <t>330 deg</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ159" t="inlineStr">
@@ -51470,27 +51470,27 @@
       </c>
       <c r="BK159" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
         </is>
       </c>
       <c r="BL159" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BM159" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BN159" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO159" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BP159" t="inlineStr"/>
@@ -51511,24 +51511,24 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>805347</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>2026-08-17T23:40:00Z</t>
@@ -51541,22 +51541,22 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -51578,22 +51578,22 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q160" t="n">
-        <v>39</v>
+        <v>55.5</v>
       </c>
       <c r="R160" t="n">
         <v>52.6</v>
       </c>
       <c r="S160" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T160" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U160" t="n">
-        <v>43.2</v>
+        <v>0.8</v>
       </c>
       <c r="V160" t="n">
         <v>50</v>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -51636,7 +51636,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr"/>
@@ -51653,127 +51653,127 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 20.9 HR allowed</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>96.7373</t>
+          <t>98.5322</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>0.1104</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>0.3149</t>
+          <t>0.268</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>38.96</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>0.1171</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BD160" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>36.23</t>
         </is>
       </c>
       <c r="BE160" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.4669</t>
         </is>
       </c>
       <c r="BG160" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.2147</t>
         </is>
       </c>
       <c r="BH160" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="BI160" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1852,34 +1852,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2834,34 +2830,30 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3988,7 +3980,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4302,7 +4294,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -6940,7 +6932,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -10826,7 +10818,7 @@
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
@@ -11810,7 +11802,7 @@
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
@@ -15792,34 +15784,30 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22458,34 +22446,30 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC69" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24200,7 +24184,7 @@
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr">
@@ -31254,34 +31238,30 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC97" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD97" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -31740,7 +31720,7 @@
       </c>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr">
@@ -37158,7 +37138,7 @@
       </c>
       <c r="BI115" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ115" t="inlineStr">
@@ -40952,7 +40932,7 @@
       </c>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr">
@@ -45416,7 +45396,7 @@
       </c>
       <c r="BI141" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ141" t="inlineStr">
@@ -45730,7 +45710,7 @@
       </c>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr">
@@ -47446,34 +47426,30 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC148" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD148" t="inlineStr"/>
       <c r="AE148" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48078,34 +48054,30 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC150" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD150" t="inlineStr"/>
       <c r="AE150" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48878,7 +48850,7 @@
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr">
@@ -49696,34 +49668,30 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC155" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD155" t="inlineStr"/>
       <c r="AE155" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -52244,34 +52212,30 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC163" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD163" t="inlineStr"/>
       <c r="AE163" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57780,7 +57744,7 @@
       </c>
       <c r="BI180" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ180" t="inlineStr">
@@ -69094,7 +69058,7 @@
       </c>
       <c r="BI216" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ216" t="inlineStr">
@@ -73164,7 +73128,7 @@
       </c>
       <c r="BI229" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ229" t="inlineStr">
@@ -78176,7 +78140,7 @@
       </c>
       <c r="BI245" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ245" t="inlineStr">
@@ -78804,7 +78768,7 @@
       </c>
       <c r="BI247" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ247" t="inlineStr">
@@ -83192,7 +83156,7 @@
       </c>
       <c r="BI261" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ261" t="inlineStr">
@@ -87818,34 +87782,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -88800,34 +88760,30 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -89954,7 +89910,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -90268,7 +90224,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -92906,7 +92862,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -20272,7 +20272,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -23050,7 +23050,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -25852,7 +25852,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -27712,7 +27712,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -28026,7 +28026,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -32200,7 +32200,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -32828,7 +32828,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -33432,7 +33432,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -35002,7 +35002,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -16946,7 +16946,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -18202,7 +18202,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -15978,7 +15978,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -22022,7 +22022,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -22960,7 +22960,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -26100,7 +26100,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -28026,7 +28026,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -29596,7 +29596,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -29910,7 +29910,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -30224,7 +30224,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -36514,7 +36514,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -38084,7 +38084,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -38398,7 +38398,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -40254,7 +40254,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -41842,7 +41842,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -42156,7 +42156,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -43098,7 +43098,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -44082,7 +44082,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -45314,7 +45314,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -47550,7 +47550,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -47864,7 +47864,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -49720,7 +49720,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -50034,7 +50034,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -51604,7 +51604,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -51918,7 +51918,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -53530,7 +53530,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -56042,7 +56042,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -56670,7 +56670,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -56984,7 +56984,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -57926,7 +57926,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -59182,7 +59182,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -59496,7 +59496,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -59810,7 +59810,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -61694,7 +61694,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -63984,7 +63984,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -64926,7 +64926,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -68104,7 +68104,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -68418,7 +68418,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -68732,7 +68732,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -17566,7 +17566,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -19178,7 +19178,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -19806,7 +19806,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -21418,7 +21418,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -25472,7 +25472,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -25786,7 +25786,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -27712,7 +27712,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -28340,7 +28340,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -31836,7 +31836,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -32126,7 +32126,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -33374,7 +33374,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -34002,7 +34002,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -34316,7 +34316,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -35572,7 +35572,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -35886,7 +35886,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -37456,7 +37456,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -37770,7 +37770,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -38712,7 +38712,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -39336,7 +39336,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -39940,7 +39940,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -40924,7 +40924,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -41214,7 +41214,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -41528,7 +41528,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -42470,7 +42470,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -42784,7 +42784,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -43412,7 +43412,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -43726,7 +43726,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -44396,7 +44396,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -44710,7 +44710,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -45628,7 +45628,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -46566,7 +46566,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -48488,7 +48488,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -49092,7 +49092,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -49406,7 +49406,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -50348,7 +50348,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -50662,7 +50662,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -52232,7 +52232,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -52588,7 +52588,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -53216,7 +53216,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -53844,7 +53844,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -54158,7 +54158,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -55100,7 +55100,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -55414,7 +55414,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -55728,7 +55728,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -57298,7 +57298,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -57612,7 +57612,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -58240,7 +58240,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -58554,7 +58554,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -60124,7 +60124,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -60438,7 +60438,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -61066,7 +61066,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -61380,7 +61380,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -62008,7 +62008,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -62322,7 +62322,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -62636,7 +62636,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -62950,7 +62950,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -63670,7 +63670,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -64298,7 +64298,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -64612,7 +64612,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -65240,7 +65240,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -65596,7 +65596,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -65910,7 +65910,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -66534,7 +66534,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -67162,7 +67162,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -67476,7 +67476,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -67790,7 +67790,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -69046,7 +69046,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -69336,7 +69336,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -15960,7 +15960,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21064,7 +21064,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22990,7 +22990,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>62.6</v>
+        <v>63</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -910,34 +910,30 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1095,7 +1091,7 @@
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1170,7 +1166,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.9</v>
+        <v>61.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1194,7 +1190,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1218,34 +1214,30 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1403,7 +1395,7 @@
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1518,7 +1510,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.5</v>
+        <v>58</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1542,7 +1534,7 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1564,34 +1556,30 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1749,7 +1737,7 @@
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -1824,7 +1812,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.9</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1848,7 +1836,7 @@
         <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -1870,34 +1858,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2055,7 +2039,7 @@
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -2130,7 +2114,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.8</v>
+        <v>54.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2154,7 +2138,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>86.40000000000001</v>
@@ -2178,34 +2162,30 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2363,7 +2343,7 @@
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -2478,7 +2458,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.8</v>
+        <v>53.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2502,7 +2482,7 @@
         <v>40.1</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -2524,34 +2504,30 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2709,7 +2685,7 @@
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -2784,7 +2760,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.4</v>
+        <v>52.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2808,7 +2784,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -2832,34 +2808,30 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3017,7 +2989,7 @@
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -3132,7 +3104,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3156,7 +3128,7 @@
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -3178,34 +3150,30 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3363,7 +3331,7 @@
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -3438,7 +3406,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>52.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3462,7 +3430,7 @@
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -3484,34 +3452,30 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3669,7 +3633,7 @@
       <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -3744,7 +3708,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3768,7 +3732,7 @@
         <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -3790,34 +3754,30 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3975,7 +3935,7 @@
       <c r="BM11" t="inlineStr"/>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -4050,7 +4010,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.9</v>
+        <v>49.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4074,7 +4034,7 @@
         <v>40.1</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -4096,34 +4056,30 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4281,7 +4237,7 @@
       <c r="BM12" t="inlineStr"/>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -4356,7 +4312,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4380,7 +4336,7 @@
         <v>35.9</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>52.4</v>
@@ -4404,34 +4360,30 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4589,7 +4541,7 @@
       <c r="BM13" t="inlineStr"/>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -4704,7 +4656,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.2</v>
+        <v>45.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4728,7 +4680,7 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -4752,34 +4704,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4937,7 +4885,7 @@
       <c r="BM14" t="inlineStr"/>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -5052,7 +5000,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5076,7 +5024,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -5098,34 +5046,30 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5283,7 +5227,7 @@
       <c r="BM15" t="inlineStr"/>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
@@ -5358,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5382,7 +5326,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -5402,28 +5346,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5581,7 +5529,7 @@
       <c r="BM16" t="inlineStr"/>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
@@ -5656,7 +5604,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.6</v>
+        <v>40.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5680,7 +5628,7 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -5702,34 +5650,30 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5887,7 +5831,7 @@
       <c r="BM17" t="inlineStr"/>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
@@ -5962,7 +5906,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.9</v>
+        <v>39.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5986,7 +5930,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -6008,34 +5952,30 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6193,7 +6133,7 @@
       <c r="BM18" t="inlineStr"/>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
@@ -6268,7 +6208,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.7</v>
+        <v>36.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6292,7 +6232,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -6314,34 +6254,30 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6499,7 +6435,7 @@
       <c r="BM19" t="inlineStr"/>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
@@ -6980,7 +6916,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>62.6</v>
+        <v>63</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7004,7 +6940,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -7026,34 +6962,30 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7211,7 +7143,7 @@
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -7286,7 +7218,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>60.9</v>
+        <v>61.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7310,7 +7242,7 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -7334,34 +7266,30 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7519,7 +7447,7 @@
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -7634,7 +7562,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.5</v>
+        <v>58</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7658,7 +7586,7 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -7680,34 +7608,30 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7865,7 +7789,7 @@
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -7940,7 +7864,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.9</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7964,7 +7888,7 @@
         <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>93.2</v>
@@ -7986,34 +7910,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8171,7 +8091,7 @@
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -8246,7 +8166,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.8</v>
+        <v>54.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8270,7 +8190,7 @@
         <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>86.40000000000001</v>
@@ -8294,34 +8214,30 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8479,7 +8395,7 @@
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -8594,7 +8510,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.8</v>
+        <v>53.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8618,7 +8534,7 @@
         <v>40.1</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>96.59999999999999</v>
@@ -8640,34 +8556,30 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8825,7 +8737,7 @@
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -8900,7 +8812,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.4</v>
+        <v>52.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8924,7 +8836,7 @@
         <v>35.9</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>93.2</v>
@@ -8948,34 +8860,30 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9133,7 +9041,7 @@
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -9248,7 +9156,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.3</v>
+        <v>52.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9272,7 +9180,7 @@
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -9294,34 +9202,30 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9479,7 +9383,7 @@
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -9554,7 +9458,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>52.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9578,7 +9482,7 @@
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>52.4</v>
@@ -9600,34 +9504,30 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9785,7 +9685,7 @@
       <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9860,7 +9760,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9884,7 +9784,7 @@
         <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>76.2</v>
@@ -9906,34 +9806,30 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10091,7 +9987,7 @@
       <c r="BM11" t="inlineStr"/>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -10166,7 +10062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>48.9</v>
+        <v>49.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10190,7 +10086,7 @@
         <v>40.1</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -10212,34 +10108,30 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10397,7 +10289,7 @@
       <c r="BM12" t="inlineStr"/>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -10472,7 +10364,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10496,7 +10388,7 @@
         <v>35.9</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>52.4</v>
@@ -10520,34 +10412,30 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10705,7 +10593,7 @@
       <c r="BM13" t="inlineStr"/>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
@@ -10820,7 +10708,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>45.2</v>
+        <v>45.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10844,7 +10732,7 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -10868,34 +10756,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11053,7 +10937,7 @@
       <c r="BM14" t="inlineStr"/>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
@@ -11168,7 +11052,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11192,7 +11076,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -11214,34 +11098,30 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11399,7 +11279,7 @@
       <c r="BM15" t="inlineStr"/>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
@@ -11474,7 +11354,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11498,7 +11378,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -11518,28 +11398,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11697,7 +11581,7 @@
       <c r="BM16" t="inlineStr"/>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
@@ -11772,7 +11656,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>39.6</v>
+        <v>40.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11796,7 +11680,7 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>64.3</v>
@@ -11818,34 +11702,30 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12003,7 +11883,7 @@
       <c r="BM17" t="inlineStr"/>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
@@ -12078,7 +11958,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.9</v>
+        <v>39.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12102,7 +11982,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -12124,34 +12004,30 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12309,7 +12185,7 @@
       <c r="BM18" t="inlineStr"/>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
@@ -12384,7 +12260,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.7</v>
+        <v>36.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12408,7 +12284,7 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -12430,34 +12306,30 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -12615,7 +12487,7 @@
       <c r="BM19" t="inlineStr"/>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -21410,7 +21410,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -28318,7 +28318,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -34598,7 +34598,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -36482,7 +36482,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -36796,7 +36796,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -37424,7 +37424,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -38052,7 +38052,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -40258,7 +40258,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -42234,7 +42234,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
